--- a/PATXOT 512/Diciembre/PATXOT 521 Diciembre.xlsx
+++ b/PATXOT 512/Diciembre/PATXOT 521 Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\PATXOT 512\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EFCA1C-509D-4A63-9359-5052FD59756D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3368D9-BF0F-4DF5-8B69-3718FFA961DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -1723,33 +1723,15 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1762,6 +1744,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1786,11 +1773,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1807,6 +1809,12 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1816,15 +1824,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2195,16 +2195,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>21</v>
       </c>
@@ -2212,79 +2212,79 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="25"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="168" t="s">
         <v>134</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="86" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="75"/>
       <c r="C16" s="11"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
         <v>135</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="213">
+      <c r="C17" s="174">
         <v>83523.360000000001</v>
       </c>
       <c r="D17" s="48"/>
       <c r="F17" s="14"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
       <c r="C18" s="173">
@@ -2292,34 +2292,34 @@
         <v>83523.360000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="86" t="s">
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
       <c r="C19" s="11"/>
     </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="75" t="s">
         <v>132</v>
       </c>
       <c r="B20" s="90"/>
-      <c r="C20" s="174">
+      <c r="C20" s="213">
         <v>37000</v>
       </c>
       <c r="F20" s="22"/>
     </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="75" t="s">
         <v>133</v>
       </c>
       <c r="B21" s="90"/>
-      <c r="C21" s="174">
+      <c r="C21" s="213">
         <v>36534.6</v>
       </c>
       <c r="F21" s="22"/>
     </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="75" t="s">
         <v>124</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="E22" s="14"/>
       <c r="F22" s="22"/>
     </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="88"/>
       <c r="B23" s="89"/>
       <c r="C23" s="60">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="F23" s="22"/>
     </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
         <v>78</v>
       </c>
@@ -2349,40 +2349,40 @@
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C25" s="61"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="61"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="75"/>
       <c r="B27" s="75"/>
       <c r="C27" s="84"/>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="75"/>
       <c r="B28" s="75"/>
       <c r="C28" s="85"/>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="75"/>
       <c r="B29" s="75"/>
       <c r="C29" s="85"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="63"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>40</v>
       </c>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E31" s="14"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
         <v>15</v>
       </c>
@@ -2403,15 +2403,15 @@
         <v>157057.96000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="145" t="s">
         <v>36</v>
       </c>
       <c r="B35" s="146"/>
       <c r="C35" s="147"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="143" t="s">
         <v>10</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>9</v>
       </c>
@@ -2433,7 +2433,7 @@
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>-157057.96000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>16</v>
       </c>
@@ -2463,23 +2463,23 @@
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19"/>
       <c r="B41" s="18"/>
       <c r="C41" s="20"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="19"/>
       <c r="B42" s="18"/>
       <c r="C42" s="20"/>
       <c r="F42" s="93"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="19"/>
       <c r="B43" s="18"/>
       <c r="C43" s="20"/>
     </row>
-    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="73" t="s">
         <v>57</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="75" t="s">
         <v>63</v>
       </c>
@@ -2498,17 +2498,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="75"/>
       <c r="B46" s="75"/>
       <c r="C46" s="82"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="83"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="79" t="s">
         <v>4</v>
       </c>
@@ -2518,22 +2518,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="18"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
@@ -2555,39 +2555,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
       <c r="E1" s="14">
         <v>159610.60999999999</v>
       </c>
-      <c r="H1" s="175" t="s">
+      <c r="H1" s="202" t="s">
         <v>131</v>
       </c>
-      <c r="I1" s="175"/>
+      <c r="I1" s="202"/>
       <c r="J1" s="14">
         <v>172630.83</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
@@ -2604,15 +2604,15 @@
       <c r="K2" s="100"/>
       <c r="L2" s="101"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="195" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="191" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="193" t="s">
+      <c r="D3" s="184" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2621,52 +2621,52 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="191" t="s">
+      <c r="G3" s="179" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="201" t="s">
+      <c r="I3" s="175" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="199" t="s">
+      <c r="J3" s="190" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="191" t="s">
+      <c r="K3" s="179" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="197"/>
-      <c r="B4" s="198"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="194"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="188"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="185"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="192"/>
+      <c r="G4" s="180"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="202"/>
-      <c r="J4" s="200"/>
-      <c r="K4" s="192"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="180"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="189">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="177">
         <v>1</v>
       </c>
-      <c r="B5" s="190"/>
+      <c r="B5" s="178"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
@@ -2702,11 +2702,11 @@
         <v>45849.318719999996</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="189">
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="177">
         <v>2</v>
       </c>
-      <c r="B6" s="190"/>
+      <c r="B6" s="178"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
@@ -2744,11 +2744,11 @@
         <v>39403.834783999991</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="189">
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="177">
         <v>3</v>
       </c>
-      <c r="B7" s="190"/>
+      <c r="B7" s="178"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
@@ -2786,11 +2786,11 @@
         <v>41397.283423999994</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="189">
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="177">
         <v>4</v>
       </c>
-      <c r="B8" s="190"/>
+      <c r="B8" s="178"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
@@ -2828,11 +2828,11 @@
         <v>49005.612399999998</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="189">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="177">
         <v>5</v>
       </c>
-      <c r="B9" s="190"/>
+      <c r="B9" s="178"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
@@ -2870,11 +2870,11 @@
         <v>41231.162704000002</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="189">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="177">
         <v>6</v>
       </c>
-      <c r="B10" s="190"/>
+      <c r="B10" s="178"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
@@ -2910,11 +2910,11 @@
         <v>41463.731711999993</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="189">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="177">
         <v>7</v>
       </c>
-      <c r="B11" s="190"/>
+      <c r="B11" s="178"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
@@ -2950,11 +2950,11 @@
         <v>60667.286943999999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="189" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="190"/>
+      <c r="B12" s="178"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -2991,11 +2991,11 @@
         <v>4452.035296</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="189" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="190"/>
+      <c r="B13" s="178"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3032,11 +3032,11 @@
         <v>4385.5870080000004</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="189" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="190"/>
+      <c r="B14" s="178"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -3073,7 +3073,7 @@
         <v>4385.5870080000004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>332241.44</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -3136,7 +3136,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -3194,7 +3194,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="27" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="26.25" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -3491,44 +3491,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="193"/>
+      <c r="G32" s="193"/>
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
+      <c r="K32" s="194"/>
       <c r="L32" s="151"/>
       <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="193"/>
+      <c r="H33" s="193"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="193"/>
+      <c r="K33" s="194"/>
       <c r="L33" s="153"/>
       <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="151"/>
@@ -3545,7 +3545,7 @@
       <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="153" t="s">
@@ -3561,7 +3561,7 @@
       <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="157"/>
@@ -3575,23 +3575,23 @@
       <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="198"/>
       <c r="L37" s="153"/>
       <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="153"/>
@@ -3605,7 +3605,7 @@
       <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="153" t="s">
@@ -3624,13 +3624,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="154"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="182"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="153" t="s">
@@ -3648,7 +3648,7 @@
       <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="153"/>
@@ -3658,11 +3658,11 @@
       <c r="I41" s="156"/>
       <c r="J41" s="156"/>
       <c r="K41" s="154"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="183"/>
+      <c r="M41" s="182"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="153" t="s">
@@ -3681,7 +3681,7 @@
       <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="163" t="s">
@@ -3700,7 +3700,7 @@
       <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="163" t="s">
@@ -3719,7 +3719,7 @@
       <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="163"/>
@@ -3733,7 +3733,7 @@
       <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="163"/>
@@ -3747,7 +3747,7 @@
       <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="156"/>
@@ -3760,7 +3760,7 @@
       <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="163"/>
@@ -3774,7 +3774,7 @@
       <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="153"/>
@@ -3788,7 +3788,7 @@
       <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="153" t="s">
@@ -3807,7 +3807,7 @@
       <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="153"/>
@@ -3821,58 +3821,58 @@
       <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="200"/>
+      <c r="G52" s="200"/>
+      <c r="H52" s="200"/>
+      <c r="I52" s="200"/>
+      <c r="J52" s="201">
         <f>SUM(J42:J51)</f>
         <v>41473.083423999997</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="194"/>
       <c r="L52" s="166"/>
       <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="194"/>
       <c r="L56" s="151"/>
       <c r="M56" s="152"/>
     </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="193"/>
+      <c r="G57" s="193"/>
+      <c r="H57" s="193"/>
+      <c r="I57" s="193"/>
+      <c r="J57" s="193"/>
+      <c r="K57" s="194"/>
       <c r="L57" s="153"/>
       <c r="M57" s="154"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E58" s="151"/>
       <c r="F58" s="155"/>
       <c r="G58" s="155"/>
@@ -3886,7 +3886,7 @@
       <c r="L58" s="153"/>
       <c r="M58" s="154"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="L59" s="153"/>
       <c r="M59" s="154"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E60" s="157"/>
       <c r="F60" s="158"/>
       <c r="G60" s="158"/>
@@ -3910,20 +3910,20 @@
       <c r="L60" s="153"/>
       <c r="M60" s="154"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
+      <c r="H61" s="197"/>
+      <c r="I61" s="197"/>
+      <c r="J61" s="197"/>
+      <c r="K61" s="198"/>
       <c r="L61" s="153"/>
       <c r="M61" s="154"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E62" s="153"/>
       <c r="F62" s="156"/>
       <c r="G62" s="156"/>
@@ -3934,7 +3934,7 @@
       <c r="L62" s="153"/>
       <c r="M62" s="154"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
@@ -3951,12 +3951,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="154"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="182"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
@@ -3971,7 +3971,7 @@
       <c r="L64" s="153"/>
       <c r="M64" s="154"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E65" s="153"/>
       <c r="F65" s="156"/>
       <c r="G65" s="156"/>
@@ -3979,10 +3979,10 @@
       <c r="I65" s="156"/>
       <c r="J65" s="156"/>
       <c r="K65" s="154"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="183"/>
+      <c r="M65" s="182"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
@@ -3998,7 +3998,7 @@
       <c r="L66" s="153"/>
       <c r="M66" s="154"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
@@ -4014,7 +4014,7 @@
       <c r="L67" s="153"/>
       <c r="M67" s="154"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="L68" s="153"/>
       <c r="M68" s="154"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E69" s="163"/>
       <c r="F69" s="156"/>
       <c r="G69" s="156"/>
@@ -4041,7 +4041,7 @@
       <c r="L69" s="153"/>
       <c r="M69" s="154"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E70" s="163"/>
       <c r="F70" s="156"/>
       <c r="G70" s="156"/>
@@ -4052,7 +4052,7 @@
       <c r="L70" s="153"/>
       <c r="M70" s="154"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="F71" s="156"/>
       <c r="G71" s="156"/>
       <c r="H71" s="156"/>
@@ -4062,7 +4062,7 @@
       <c r="L71" s="153"/>
       <c r="M71" s="154"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E72" s="163"/>
       <c r="F72" s="156"/>
       <c r="G72" s="156"/>
@@ -4073,7 +4073,7 @@
       <c r="L72" s="153"/>
       <c r="M72" s="154"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E73" s="153"/>
       <c r="F73" s="156"/>
       <c r="G73" s="156"/>
@@ -4084,7 +4084,7 @@
       <c r="L73" s="153"/>
       <c r="M73" s="154"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E74" s="153"/>
       <c r="F74" s="156"/>
       <c r="G74" s="156"/>
@@ -4095,7 +4095,7 @@
       <c r="L74" s="153"/>
       <c r="M74" s="154"/>
     </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="153"/>
       <c r="F75" s="156"/>
       <c r="G75" s="156"/>
@@ -4106,50 +4106,50 @@
       <c r="L75" s="164"/>
       <c r="M75" s="165"/>
     </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
+      <c r="H76" s="200"/>
+      <c r="I76" s="200"/>
+      <c r="J76" s="201">
         <f>SUM(J66:J75)</f>
         <v>49005.612399999998</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="194"/>
       <c r="L76" s="166"/>
       <c r="M76" s="167"/>
     </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="193"/>
+      <c r="G83" s="193"/>
+      <c r="H83" s="193"/>
+      <c r="I83" s="193"/>
+      <c r="J83" s="193"/>
+      <c r="K83" s="194"/>
       <c r="L83" s="151"/>
       <c r="M83" s="152"/>
     </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="193"/>
+      <c r="G84" s="193"/>
+      <c r="H84" s="193"/>
+      <c r="I84" s="193"/>
+      <c r="J84" s="193"/>
+      <c r="K84" s="194"/>
       <c r="L84" s="153"/>
       <c r="M84" s="154"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E85" s="151"/>
       <c r="F85" s="155"/>
       <c r="G85" s="155"/>
@@ -4163,7 +4163,7 @@
       <c r="L85" s="153"/>
       <c r="M85" s="154"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
@@ -4176,7 +4176,7 @@
       <c r="L86" s="153"/>
       <c r="M86" s="154"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E87" s="157"/>
       <c r="F87" s="158"/>
       <c r="G87" s="158"/>
@@ -4187,20 +4187,20 @@
       <c r="L87" s="153"/>
       <c r="M87" s="154"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="197"/>
+      <c r="G88" s="197"/>
+      <c r="H88" s="197"/>
+      <c r="I88" s="197"/>
+      <c r="J88" s="197"/>
+      <c r="K88" s="198"/>
       <c r="L88" s="153"/>
       <c r="M88" s="154"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E89" s="153"/>
       <c r="F89" s="156"/>
       <c r="G89" s="156"/>
@@ -4211,7 +4211,7 @@
       <c r="L89" s="153"/>
       <c r="M89" s="154"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
@@ -4228,12 +4228,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="154"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M90" s="182"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
@@ -4248,7 +4248,7 @@
       <c r="L91" s="153"/>
       <c r="M91" s="154"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E92" s="153"/>
       <c r="F92" s="156"/>
       <c r="G92" s="156"/>
@@ -4256,10 +4256,10 @@
       <c r="I92" s="156"/>
       <c r="J92" s="156"/>
       <c r="K92" s="154"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="183"/>
+      <c r="M92" s="182"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
@@ -4275,7 +4275,7 @@
       <c r="L93" s="153"/>
       <c r="M93" s="154"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
@@ -4291,7 +4291,7 @@
       <c r="L94" s="153"/>
       <c r="M94" s="154"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
@@ -4306,7 +4306,7 @@
       <c r="L95" s="153"/>
       <c r="M95" s="154"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E96" s="163"/>
       <c r="F96" s="156"/>
       <c r="G96" s="156"/>
@@ -4317,7 +4317,7 @@
       <c r="L96" s="153"/>
       <c r="M96" s="154"/>
     </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="163"/>
       <c r="F97" s="156"/>
       <c r="G97" s="156"/>
@@ -4328,7 +4328,7 @@
       <c r="L97" s="153"/>
       <c r="M97" s="154"/>
     </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F98" s="156"/>
       <c r="G98" s="156"/>
       <c r="H98" s="156"/>
@@ -4338,7 +4338,7 @@
       <c r="L98" s="153"/>
       <c r="M98" s="154"/>
     </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="163"/>
       <c r="F99" s="156"/>
       <c r="G99" s="156"/>
@@ -4349,7 +4349,7 @@
       <c r="L99" s="153"/>
       <c r="M99" s="154"/>
     </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E100" s="153"/>
       <c r="F100" s="156"/>
       <c r="G100" s="156"/>
@@ -4360,7 +4360,7 @@
       <c r="L100" s="153"/>
       <c r="M100" s="154"/>
     </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E101" s="153"/>
       <c r="F101" s="156"/>
       <c r="G101" s="156"/>
@@ -4371,7 +4371,7 @@
       <c r="L101" s="153"/>
       <c r="M101" s="154"/>
     </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E102" s="153"/>
       <c r="F102" s="156"/>
       <c r="G102" s="156"/>
@@ -4382,50 +4382,50 @@
       <c r="L102" s="164"/>
       <c r="M102" s="165"/>
     </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="200"/>
+      <c r="G103" s="200"/>
+      <c r="H103" s="200"/>
+      <c r="I103" s="200"/>
+      <c r="J103" s="201">
         <f>SUM(J93:J102)</f>
         <v>41487.621711999993</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="194"/>
       <c r="L103" s="166"/>
       <c r="M103" s="167"/>
     </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="193"/>
+      <c r="G108" s="193"/>
+      <c r="H108" s="193"/>
+      <c r="I108" s="193"/>
+      <c r="J108" s="193"/>
+      <c r="K108" s="194"/>
       <c r="L108" s="151"/>
       <c r="M108" s="152"/>
     </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="193"/>
+      <c r="G109" s="193"/>
+      <c r="H109" s="193"/>
+      <c r="I109" s="193"/>
+      <c r="J109" s="193"/>
+      <c r="K109" s="194"/>
       <c r="L109" s="153"/>
       <c r="M109" s="154"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E110" s="151"/>
       <c r="F110" s="155"/>
       <c r="G110" s="155"/>
@@ -4439,7 +4439,7 @@
       <c r="L110" s="153"/>
       <c r="M110" s="154"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
@@ -4452,7 +4452,7 @@
       <c r="L111" s="153"/>
       <c r="M111" s="154"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E112" s="157"/>
       <c r="F112" s="158"/>
       <c r="G112" s="158"/>
@@ -4463,20 +4463,20 @@
       <c r="L112" s="153"/>
       <c r="M112" s="154"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="197"/>
+      <c r="G113" s="197"/>
+      <c r="H113" s="197"/>
+      <c r="I113" s="197"/>
+      <c r="J113" s="197"/>
+      <c r="K113" s="198"/>
       <c r="L113" s="153"/>
       <c r="M113" s="154"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E114" s="153"/>
       <c r="F114" s="156"/>
       <c r="G114" s="156"/>
@@ -4487,7 +4487,7 @@
       <c r="L114" s="153"/>
       <c r="M114" s="154"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
@@ -4504,12 +4504,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="154"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="182"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
@@ -4524,7 +4524,7 @@
       <c r="L116" s="153"/>
       <c r="M116" s="154"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E117" s="153"/>
       <c r="F117" s="156"/>
       <c r="G117" s="156"/>
@@ -4532,10 +4532,10 @@
       <c r="I117" s="156"/>
       <c r="J117" s="156"/>
       <c r="K117" s="154"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="183"/>
+      <c r="M117" s="182"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
@@ -4551,7 +4551,7 @@
       <c r="L118" s="153"/>
       <c r="M118" s="154"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
@@ -4567,7 +4567,7 @@
       <c r="L119" s="153"/>
       <c r="M119" s="154"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
@@ -4583,7 +4583,7 @@
       <c r="L120" s="153"/>
       <c r="M120" s="154"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E121" s="163"/>
       <c r="F121" s="156"/>
       <c r="G121" s="156"/>
@@ -4594,7 +4594,7 @@
       <c r="L121" s="153"/>
       <c r="M121" s="154"/>
     </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E122" s="163"/>
       <c r="F122" s="156"/>
       <c r="G122" s="156"/>
@@ -4605,7 +4605,7 @@
       <c r="L122" s="153"/>
       <c r="M122" s="154"/>
     </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F123" s="156"/>
       <c r="G123" s="156"/>
       <c r="H123" s="156"/>
@@ -4615,7 +4615,7 @@
       <c r="L123" s="153"/>
       <c r="M123" s="154"/>
     </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E124" s="163"/>
       <c r="F124" s="156"/>
       <c r="G124" s="156"/>
@@ -4626,7 +4626,7 @@
       <c r="L124" s="153"/>
       <c r="M124" s="154"/>
     </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E125" s="153"/>
       <c r="F125" s="156"/>
       <c r="G125" s="156"/>
@@ -4637,7 +4637,7 @@
       <c r="L125" s="153"/>
       <c r="M125" s="154"/>
     </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E126" s="153"/>
       <c r="F126" s="156"/>
       <c r="G126" s="156"/>
@@ -4648,7 +4648,7 @@
       <c r="L126" s="153"/>
       <c r="M126" s="154"/>
     </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E127" s="153"/>
       <c r="F127" s="156"/>
       <c r="G127" s="156"/>
@@ -4659,29 +4659,49 @@
       <c r="L127" s="164"/>
       <c r="M127" s="165"/>
     </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="200"/>
+      <c r="G128" s="200"/>
+      <c r="H128" s="200"/>
+      <c r="I128" s="200"/>
+      <c r="J128" s="201">
         <f>SUM(J118:J127)</f>
         <v>45796.978719999999</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="194"/>
       <c r="L128" s="166"/>
       <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E108:K108"/>
+    <mergeCell ref="E109:K109"/>
+    <mergeCell ref="E113:K113"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="E57:K57"/>
+    <mergeCell ref="E61:K61"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E33:K33"/>
+    <mergeCell ref="E37:K37"/>
+    <mergeCell ref="E76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="C3:C4"/>
@@ -4698,31 +4718,11 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E108:K108"/>
-    <mergeCell ref="E109:K109"/>
-    <mergeCell ref="E113:K113"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="E56:K56"/>
-    <mergeCell ref="E57:K57"/>
-    <mergeCell ref="E61:K61"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="E33:K33"/>
-    <mergeCell ref="E37:K37"/>
-    <mergeCell ref="E76:I76"/>
-    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4733,16 +4733,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="110" t="s">
         <v>79</v>
       </c>
@@ -4762,12 +4762,12 @@
       <c r="K1" s="113"/>
       <c r="L1" s="114"/>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H2" s="115"/>
       <c r="I2" s="115"/>
       <c r="J2" s="115"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B3" s="116" t="s">
         <v>82</v>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="K3" s="5"/>
       <c r="M3" s="118"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" s="116"/>
       <c r="C4" s="110" t="s">
         <v>88</v>
@@ -4811,7 +4811,7 @@
       <c r="I4" s="119"/>
       <c r="J4" s="119"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>90</v>
       </c>
@@ -4844,7 +4844,7 @@
       <c r="L5" s="121"/>
       <c r="M5" s="122"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -4877,7 +4877,7 @@
       <c r="L6" s="121"/>
       <c r="M6" s="122"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>92</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="L7" s="121"/>
       <c r="M7" s="122"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>93</v>
       </c>
@@ -4942,7 +4942,7 @@
       <c r="L8" s="121"/>
       <c r="M8" s="122"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>94</v>
       </c>
@@ -4975,7 +4975,7 @@
       <c r="L9" s="121"/>
       <c r="M9" s="122"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>95</v>
       </c>
@@ -5008,7 +5008,7 @@
       <c r="L10" s="121"/>
       <c r="M10" s="122"/>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
@@ -5041,7 +5041,7 @@
       <c r="L11" s="121"/>
       <c r="M11" s="122"/>
     </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="124"/>
       <c r="C12" s="125">
         <f>SUM(C5:C11)</f>
@@ -5069,13 +5069,13 @@
       <c r="K12" s="124"/>
       <c r="L12" s="127"/>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C13" s="128"/>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
     </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>97</v>
       </c>
@@ -5087,7 +5087,7 @@
       <c r="I14" s="116"/>
       <c r="J14" s="116"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>98</v>
       </c>
@@ -5095,7 +5095,7 @@
       <c r="I15" s="116"/>
       <c r="J15" s="116"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B16" s="116"/>
       <c r="C16" s="110"/>
       <c r="D16" s="110"/>
@@ -5106,7 +5106,7 @@
       <c r="J16" s="110"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="116"/>
       <c r="C17" s="110"/>
       <c r="D17" s="110"/>
@@ -5116,12 +5116,12 @@
       <c r="I17" s="119"/>
       <c r="J17" s="119"/>
     </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H18" s="116"/>
       <c r="I18" s="116"/>
       <c r="J18" s="116"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C19" s="130"/>
       <c r="D19" s="131"/>
       <c r="E19" s="131"/>
@@ -5134,7 +5134,7 @@
       <c r="L19" s="131"/>
       <c r="M19" s="133"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C20" s="134"/>
       <c r="E20" t="s">
         <v>99</v>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="M20" s="136"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
       <c r="C21" s="134"/>
       <c r="D21" t="s">
         <v>101</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M21" s="136"/>
     </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C22" s="137"/>
       <c r="D22" s="138"/>
       <c r="E22" s="138"/>
@@ -5185,16 +5185,16 @@
       <c r="L22" s="138"/>
       <c r="M22" s="139"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K25" s="140" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G26" s="5"/>
       <c r="K26" s="118"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
         <v>105</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
         <v>95</v>
@@ -5221,7 +5221,7 @@
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
         <v>107</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
         <v>108</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J33" s="118" t="s">
         <v>109</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
       <c r="K34" s="112">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
@@ -5260,22 +5260,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="12" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="0.140625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="11" max="11" width="0.140625" customWidth="1"/>
     <col min="12" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D1" s="55">
         <v>50000</v>
       </c>
@@ -5285,14 +5285,14 @@
       <c r="I1" s="207"/>
       <c r="J1" s="207"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="1"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
         <v>56</v>
       </c>
@@ -5315,7 +5315,7 @@
       <c r="N3" s="31"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="P4" s="21"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5389,7 +5389,7 @@
       <c r="N5" s="204"/>
       <c r="P5" s="21"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="P6" s="21"/>
     </row>
-    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>2</v>
       </c>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P7" s="21"/>
     </row>
-    <row r="8" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>3</v>
       </c>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="P8" s="21"/>
     </row>
-    <row r="9" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>4</v>
       </c>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="P9" s="21"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>5</v>
       </c>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="P10" s="21"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>6</v>
       </c>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="P11" s="21"/>
     </row>
-    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>7</v>
       </c>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="P12" s="21"/>
     </row>
-    <row r="13" spans="1:16" ht="27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>8</v>
       </c>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="P13" s="21"/>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>11</v>
       </c>
@@ -5839,42 +5839,42 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N128"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="1.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="1.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="209" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="211" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="209" t="s">
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="211" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="209"/>
-      <c r="H1" s="209"/>
-      <c r="I1" s="210">
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="212">
         <v>800000</v>
       </c>
-      <c r="J1" s="210"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J1" s="212"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
       <c r="B2" s="97"/>
       <c r="C2" s="98"/>
@@ -5888,15 +5888,15 @@
       <c r="K2" s="100"/>
       <c r="L2" s="101"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="195" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="196"/>
-      <c r="C3" s="191" t="s">
+      <c r="B3" s="187"/>
+      <c r="C3" s="179" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="193" t="s">
+      <c r="D3" s="184" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5905,50 +5905,50 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="191" t="s">
+      <c r="G3" s="179" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="191" t="s">
+      <c r="H3" s="179" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="201" t="s">
+      <c r="I3" s="175" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="193" t="s">
+      <c r="J3" s="184" t="s">
         <v>128</v>
       </c>
       <c r="K3" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="L3" s="211" t="s">
+      <c r="L3" s="208" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="197"/>
-      <c r="B4" s="198"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="194"/>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="188"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="185"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="192"/>
-      <c r="H4" s="192"/>
-      <c r="I4" s="202"/>
-      <c r="J4" s="194"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="176"/>
+      <c r="J4" s="185"/>
       <c r="K4" s="170" t="s">
         <v>129</v>
       </c>
-      <c r="L4" s="212"/>
-    </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="189">
+      <c r="L4" s="209"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="177">
         <v>1</v>
       </c>
-      <c r="B5" s="190"/>
+      <c r="B5" s="178"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
@@ -5984,11 +5984,11 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A6" s="189">
+    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="177">
         <v>2</v>
       </c>
-      <c r="B6" s="190"/>
+      <c r="B6" s="178"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
@@ -6026,11 +6026,11 @@
         <v>64880.003495999961</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="189">
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="177">
         <v>3</v>
       </c>
-      <c r="B7" s="190"/>
+      <c r="B7" s="178"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
@@ -6068,11 +6068,11 @@
         <v>99680</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="189">
+    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="177">
         <v>4</v>
       </c>
-      <c r="B8" s="190"/>
+      <c r="B8" s="178"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
@@ -6110,11 +6110,11 @@
         <v>118000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="189">
+    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="177">
         <v>5</v>
       </c>
-      <c r="B9" s="190"/>
+      <c r="B9" s="178"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
@@ -6152,11 +6152,11 @@
         <v>99279.992624999984</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="189">
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="177">
         <v>6</v>
       </c>
-      <c r="B10" s="190"/>
+      <c r="B10" s="178"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
@@ -6192,11 +6192,11 @@
         <v>94999.311648000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="189">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="177">
         <v>7</v>
       </c>
-      <c r="B11" s="190"/>
+      <c r="B11" s="178"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
@@ -6232,11 +6232,11 @@
         <v>146080.00000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="189" t="s">
+    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="190"/>
+      <c r="B12" s="178"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
@@ -6273,11 +6273,11 @@
         <v>10720</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="189" t="s">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="190"/>
+      <c r="B13" s="178"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6314,11 +6314,11 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="189" t="s">
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="190"/>
+      <c r="B14" s="178"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
@@ -6355,7 +6355,7 @@
         <v>10560</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="103" t="s">
         <v>11</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>765159.30776899995</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
         <v>49</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>7454</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>51</v>
       </c>
@@ -6421,7 +6421,7 @@
       <c r="K19" s="53"/>
       <c r="L19" s="31"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>0</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6479,7 +6479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>1</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>2</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>3</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>6</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>7</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="40.200000000000003" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="39" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>8</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>11</v>
       </c>
@@ -6776,44 +6776,44 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="N31"/>
     </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="180" t="s">
+      <c r="E32" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="181"/>
-      <c r="G32" s="181"/>
-      <c r="H32" s="181"/>
-      <c r="I32" s="181"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="179"/>
+      <c r="F32" s="193"/>
+      <c r="G32" s="193"/>
+      <c r="H32" s="193"/>
+      <c r="I32" s="193"/>
+      <c r="J32" s="193"/>
+      <c r="K32" s="194"/>
       <c r="L32" s="151"/>
       <c r="M32" s="152"/>
       <c r="N32"/>
     </row>
-    <row r="33" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="182" t="s">
+      <c r="E33" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
-      <c r="H33" s="181"/>
-      <c r="I33" s="181"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="179"/>
+      <c r="F33" s="193"/>
+      <c r="G33" s="193"/>
+      <c r="H33" s="193"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="193"/>
+      <c r="K33" s="194"/>
       <c r="L33" s="153"/>
       <c r="M33" s="154"/>
       <c r="N33"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="151"/>
@@ -6830,7 +6830,7 @@
       <c r="M34" s="154"/>
       <c r="N34"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="153" t="s">
@@ -6846,7 +6846,7 @@
       <c r="M35" s="154"/>
       <c r="N35"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="157"/>
@@ -6860,23 +6860,23 @@
       <c r="M36" s="154"/>
       <c r="N36"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="183" t="s">
+      <c r="E37" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="184"/>
-      <c r="G37" s="184"/>
-      <c r="H37" s="184"/>
-      <c r="I37" s="184"/>
-      <c r="J37" s="184"/>
-      <c r="K37" s="185"/>
+      <c r="F37" s="197"/>
+      <c r="G37" s="197"/>
+      <c r="H37" s="197"/>
+      <c r="I37" s="197"/>
+      <c r="J37" s="197"/>
+      <c r="K37" s="198"/>
       <c r="L37" s="153"/>
       <c r="M37" s="154"/>
       <c r="N37"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="153"/>
@@ -6890,7 +6890,7 @@
       <c r="M38" s="154"/>
       <c r="N38"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="153" t="s">
@@ -6909,13 +6909,13 @@
         <v>45674</v>
       </c>
       <c r="K39" s="154"/>
-      <c r="L39" s="186" t="s">
+      <c r="L39" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="187"/>
+      <c r="M39" s="182"/>
       <c r="N39"/>
     </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="153" t="s">
@@ -6933,7 +6933,7 @@
       <c r="M40" s="154"/>
       <c r="N40"/>
     </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="153"/>
@@ -6943,11 +6943,11 @@
       <c r="I41" s="156"/>
       <c r="J41" s="156"/>
       <c r="K41" s="154"/>
-      <c r="L41" s="188"/>
-      <c r="M41" s="187"/>
+      <c r="L41" s="183"/>
+      <c r="M41" s="182"/>
       <c r="N41"/>
     </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="153" t="s">
@@ -6966,7 +6966,7 @@
       <c r="M42" s="154"/>
       <c r="N42"/>
     </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="163" t="s">
@@ -6985,7 +6985,7 @@
       <c r="M43" s="154"/>
       <c r="N43"/>
     </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="163" t="s">
@@ -7004,7 +7004,7 @@
       <c r="M44" s="154"/>
       <c r="N44"/>
     </row>
-    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="163"/>
@@ -7018,7 +7018,7 @@
       <c r="M45" s="154"/>
       <c r="N45"/>
     </row>
-    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="163"/>
@@ -7032,7 +7032,7 @@
       <c r="M46" s="154"/>
       <c r="N46"/>
     </row>
-    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="F47" s="156"/>
@@ -7045,7 +7045,7 @@
       <c r="M47" s="154"/>
       <c r="N47"/>
     </row>
-    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="163"/>
@@ -7059,7 +7059,7 @@
       <c r="M48" s="154"/>
       <c r="N48"/>
     </row>
-    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="153"/>
@@ -7073,7 +7073,7 @@
       <c r="M49" s="154"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="153" t="s">
@@ -7092,7 +7092,7 @@
       <c r="M50" s="154"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="153"/>
@@ -7106,58 +7106,58 @@
       <c r="M51" s="165"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="176" t="s">
+      <c r="E52" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="178">
+      <c r="F52" s="200"/>
+      <c r="G52" s="200"/>
+      <c r="H52" s="200"/>
+      <c r="I52" s="200"/>
+      <c r="J52" s="201">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="179"/>
+      <c r="K52" s="194"/>
       <c r="L52" s="166"/>
       <c r="M52" s="167"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="N53"/>
     </row>
-    <row r="55" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="56" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E56" s="180" t="s">
+    <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E56" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="181"/>
-      <c r="G56" s="181"/>
-      <c r="H56" s="181"/>
-      <c r="I56" s="181"/>
-      <c r="J56" s="181"/>
-      <c r="K56" s="179"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="194"/>
       <c r="L56" s="151"/>
       <c r="M56" s="152"/>
     </row>
-    <row r="57" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="182" t="s">
+    <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E57" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="181"/>
-      <c r="G57" s="181"/>
-      <c r="H57" s="181"/>
-      <c r="I57" s="181"/>
-      <c r="J57" s="181"/>
-      <c r="K57" s="179"/>
+      <c r="F57" s="193"/>
+      <c r="G57" s="193"/>
+      <c r="H57" s="193"/>
+      <c r="I57" s="193"/>
+      <c r="J57" s="193"/>
+      <c r="K57" s="194"/>
       <c r="L57" s="153"/>
       <c r="M57" s="154"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E58" s="151"/>
       <c r="F58" s="155"/>
       <c r="G58" s="155"/>
@@ -7171,7 +7171,7 @@
       <c r="L58" s="153"/>
       <c r="M58" s="154"/>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E59" s="153" t="s">
         <v>113</v>
       </c>
@@ -7184,7 +7184,7 @@
       <c r="L59" s="153"/>
       <c r="M59" s="154"/>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E60" s="157"/>
       <c r="F60" s="158"/>
       <c r="G60" s="158"/>
@@ -7195,20 +7195,20 @@
       <c r="L60" s="153"/>
       <c r="M60" s="154"/>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="E61" s="183" t="s">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="E61" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="185"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
+      <c r="H61" s="197"/>
+      <c r="I61" s="197"/>
+      <c r="J61" s="197"/>
+      <c r="K61" s="198"/>
       <c r="L61" s="153"/>
       <c r="M61" s="154"/>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E62" s="153"/>
       <c r="F62" s="156"/>
       <c r="G62" s="156"/>
@@ -7219,7 +7219,7 @@
       <c r="L62" s="153"/>
       <c r="M62" s="154"/>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E63" s="153" t="s">
         <v>114</v>
       </c>
@@ -7236,12 +7236,12 @@
         <v>45674</v>
       </c>
       <c r="K63" s="154"/>
-      <c r="L63" s="186" t="s">
+      <c r="L63" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="187"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="M63" s="182"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.25">
       <c r="E64" s="153" t="s">
         <v>117</v>
       </c>
@@ -7256,7 +7256,7 @@
       <c r="L64" s="153"/>
       <c r="M64" s="154"/>
     </row>
-    <row r="65" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E65" s="153"/>
       <c r="F65" s="156"/>
       <c r="G65" s="156"/>
@@ -7264,10 +7264,10 @@
       <c r="I65" s="156"/>
       <c r="J65" s="156"/>
       <c r="K65" s="154"/>
-      <c r="L65" s="188"/>
-      <c r="M65" s="187"/>
-    </row>
-    <row r="66" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L65" s="183"/>
+      <c r="M65" s="182"/>
+    </row>
+    <row r="66" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E66" s="153" t="s">
         <v>48</v>
       </c>
@@ -7283,7 +7283,7 @@
       <c r="L66" s="153"/>
       <c r="M66" s="154"/>
     </row>
-    <row r="67" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E67" s="163" t="s">
         <v>118</v>
       </c>
@@ -7299,7 +7299,7 @@
       <c r="L67" s="153"/>
       <c r="M67" s="154"/>
     </row>
-    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E68" s="163" t="s">
         <v>120</v>
       </c>
@@ -7315,7 +7315,7 @@
       <c r="L68" s="153"/>
       <c r="M68" s="154"/>
     </row>
-    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E69" s="163"/>
       <c r="F69" s="156"/>
       <c r="G69" s="156"/>
@@ -7326,7 +7326,7 @@
       <c r="L69" s="153"/>
       <c r="M69" s="154"/>
     </row>
-    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E70" s="163"/>
       <c r="F70" s="156"/>
       <c r="G70" s="156"/>
@@ -7337,7 +7337,7 @@
       <c r="L70" s="153"/>
       <c r="M70" s="154"/>
     </row>
-    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="F71" s="156"/>
       <c r="G71" s="156"/>
       <c r="H71" s="156"/>
@@ -7347,7 +7347,7 @@
       <c r="L71" s="153"/>
       <c r="M71" s="154"/>
     </row>
-    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E72" s="163"/>
       <c r="F72" s="156"/>
       <c r="G72" s="156"/>
@@ -7358,7 +7358,7 @@
       <c r="L72" s="153"/>
       <c r="M72" s="154"/>
     </row>
-    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E73" s="153"/>
       <c r="F73" s="156"/>
       <c r="G73" s="156"/>
@@ -7369,7 +7369,7 @@
       <c r="L73" s="153"/>
       <c r="M73" s="154"/>
     </row>
-    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="E74" s="153"/>
       <c r="F74" s="156"/>
       <c r="G74" s="156"/>
@@ -7380,7 +7380,7 @@
       <c r="L74" s="153"/>
       <c r="M74" s="154"/>
     </row>
-    <row r="75" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E75" s="153"/>
       <c r="F75" s="156"/>
       <c r="G75" s="156"/>
@@ -7391,50 +7391,50 @@
       <c r="L75" s="164"/>
       <c r="M75" s="165"/>
     </row>
-    <row r="76" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E76" s="176" t="s">
+    <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E76" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="178">
+      <c r="F76" s="200"/>
+      <c r="G76" s="200"/>
+      <c r="H76" s="200"/>
+      <c r="I76" s="200"/>
+      <c r="J76" s="201">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="179"/>
+      <c r="K76" s="194"/>
       <c r="L76" s="166"/>
       <c r="M76" s="167"/>
     </row>
-    <row r="82" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="83" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="180" t="s">
+    <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E83" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="181"/>
-      <c r="I83" s="181"/>
-      <c r="J83" s="181"/>
-      <c r="K83" s="179"/>
+      <c r="F83" s="193"/>
+      <c r="G83" s="193"/>
+      <c r="H83" s="193"/>
+      <c r="I83" s="193"/>
+      <c r="J83" s="193"/>
+      <c r="K83" s="194"/>
       <c r="L83" s="151"/>
       <c r="M83" s="152"/>
     </row>
-    <row r="84" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="182" t="s">
+    <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E84" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="181"/>
-      <c r="G84" s="181"/>
-      <c r="H84" s="181"/>
-      <c r="I84" s="181"/>
-      <c r="J84" s="181"/>
-      <c r="K84" s="179"/>
+      <c r="F84" s="193"/>
+      <c r="G84" s="193"/>
+      <c r="H84" s="193"/>
+      <c r="I84" s="193"/>
+      <c r="J84" s="193"/>
+      <c r="K84" s="194"/>
       <c r="L84" s="153"/>
       <c r="M84" s="154"/>
     </row>
-    <row r="85" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E85" s="151"/>
       <c r="F85" s="155"/>
       <c r="G85" s="155"/>
@@ -7448,7 +7448,7 @@
       <c r="L85" s="153"/>
       <c r="M85" s="154"/>
     </row>
-    <row r="86" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E86" s="153" t="s">
         <v>113</v>
       </c>
@@ -7461,7 +7461,7 @@
       <c r="L86" s="153"/>
       <c r="M86" s="154"/>
     </row>
-    <row r="87" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E87" s="157"/>
       <c r="F87" s="158"/>
       <c r="G87" s="158"/>
@@ -7472,20 +7472,20 @@
       <c r="L87" s="153"/>
       <c r="M87" s="154"/>
     </row>
-    <row r="88" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E88" s="183" t="s">
+    <row r="88" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E88" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="184"/>
-      <c r="G88" s="184"/>
-      <c r="H88" s="184"/>
-      <c r="I88" s="184"/>
-      <c r="J88" s="184"/>
-      <c r="K88" s="185"/>
+      <c r="F88" s="197"/>
+      <c r="G88" s="197"/>
+      <c r="H88" s="197"/>
+      <c r="I88" s="197"/>
+      <c r="J88" s="197"/>
+      <c r="K88" s="198"/>
       <c r="L88" s="153"/>
       <c r="M88" s="154"/>
     </row>
-    <row r="89" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E89" s="153"/>
       <c r="F89" s="156"/>
       <c r="G89" s="156"/>
@@ -7496,7 +7496,7 @@
       <c r="L89" s="153"/>
       <c r="M89" s="154"/>
     </row>
-    <row r="90" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E90" s="153" t="s">
         <v>114</v>
       </c>
@@ -7513,12 +7513,12 @@
         <v>45674</v>
       </c>
       <c r="K90" s="154"/>
-      <c r="L90" s="186" t="s">
+      <c r="L90" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="187"/>
-    </row>
-    <row r="91" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M90" s="182"/>
+    </row>
+    <row r="91" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E91" s="153" t="s">
         <v>117</v>
       </c>
@@ -7533,7 +7533,7 @@
       <c r="L91" s="153"/>
       <c r="M91" s="154"/>
     </row>
-    <row r="92" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E92" s="153"/>
       <c r="F92" s="156"/>
       <c r="G92" s="156"/>
@@ -7541,10 +7541,10 @@
       <c r="I92" s="156"/>
       <c r="J92" s="156"/>
       <c r="K92" s="154"/>
-      <c r="L92" s="188"/>
-      <c r="M92" s="187"/>
-    </row>
-    <row r="93" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L92" s="183"/>
+      <c r="M92" s="182"/>
+    </row>
+    <row r="93" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E93" s="153" t="s">
         <v>48</v>
       </c>
@@ -7560,7 +7560,7 @@
       <c r="L93" s="153"/>
       <c r="M93" s="154"/>
     </row>
-    <row r="94" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E94" s="163" t="s">
         <v>118</v>
       </c>
@@ -7576,7 +7576,7 @@
       <c r="L94" s="153"/>
       <c r="M94" s="154"/>
     </row>
-    <row r="95" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E95" s="163" t="s">
         <v>121</v>
       </c>
@@ -7591,7 +7591,7 @@
       <c r="L95" s="153"/>
       <c r="M95" s="154"/>
     </row>
-    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E96" s="163"/>
       <c r="F96" s="156"/>
       <c r="G96" s="156"/>
@@ -7602,7 +7602,7 @@
       <c r="L96" s="153"/>
       <c r="M96" s="154"/>
     </row>
-    <row r="97" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E97" s="163"/>
       <c r="F97" s="156"/>
       <c r="G97" s="156"/>
@@ -7613,7 +7613,7 @@
       <c r="L97" s="153"/>
       <c r="M97" s="154"/>
     </row>
-    <row r="98" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F98" s="156"/>
       <c r="G98" s="156"/>
       <c r="H98" s="156"/>
@@ -7623,7 +7623,7 @@
       <c r="L98" s="153"/>
       <c r="M98" s="154"/>
     </row>
-    <row r="99" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E99" s="163"/>
       <c r="F99" s="156"/>
       <c r="G99" s="156"/>
@@ -7634,7 +7634,7 @@
       <c r="L99" s="153"/>
       <c r="M99" s="154"/>
     </row>
-    <row r="100" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E100" s="153"/>
       <c r="F100" s="156"/>
       <c r="G100" s="156"/>
@@ -7645,7 +7645,7 @@
       <c r="L100" s="153"/>
       <c r="M100" s="154"/>
     </row>
-    <row r="101" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E101" s="153"/>
       <c r="F101" s="156"/>
       <c r="G101" s="156"/>
@@ -7656,7 +7656,7 @@
       <c r="L101" s="153"/>
       <c r="M101" s="154"/>
     </row>
-    <row r="102" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E102" s="153"/>
       <c r="F102" s="156"/>
       <c r="G102" s="156"/>
@@ -7667,50 +7667,50 @@
       <c r="L102" s="164"/>
       <c r="M102" s="165"/>
     </row>
-    <row r="103" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="176" t="s">
+    <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E103" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="177"/>
-      <c r="G103" s="177"/>
-      <c r="H103" s="177"/>
-      <c r="I103" s="177"/>
-      <c r="J103" s="178">
+      <c r="F103" s="200"/>
+      <c r="G103" s="200"/>
+      <c r="H103" s="200"/>
+      <c r="I103" s="200"/>
+      <c r="J103" s="201">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="179"/>
+      <c r="K103" s="194"/>
       <c r="L103" s="166"/>
       <c r="M103" s="167"/>
     </row>
-    <row r="107" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="108" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E108" s="180" t="s">
+    <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E108" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="181"/>
-      <c r="G108" s="181"/>
-      <c r="H108" s="181"/>
-      <c r="I108" s="181"/>
-      <c r="J108" s="181"/>
-      <c r="K108" s="179"/>
+      <c r="F108" s="193"/>
+      <c r="G108" s="193"/>
+      <c r="H108" s="193"/>
+      <c r="I108" s="193"/>
+      <c r="J108" s="193"/>
+      <c r="K108" s="194"/>
       <c r="L108" s="151"/>
       <c r="M108" s="152"/>
     </row>
-    <row r="109" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E109" s="182" t="s">
+    <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E109" s="195" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="181"/>
-      <c r="G109" s="181"/>
-      <c r="H109" s="181"/>
-      <c r="I109" s="181"/>
-      <c r="J109" s="181"/>
-      <c r="K109" s="179"/>
+      <c r="F109" s="193"/>
+      <c r="G109" s="193"/>
+      <c r="H109" s="193"/>
+      <c r="I109" s="193"/>
+      <c r="J109" s="193"/>
+      <c r="K109" s="194"/>
       <c r="L109" s="153"/>
       <c r="M109" s="154"/>
     </row>
-    <row r="110" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E110" s="151"/>
       <c r="F110" s="155"/>
       <c r="G110" s="155"/>
@@ -7724,7 +7724,7 @@
       <c r="L110" s="153"/>
       <c r="M110" s="154"/>
     </row>
-    <row r="111" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E111" s="153" t="s">
         <v>113</v>
       </c>
@@ -7737,7 +7737,7 @@
       <c r="L111" s="153"/>
       <c r="M111" s="154"/>
     </row>
-    <row r="112" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E112" s="157"/>
       <c r="F112" s="158"/>
       <c r="G112" s="158"/>
@@ -7748,20 +7748,20 @@
       <c r="L112" s="153"/>
       <c r="M112" s="154"/>
     </row>
-    <row r="113" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E113" s="183" t="s">
+    <row r="113" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E113" s="196" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="184"/>
-      <c r="G113" s="184"/>
-      <c r="H113" s="184"/>
-      <c r="I113" s="184"/>
-      <c r="J113" s="184"/>
-      <c r="K113" s="185"/>
+      <c r="F113" s="197"/>
+      <c r="G113" s="197"/>
+      <c r="H113" s="197"/>
+      <c r="I113" s="197"/>
+      <c r="J113" s="197"/>
+      <c r="K113" s="198"/>
       <c r="L113" s="153"/>
       <c r="M113" s="154"/>
     </row>
-    <row r="114" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E114" s="153"/>
       <c r="F114" s="156"/>
       <c r="G114" s="156"/>
@@ -7772,7 +7772,7 @@
       <c r="L114" s="153"/>
       <c r="M114" s="154"/>
     </row>
-    <row r="115" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E115" s="153" t="s">
         <v>114</v>
       </c>
@@ -7789,12 +7789,12 @@
         <v>45674</v>
       </c>
       <c r="K115" s="154"/>
-      <c r="L115" s="186" t="s">
+      <c r="L115" s="181" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="187"/>
-    </row>
-    <row r="116" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="M115" s="182"/>
+    </row>
+    <row r="116" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E116" s="153" t="s">
         <v>117</v>
       </c>
@@ -7809,7 +7809,7 @@
       <c r="L116" s="153"/>
       <c r="M116" s="154"/>
     </row>
-    <row r="117" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E117" s="153"/>
       <c r="F117" s="156"/>
       <c r="G117" s="156"/>
@@ -7817,10 +7817,10 @@
       <c r="I117" s="156"/>
       <c r="J117" s="156"/>
       <c r="K117" s="154"/>
-      <c r="L117" s="188"/>
-      <c r="M117" s="187"/>
-    </row>
-    <row r="118" spans="5:13" x14ac:dyDescent="0.3">
+      <c r="L117" s="183"/>
+      <c r="M117" s="182"/>
+    </row>
+    <row r="118" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E118" s="153" t="s">
         <v>48</v>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="L118" s="153"/>
       <c r="M118" s="154"/>
     </row>
-    <row r="119" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E119" s="163" t="s">
         <v>118</v>
       </c>
@@ -7852,7 +7852,7 @@
       <c r="L119" s="153"/>
       <c r="M119" s="154"/>
     </row>
-    <row r="120" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E120" s="163" t="s">
         <v>122</v>
       </c>
@@ -7868,7 +7868,7 @@
       <c r="L120" s="153"/>
       <c r="M120" s="154"/>
     </row>
-    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E121" s="163"/>
       <c r="F121" s="156"/>
       <c r="G121" s="156"/>
@@ -7879,7 +7879,7 @@
       <c r="L121" s="153"/>
       <c r="M121" s="154"/>
     </row>
-    <row r="122" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E122" s="163"/>
       <c r="F122" s="156"/>
       <c r="G122" s="156"/>
@@ -7890,7 +7890,7 @@
       <c r="L122" s="153"/>
       <c r="M122" s="154"/>
     </row>
-    <row r="123" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F123" s="156"/>
       <c r="G123" s="156"/>
       <c r="H123" s="156"/>
@@ -7900,7 +7900,7 @@
       <c r="L123" s="153"/>
       <c r="M123" s="154"/>
     </row>
-    <row r="124" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E124" s="163"/>
       <c r="F124" s="156"/>
       <c r="G124" s="156"/>
@@ -7911,7 +7911,7 @@
       <c r="L124" s="153"/>
       <c r="M124" s="154"/>
     </row>
-    <row r="125" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E125" s="153"/>
       <c r="F125" s="156"/>
       <c r="G125" s="156"/>
@@ -7922,7 +7922,7 @@
       <c r="L125" s="153"/>
       <c r="M125" s="154"/>
     </row>
-    <row r="126" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E126" s="153"/>
       <c r="F126" s="156"/>
       <c r="G126" s="156"/>
@@ -7933,7 +7933,7 @@
       <c r="L126" s="153"/>
       <c r="M126" s="154"/>
     </row>
-    <row r="127" spans="5:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E127" s="153"/>
       <c r="F127" s="156"/>
       <c r="G127" s="156"/>
@@ -7944,24 +7944,58 @@
       <c r="L127" s="164"/>
       <c r="M127" s="165"/>
     </row>
-    <row r="128" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E128" s="176" t="s">
+    <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E128" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="177"/>
-      <c r="G128" s="177"/>
-      <c r="H128" s="177"/>
-      <c r="I128" s="177"/>
-      <c r="J128" s="178">
+      <c r="F128" s="200"/>
+      <c r="G128" s="200"/>
+      <c r="H128" s="200"/>
+      <c r="I128" s="200"/>
+      <c r="J128" s="201">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="179"/>
+      <c r="K128" s="194"/>
       <c r="L128" s="166"/>
       <c r="M128" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -7978,40 +8012,6 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/PATXOT 512/Diciembre/PATXOT 521 Diciembre.xlsx
+++ b/PATXOT 512/Diciembre/PATXOT 521 Diciembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PATXOT 512\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3368D9-BF0F-4DF5-8B69-3718FFA961DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7BF0F2-BE62-4834-AC88-D2DB7554A4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$41</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'PRORRATEO EXPRESS'!$A$1:$L$16</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="136">
   <si>
     <t>UF</t>
   </si>
@@ -401,9 +401,6 @@
     <t>ABONA DE MENOS</t>
   </si>
   <si>
-    <t>ENERO 2025</t>
-  </si>
-  <si>
     <t>Prevision ordinaria</t>
   </si>
   <si>
@@ -425,9 +422,6 @@
     <t>MANO DE OBRA (2/2)</t>
   </si>
   <si>
-    <t>EDESUR:</t>
-  </si>
-  <si>
     <t>Honorarios Administracion</t>
   </si>
   <si>
@@ -441,6 +435,9 @@
   </si>
   <si>
     <t>Edesur - DICIEMBRE</t>
+  </si>
+  <si>
+    <t>DICIEMBRE 2025</t>
   </si>
 </sst>
 </file>
@@ -1452,7 +1449,7 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1654,9 +1651,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1722,16 +1716,32 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1744,11 +1754,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1773,26 +1778,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="22" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1809,12 +1799,6 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1824,7 +1808,24 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2228,8 +2229,8 @@
       <c r="C5" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="168" t="s">
-        <v>134</v>
+      <c r="A7" s="167" t="s">
+        <v>132</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
@@ -2273,12 +2274,12 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="75" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B17" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="174">
+      <c r="C17" s="214">
         <v>83523.360000000001</v>
       </c>
       <c r="D17" s="48"/>
@@ -2287,7 +2288,7 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="88"/>
       <c r="B18" s="89"/>
-      <c r="C18" s="173">
+      <c r="C18" s="60">
         <f>SUM(C17:C17)</f>
         <v>83523.360000000001</v>
       </c>
@@ -2297,31 +2298,31 @@
         <v>35</v>
       </c>
       <c r="B19" s="87"/>
-      <c r="C19" s="11"/>
+      <c r="C19" s="215"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="75" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B20" s="90"/>
-      <c r="C20" s="213">
+      <c r="C20" s="84">
         <v>37000</v>
       </c>
       <c r="F20" s="22"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B21" s="90"/>
-      <c r="C21" s="213">
+      <c r="C21" s="84">
         <v>36534.6</v>
       </c>
       <c r="F21" s="22"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B22" s="87"/>
       <c r="C22" s="85"/>
@@ -2405,19 +2406,19 @@
     </row>
     <row r="34" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="145" t="s">
+      <c r="A35" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="146"/>
-      <c r="C35" s="147"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="146"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="143" t="s">
+      <c r="A36" s="142" t="s">
         <v>10</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="144">
-        <v>-728212.36639999994</v>
+      <c r="C36" s="143">
+        <v>-655708.39639999974</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -2428,16 +2429,17 @@
       </c>
       <c r="C37" s="32">
         <f>'prorrateo '!F15</f>
-        <v>404745.41000000015</v>
+        <v>332241.44</v>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C38" s="92">
+        <f>-edesur!H1</f>
         <v>-301581.15999999997</v>
       </c>
       <c r="D38" s="14"/>
@@ -2560,7 +2562,7 @@
     <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
@@ -2576,16 +2578,13 @@
       <c r="A1" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="14">
-        <v>159610.60999999999</v>
-      </c>
-      <c r="H1" s="202" t="s">
-        <v>131</v>
-      </c>
-      <c r="I1" s="202"/>
-      <c r="J1" s="14">
-        <v>172630.83</v>
-      </c>
+      <c r="E1" s="207">
+        <v>157057.96000000002</v>
+      </c>
+      <c r="F1" s="207"/>
+      <c r="H1" s="172"/>
+      <c r="I1" s="172"/>
+      <c r="J1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96">
@@ -2605,14 +2604,14 @@
       <c r="L2" s="101"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="186" t="s">
+      <c r="A3" s="192" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="179" t="s">
+      <c r="B3" s="193"/>
+      <c r="C3" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="190" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -2621,19 +2620,19 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="179" t="s">
+      <c r="G3" s="188" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="175" t="s">
+      <c r="I3" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="190" t="s">
+      <c r="J3" s="196" t="s">
         <v>110</v>
       </c>
-      <c r="K3" s="179" t="s">
+      <c r="K3" s="188" t="s">
         <v>42</v>
       </c>
       <c r="L3" s="45" t="s">
@@ -2641,48 +2640,48 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="188"/>
-      <c r="B4" s="189"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="185"/>
+      <c r="A4" s="194"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="191"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="180"/>
+      <c r="G4" s="189"/>
       <c r="H4" s="37">
         <v>0.04</v>
       </c>
-      <c r="I4" s="176"/>
-      <c r="J4" s="191"/>
-      <c r="K4" s="180"/>
+      <c r="I4" s="199"/>
+      <c r="J4" s="197"/>
+      <c r="K4" s="189"/>
       <c r="L4" s="38" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="177">
+    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="186">
         <v>1</v>
       </c>
-      <c r="B5" s="178"/>
+      <c r="B5" s="187"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="58"/>
-      <c r="E5" s="148">
-        <v>55854.866580000002</v>
-      </c>
-      <c r="F5" s="149">
+      <c r="E5" s="147">
+        <v>45849.318719999996</v>
+      </c>
+      <c r="F5" s="148">
         <f>E5</f>
-        <v>55854.866580000002</v>
-      </c>
-      <c r="G5" s="150">
+        <v>45849.318719999996</v>
+      </c>
+      <c r="G5" s="149">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="150">
+      <c r="H5" s="149">
         <f>IF(G5&gt;0,G5*4%,0)</f>
         <v>0</v>
       </c>
@@ -2691,40 +2690,40 @@
       </c>
       <c r="J5" s="95">
         <f>E$1*I5/100</f>
-        <v>22026.264180000002</v>
-      </c>
-      <c r="K5" s="141">
-        <f>J$1*I5/100</f>
-        <v>23823.054539999997</v>
+        <v>21673.998480000002</v>
+      </c>
+      <c r="K5" s="140">
+        <f>edesur!H5</f>
+        <v>25000</v>
       </c>
       <c r="L5" s="102">
         <f>G5+H5+J5+K5</f>
-        <v>45849.318719999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="177">
+        <v>46673.998480000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="186">
         <v>2</v>
       </c>
-      <c r="B6" s="178"/>
+      <c r="B6" s="187"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D6" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="148">
-        <v>48002.805626000001</v>
-      </c>
-      <c r="F6" s="149">
+      <c r="E6" s="147">
+        <v>39403.834783999991</v>
+      </c>
+      <c r="F6" s="148">
         <f t="shared" ref="F6:F14" si="0">E6</f>
-        <v>48002.805626000001</v>
-      </c>
-      <c r="G6" s="150">
+        <v>39403.834783999991</v>
+      </c>
+      <c r="G6" s="149">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="150">
+      <c r="H6" s="149">
         <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
@@ -2733,40 +2732,40 @@
       </c>
       <c r="J6" s="95">
         <f t="shared" ref="J6:J14" si="3">E$1*I6/100</f>
-        <v>18929.818345999996</v>
-      </c>
-      <c r="K6" s="141">
-        <f t="shared" ref="K6:K14" si="4">J$1*I6/100</f>
-        <v>20474.016437999999</v>
+        <v>18627.074056000001</v>
+      </c>
+      <c r="K6" s="140">
+        <f>edesur!H6</f>
+        <v>74547.000664303734</v>
       </c>
       <c r="L6" s="102">
-        <f t="shared" ref="L6:L14" si="5">G6+H6+J6+K6</f>
-        <v>39403.834783999991</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="177">
+        <f t="shared" ref="L6:L14" si="4">G6+H6+J6+K6</f>
+        <v>93174.074720303732</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="186">
         <v>3</v>
       </c>
-      <c r="B7" s="178"/>
+      <c r="B7" s="187"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="213" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="148">
-        <v>50431.278086000006</v>
-      </c>
-      <c r="F7" s="149">
+      <c r="E7" s="147">
+        <v>41397.283423999994</v>
+      </c>
+      <c r="F7" s="148">
         <f t="shared" si="0"/>
-        <v>50431.278086000006</v>
-      </c>
-      <c r="G7" s="150">
+        <v>41397.283423999994</v>
+      </c>
+      <c r="G7" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="150">
+      <c r="H7" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2775,40 +2774,40 @@
       </c>
       <c r="J7" s="95">
         <f t="shared" si="3"/>
-        <v>19887.482005999998</v>
-      </c>
-      <c r="K7" s="141">
+        <v>19569.421816000005</v>
+      </c>
+      <c r="K7" s="140">
+        <f>edesur!H7</f>
+        <v>25000</v>
+      </c>
+      <c r="L7" s="102">
         <f t="shared" si="4"/>
-        <v>21509.801417999999</v>
-      </c>
-      <c r="L7" s="102">
-        <f t="shared" si="5"/>
-        <v>41397.283423999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="177">
+        <v>44569.421816000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="186">
         <v>4</v>
       </c>
-      <c r="B8" s="178"/>
+      <c r="B8" s="187"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="148">
-        <v>59699.947975000003</v>
-      </c>
-      <c r="F8" s="149">
+      <c r="E8" s="147">
+        <v>49005.612399999998</v>
+      </c>
+      <c r="F8" s="148">
         <f t="shared" si="0"/>
-        <v>59699.947975000003</v>
-      </c>
-      <c r="G8" s="150">
+        <v>49005.612399999998</v>
+      </c>
+      <c r="G8" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="150">
+      <c r="H8" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2817,40 +2816,40 @@
       </c>
       <c r="J8" s="95">
         <f t="shared" si="3"/>
-        <v>23542.564974999998</v>
-      </c>
-      <c r="K8" s="141">
+        <v>23166.0491</v>
+      </c>
+      <c r="K8" s="140">
+        <f>edesur!H8</f>
+        <v>81393.15378653571</v>
+      </c>
+      <c r="L8" s="102">
         <f t="shared" si="4"/>
-        <v>25463.047424999997</v>
-      </c>
-      <c r="L8" s="102">
-        <f t="shared" si="5"/>
-        <v>49005.612399999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="177">
+        <v>104559.20288653571</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="186">
         <v>5</v>
       </c>
-      <c r="B9" s="178"/>
+      <c r="B9" s="187"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="148">
-        <v>50228.905381000004</v>
-      </c>
-      <c r="F9" s="149">
+      <c r="E9" s="147">
+        <v>41231.162704000002</v>
+      </c>
+      <c r="F9" s="148">
         <f t="shared" si="0"/>
-        <v>50228.905381000004</v>
-      </c>
-      <c r="G9" s="150">
+        <v>41231.162704000002</v>
+      </c>
+      <c r="G9" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H9" s="150">
+      <c r="H9" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2859,38 +2858,38 @@
       </c>
       <c r="J9" s="95">
         <f t="shared" si="3"/>
-        <v>19807.676700999997</v>
-      </c>
-      <c r="K9" s="141">
-        <f t="shared" si="4"/>
-        <v>21423.486003000002</v>
+        <v>19490.892836000003</v>
+      </c>
+      <c r="K9" s="140">
+        <f>edesur!H9</f>
+        <v>45641.020814879841</v>
       </c>
       <c r="L9" s="102">
         <f>G9+H9+J9+K9</f>
-        <v>41231.162704000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177">
+        <v>65131.91365087984</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="186">
         <v>6</v>
       </c>
-      <c r="B10" s="178"/>
+      <c r="B10" s="187"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="72"/>
-      <c r="E10" s="148">
-        <v>50512.227168000012</v>
-      </c>
-      <c r="F10" s="149">
+      <c r="E10" s="147">
+        <v>41463.731711999993</v>
+      </c>
+      <c r="F10" s="148">
         <f t="shared" si="0"/>
-        <v>50512.227168000012</v>
-      </c>
-      <c r="G10" s="150">
+        <v>41463.731711999993</v>
+      </c>
+      <c r="G10" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="150">
+      <c r="H10" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2899,38 +2898,38 @@
       </c>
       <c r="J10" s="95">
         <f t="shared" si="3"/>
-        <v>19919.404127999998</v>
-      </c>
-      <c r="K10" s="141">
+        <v>19600.833408000002</v>
+      </c>
+      <c r="K10" s="140">
+        <f>edesur!H10</f>
+        <v>25000</v>
+      </c>
+      <c r="L10" s="102">
         <f t="shared" si="4"/>
-        <v>21544.327583999999</v>
-      </c>
-      <c r="L10" s="102">
-        <f t="shared" si="5"/>
-        <v>41463.731711999993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177">
+        <v>44600.833408000006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="186">
         <v>7</v>
       </c>
-      <c r="B11" s="178"/>
+      <c r="B11" s="187"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="72"/>
-      <c r="E11" s="148">
-        <v>73906.511866000015</v>
-      </c>
-      <c r="F11" s="149">
+      <c r="E11" s="147">
+        <v>60667.286943999999</v>
+      </c>
+      <c r="F11" s="148">
         <f t="shared" si="0"/>
-        <v>73906.511866000015</v>
-      </c>
-      <c r="G11" s="150">
+        <v>60667.286943999999</v>
+      </c>
+      <c r="G11" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="150">
+      <c r="H11" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2939,39 +2938,39 @@
       </c>
       <c r="J11" s="95">
         <f t="shared" si="3"/>
-        <v>29144.897385999997</v>
-      </c>
-      <c r="K11" s="141">
+        <v>28678.783496000007</v>
+      </c>
+      <c r="K11" s="140">
+        <f>edesur!H11</f>
+        <v>25000</v>
+      </c>
+      <c r="L11" s="102">
         <f t="shared" si="4"/>
-        <v>31522.389558000003</v>
-      </c>
-      <c r="L11" s="102">
-        <f t="shared" si="5"/>
-        <v>60667.286943999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="177" t="s">
+        <v>53678.783496000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="186" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="178"/>
+      <c r="B12" s="187"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="72"/>
-      <c r="E12" s="148">
-        <v>5423.5884940000014</v>
-      </c>
-      <c r="F12" s="149">
+      <c r="E12" s="147">
+        <v>4452.035296</v>
+      </c>
+      <c r="F12" s="148">
         <f t="shared" si="0"/>
-        <v>5423.5884940000014</v>
-      </c>
-      <c r="G12" s="150">
+        <v>4452.035296</v>
+      </c>
+      <c r="G12" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="150">
+      <c r="H12" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2980,39 +2979,36 @@
       </c>
       <c r="J12" s="95">
         <f t="shared" si="3"/>
-        <v>2138.7821739999999</v>
-      </c>
-      <c r="K12" s="141">
+        <v>2104.5766640000006</v>
+      </c>
+      <c r="K12" s="140"/>
+      <c r="L12" s="102">
         <f t="shared" si="4"/>
-        <v>2313.2531220000001</v>
-      </c>
-      <c r="L12" s="102">
-        <f t="shared" si="5"/>
-        <v>4452.035296</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="177" t="s">
+        <v>2104.5766640000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="186" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="178"/>
+      <c r="B13" s="187"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="72"/>
-      <c r="E13" s="148">
-        <v>5342.6394120000004</v>
-      </c>
-      <c r="F13" s="149">
+      <c r="E13" s="147">
+        <v>4385.5870080000004</v>
+      </c>
+      <c r="F13" s="148">
         <f t="shared" si="0"/>
-        <v>5342.6394120000004</v>
-      </c>
-      <c r="G13" s="150">
+        <v>4385.5870080000004</v>
+      </c>
+      <c r="G13" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="150">
+      <c r="H13" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3021,39 +3017,36 @@
       </c>
       <c r="J13" s="95">
         <f t="shared" si="3"/>
-        <v>2106.860052</v>
-      </c>
-      <c r="K13" s="141">
+        <v>2073.1650720000007</v>
+      </c>
+      <c r="K13" s="140"/>
+      <c r="L13" s="102">
         <f t="shared" si="4"/>
-        <v>2278.726956</v>
-      </c>
-      <c r="L13" s="102">
-        <f t="shared" si="5"/>
-        <v>4385.5870080000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="177" t="s">
+        <v>2073.1650720000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="186" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="178"/>
+      <c r="B14" s="187"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="72"/>
-      <c r="E14" s="148">
-        <v>5342.6394120000004</v>
-      </c>
-      <c r="F14" s="149">
+      <c r="E14" s="147">
+        <v>4385.5870080000004</v>
+      </c>
+      <c r="F14" s="148">
         <f t="shared" si="0"/>
-        <v>5342.6394120000004</v>
-      </c>
-      <c r="G14" s="150">
+        <v>4385.5870080000004</v>
+      </c>
+      <c r="G14" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H14" s="150">
+      <c r="H14" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -3062,15 +3055,12 @@
       </c>
       <c r="J14" s="95">
         <f t="shared" si="3"/>
-        <v>2106.860052</v>
-      </c>
-      <c r="K14" s="141">
+        <v>2073.1650720000007</v>
+      </c>
+      <c r="K14" s="140"/>
+      <c r="L14" s="102">
         <f t="shared" si="4"/>
-        <v>2278.726956</v>
-      </c>
-      <c r="L14" s="102">
-        <f t="shared" si="5"/>
-        <v>4385.5870080000004</v>
+        <v>2073.1650720000007</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3082,11 +3072,11 @@
       <c r="D15" s="105"/>
       <c r="E15" s="42">
         <f>SUM(E5:E14)</f>
-        <v>404745.41000000015</v>
+        <v>332241.44</v>
       </c>
       <c r="F15" s="106">
         <f>SUM(F5:F14)</f>
-        <v>404745.41000000015</v>
+        <v>332241.44</v>
       </c>
       <c r="G15" s="106"/>
       <c r="H15" s="107">
@@ -3094,20 +3084,20 @@
         <v>0</v>
       </c>
       <c r="I15" s="108">
-        <f t="shared" ref="I15" si="6">SUM(I5:I14)</f>
+        <f t="shared" ref="I15" si="5">SUM(I5:I14)</f>
         <v>100</v>
       </c>
       <c r="J15" s="39">
         <f>SUM(J5:J14)</f>
-        <v>159610.60999999999</v>
+        <v>157057.96000000002</v>
       </c>
       <c r="K15" s="42">
         <f>SUM(K5:K11)</f>
-        <v>165760.12296599997</v>
+        <v>301581.1752657193</v>
       </c>
       <c r="L15" s="42">
         <f>SUM(L5:L14)</f>
-        <v>332241.44</v>
+        <v>458639.13526571926</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
@@ -3253,7 +3243,7 @@
         <v>0.122</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" ref="J23:J29" si="7">0*I23</f>
+        <f t="shared" ref="J23:J29" si="6">0*I23</f>
         <v>0</v>
       </c>
       <c r="K23" s="41"/>
@@ -3288,7 +3278,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J24" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K24" s="41"/>
@@ -3319,7 +3309,7 @@
         <v>0.11700000000000001</v>
       </c>
       <c r="J25" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K25" s="41"/>
@@ -3350,7 +3340,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K26" s="41"/>
@@ -3381,7 +3371,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K27" s="41"/>
@@ -3415,7 +3405,7 @@
         <v>0.127</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K28" s="41"/>
@@ -3449,7 +3439,7 @@
         <v>0.127</v>
       </c>
       <c r="J29" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K29" s="41"/>
@@ -3478,11 +3468,11 @@
         <v>0</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" ref="I30:J30" si="8">SUM(I22:I29)</f>
+        <f t="shared" ref="I30:J30" si="7">SUM(I22:I29)</f>
         <v>1</v>
       </c>
       <c r="J30" s="39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K30" s="42"/>
@@ -3499,345 +3489,345 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="192" t="s">
+      <c r="E32" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="194"/>
-      <c r="L32" s="151"/>
-      <c r="M32" s="152"/>
+      <c r="F32" s="178"/>
+      <c r="G32" s="178"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="151"/>
       <c r="N32"/>
     </row>
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="195" t="s">
+      <c r="E33" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="193"/>
-      <c r="G33" s="193"/>
-      <c r="H33" s="193"/>
-      <c r="I33" s="193"/>
-      <c r="J33" s="193"/>
-      <c r="K33" s="194"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="154"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="178"/>
+      <c r="H33" s="178"/>
+      <c r="I33" s="178"/>
+      <c r="J33" s="178"/>
+      <c r="K33" s="176"/>
+      <c r="L33" s="152"/>
+      <c r="M33" s="153"/>
       <c r="N33"/>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156">
+      <c r="E34" s="150"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="155"/>
+      <c r="J34" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="154"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="154"/>
+      <c r="K34" s="153"/>
+      <c r="L34" s="152"/>
+      <c r="M34" s="153"/>
       <c r="N34"/>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="153" t="s">
+      <c r="E35" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F35" s="156"/>
-      <c r="G35" s="156"/>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="156"/>
-      <c r="K35" s="154"/>
-      <c r="L35" s="153"/>
-      <c r="M35" s="154"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="155"/>
+      <c r="H35" s="155"/>
+      <c r="I35" s="155"/>
+      <c r="J35" s="155"/>
+      <c r="K35" s="153"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="153"/>
       <c r="N35"/>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="157"/>
-      <c r="F36" s="158"/>
-      <c r="G36" s="158"/>
-      <c r="H36" s="158"/>
-      <c r="I36" s="158"/>
-      <c r="J36" s="158"/>
-      <c r="K36" s="159"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="154"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="157"/>
+      <c r="H36" s="157"/>
+      <c r="I36" s="157"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="158"/>
+      <c r="L36" s="152"/>
+      <c r="M36" s="153"/>
       <c r="N36"/>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="196" t="s">
+      <c r="E37" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="197"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="197"/>
-      <c r="I37" s="197"/>
-      <c r="J37" s="197"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="153"/>
-      <c r="M37" s="154"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="181"/>
+      <c r="H37" s="181"/>
+      <c r="I37" s="181"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="182"/>
+      <c r="L37" s="152"/>
+      <c r="M37" s="153"/>
       <c r="N37"/>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="153"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="154"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="154"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="155"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="155"/>
+      <c r="J38" s="155"/>
+      <c r="K38" s="153"/>
+      <c r="L38" s="152"/>
+      <c r="M38" s="153"/>
       <c r="N38"/>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="153" t="s">
+      <c r="E39" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="156"/>
-      <c r="G39" s="156" t="str">
+      <c r="F39" s="155"/>
+      <c r="G39" s="155" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="156"/>
-      <c r="I39" s="156" t="s">
+      <c r="H39" s="155"/>
+      <c r="I39" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J39" s="160">
+      <c r="J39" s="159">
         <v>45674</v>
       </c>
-      <c r="K39" s="154"/>
-      <c r="L39" s="181" t="s">
+      <c r="K39" s="153"/>
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="182"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="153" t="s">
+      <c r="E40" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="161">
+      <c r="F40" s="160">
         <v>3</v>
       </c>
-      <c r="G40" s="156"/>
-      <c r="H40" s="156"/>
-      <c r="I40" s="156"/>
-      <c r="J40" s="156"/>
-      <c r="K40" s="154"/>
-      <c r="L40" s="153"/>
-      <c r="M40" s="154"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="152"/>
+      <c r="M40" s="153"/>
       <c r="N40"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="153"/>
-      <c r="F41" s="156"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="156"/>
-      <c r="J41" s="156"/>
-      <c r="K41" s="154"/>
-      <c r="L41" s="183"/>
-      <c r="M41" s="182"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
+      <c r="K41" s="153"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="153" t="s">
+      <c r="E42" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="162">
+      <c r="F42" s="155"/>
+      <c r="G42" s="155"/>
+      <c r="H42" s="155"/>
+      <c r="I42" s="155"/>
+      <c r="J42" s="161">
         <f>J7</f>
-        <v>19887.482005999998</v>
-      </c>
-      <c r="K42" s="154"/>
-      <c r="L42" s="153"/>
-      <c r="M42" s="154"/>
+        <v>19569.421816000005</v>
+      </c>
+      <c r="K42" s="153"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="153"/>
       <c r="N42"/>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="163" t="s">
+      <c r="E43" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="156"/>
-      <c r="I43" s="156"/>
-      <c r="J43" s="162">
+      <c r="F43" s="155"/>
+      <c r="G43" s="155"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="161">
         <f>K7</f>
-        <v>21509.801417999999</v>
-      </c>
-      <c r="K43" s="154"/>
-      <c r="L43" s="153"/>
-      <c r="M43" s="154"/>
+        <v>25000</v>
+      </c>
+      <c r="K43" s="153"/>
+      <c r="L43" s="152"/>
+      <c r="M43" s="153"/>
       <c r="N43"/>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="163" t="s">
+      <c r="E44" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="156"/>
-      <c r="G44" s="156"/>
-      <c r="H44" s="156"/>
-      <c r="I44" s="156"/>
-      <c r="J44" s="162">
+      <c r="F44" s="155"/>
+      <c r="G44" s="155"/>
+      <c r="H44" s="155"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="161">
         <f>G7+H7</f>
         <v>0</v>
       </c>
-      <c r="K44" s="154"/>
-      <c r="L44" s="153"/>
-      <c r="M44" s="154"/>
+      <c r="K44" s="153"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="153"/>
       <c r="N44"/>
     </row>
     <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="163"/>
-      <c r="F45" s="156"/>
-      <c r="G45" s="156"/>
-      <c r="H45" s="156"/>
-      <c r="I45" s="156"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="154"/>
-      <c r="L45" s="153"/>
-      <c r="M45" s="154"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
+      <c r="H45" s="155"/>
+      <c r="I45" s="155"/>
+      <c r="J45" s="161"/>
+      <c r="K45" s="153"/>
+      <c r="L45" s="152"/>
+      <c r="M45" s="153"/>
       <c r="N45"/>
     </row>
     <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="163"/>
-      <c r="F46" s="156"/>
-      <c r="G46" s="156"/>
-      <c r="H46" s="156"/>
-      <c r="I46" s="156"/>
-      <c r="J46" s="162"/>
-      <c r="K46" s="154"/>
-      <c r="L46" s="153"/>
-      <c r="M46" s="154"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="155"/>
+      <c r="G46" s="155"/>
+      <c r="H46" s="155"/>
+      <c r="I46" s="155"/>
+      <c r="J46" s="161"/>
+      <c r="K46" s="153"/>
+      <c r="L46" s="152"/>
+      <c r="M46" s="153"/>
       <c r="N46"/>
     </row>
     <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="156"/>
-      <c r="G47" s="156"/>
-      <c r="H47" s="156"/>
-      <c r="I47" s="156"/>
-      <c r="J47" s="162"/>
-      <c r="K47" s="154"/>
-      <c r="L47" s="153"/>
-      <c r="M47" s="154"/>
+      <c r="F47" s="155"/>
+      <c r="G47" s="155"/>
+      <c r="H47" s="155"/>
+      <c r="I47" s="155"/>
+      <c r="J47" s="161"/>
+      <c r="K47" s="153"/>
+      <c r="L47" s="152"/>
+      <c r="M47" s="153"/>
       <c r="N47"/>
     </row>
     <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="163"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="156"/>
-      <c r="H48" s="156"/>
-      <c r="I48" s="156"/>
-      <c r="J48" s="162"/>
-      <c r="K48" s="154"/>
-      <c r="L48" s="153"/>
-      <c r="M48" s="154"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="155"/>
+      <c r="G48" s="155"/>
+      <c r="H48" s="155"/>
+      <c r="I48" s="155"/>
+      <c r="J48" s="161"/>
+      <c r="K48" s="153"/>
+      <c r="L48" s="152"/>
+      <c r="M48" s="153"/>
       <c r="N48"/>
     </row>
     <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="153"/>
-      <c r="F49" s="156"/>
-      <c r="G49" s="156"/>
-      <c r="H49" s="156"/>
-      <c r="I49" s="156"/>
-      <c r="J49" s="156"/>
-      <c r="K49" s="154"/>
-      <c r="L49" s="153"/>
-      <c r="M49" s="154"/>
+      <c r="E49" s="152"/>
+      <c r="F49" s="155"/>
+      <c r="G49" s="155"/>
+      <c r="H49" s="155"/>
+      <c r="I49" s="155"/>
+      <c r="J49" s="155"/>
+      <c r="K49" s="153"/>
+      <c r="L49" s="152"/>
+      <c r="M49" s="153"/>
       <c r="N49"/>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="153" t="s">
+      <c r="E50" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="156"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="156"/>
-      <c r="I50" s="156"/>
-      <c r="J50" s="156">
+      <c r="F50" s="155"/>
+      <c r="G50" s="155"/>
+      <c r="H50" s="155"/>
+      <c r="I50" s="155"/>
+      <c r="J50" s="155">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="154"/>
-      <c r="L50" s="153"/>
-      <c r="M50" s="154"/>
+      <c r="K50" s="153"/>
+      <c r="L50" s="152"/>
+      <c r="M50" s="153"/>
       <c r="N50"/>
     </row>
     <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="153"/>
-      <c r="F51" s="156"/>
-      <c r="G51" s="156"/>
-      <c r="H51" s="156"/>
-      <c r="I51" s="156"/>
-      <c r="J51" s="156"/>
-      <c r="K51" s="154"/>
-      <c r="L51" s="164"/>
-      <c r="M51" s="165"/>
+      <c r="E51" s="152"/>
+      <c r="F51" s="155"/>
+      <c r="G51" s="155"/>
+      <c r="H51" s="155"/>
+      <c r="I51" s="155"/>
+      <c r="J51" s="155"/>
+      <c r="K51" s="153"/>
+      <c r="L51" s="163"/>
+      <c r="M51" s="164"/>
       <c r="N51"/>
     </row>
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="199" t="s">
+      <c r="E52" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="200"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="200"/>
-      <c r="I52" s="200"/>
-      <c r="J52" s="201">
+      <c r="F52" s="174"/>
+      <c r="G52" s="174"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="175">
         <f>SUM(J42:J51)</f>
-        <v>41473.083423999997</v>
-      </c>
-      <c r="K52" s="194"/>
-      <c r="L52" s="166"/>
-      <c r="M52" s="167"/>
+        <v>44645.221816000005</v>
+      </c>
+      <c r="K52" s="176"/>
+      <c r="L52" s="165"/>
+      <c r="M52" s="166"/>
       <c r="N52"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.25">
@@ -3847,836 +3837,867 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="192" t="s">
+      <c r="E56" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="194"/>
-      <c r="L56" s="151"/>
-      <c r="M56" s="152"/>
+      <c r="F56" s="178"/>
+      <c r="G56" s="178"/>
+      <c r="H56" s="178"/>
+      <c r="I56" s="178"/>
+      <c r="J56" s="178"/>
+      <c r="K56" s="176"/>
+      <c r="L56" s="150"/>
+      <c r="M56" s="151"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="195" t="s">
+      <c r="E57" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="193"/>
-      <c r="G57" s="193"/>
-      <c r="H57" s="193"/>
-      <c r="I57" s="193"/>
-      <c r="J57" s="193"/>
-      <c r="K57" s="194"/>
-      <c r="L57" s="153"/>
-      <c r="M57" s="154"/>
+      <c r="F57" s="178"/>
+      <c r="G57" s="178"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="178"/>
+      <c r="J57" s="178"/>
+      <c r="K57" s="176"/>
+      <c r="L57" s="152"/>
+      <c r="M57" s="153"/>
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E58" s="151"/>
-      <c r="F58" s="155"/>
-      <c r="G58" s="155"/>
-      <c r="H58" s="155"/>
-      <c r="I58" s="156"/>
-      <c r="J58" s="156">
+      <c r="E58" s="150"/>
+      <c r="F58" s="154"/>
+      <c r="G58" s="154"/>
+      <c r="H58" s="154"/>
+      <c r="I58" s="155"/>
+      <c r="J58" s="155">
         <f>J34</f>
         <v>0</v>
       </c>
-      <c r="K58" s="154"/>
-      <c r="L58" s="153"/>
-      <c r="M58" s="154"/>
+      <c r="K58" s="153"/>
+      <c r="L58" s="152"/>
+      <c r="M58" s="153"/>
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E59" s="153" t="s">
+      <c r="E59" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F59" s="156"/>
-      <c r="G59" s="156"/>
-      <c r="H59" s="156"/>
-      <c r="I59" s="156"/>
-      <c r="J59" s="156"/>
-      <c r="K59" s="154"/>
-      <c r="L59" s="153"/>
-      <c r="M59" s="154"/>
+      <c r="F59" s="155"/>
+      <c r="G59" s="155"/>
+      <c r="H59" s="155"/>
+      <c r="I59" s="155"/>
+      <c r="J59" s="155"/>
+      <c r="K59" s="153"/>
+      <c r="L59" s="152"/>
+      <c r="M59" s="153"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E60" s="157"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="158"/>
-      <c r="H60" s="158"/>
-      <c r="I60" s="158"/>
-      <c r="J60" s="158"/>
-      <c r="K60" s="159"/>
-      <c r="L60" s="153"/>
-      <c r="M60" s="154"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="157"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="157"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="158"/>
+      <c r="L60" s="152"/>
+      <c r="M60" s="153"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="196" t="s">
+      <c r="E61" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="197"/>
-      <c r="G61" s="197"/>
-      <c r="H61" s="197"/>
-      <c r="I61" s="197"/>
-      <c r="J61" s="197"/>
-      <c r="K61" s="198"/>
-      <c r="L61" s="153"/>
-      <c r="M61" s="154"/>
+      <c r="F61" s="181"/>
+      <c r="G61" s="181"/>
+      <c r="H61" s="181"/>
+      <c r="I61" s="181"/>
+      <c r="J61" s="181"/>
+      <c r="K61" s="182"/>
+      <c r="L61" s="152"/>
+      <c r="M61" s="153"/>
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E62" s="153"/>
-      <c r="F62" s="156"/>
-      <c r="G62" s="156"/>
-      <c r="H62" s="156"/>
-      <c r="I62" s="156"/>
-      <c r="J62" s="156"/>
-      <c r="K62" s="154"/>
-      <c r="L62" s="153"/>
-      <c r="M62" s="154"/>
+      <c r="E62" s="152"/>
+      <c r="F62" s="155"/>
+      <c r="G62" s="155"/>
+      <c r="H62" s="155"/>
+      <c r="I62" s="155"/>
+      <c r="J62" s="155"/>
+      <c r="K62" s="153"/>
+      <c r="L62" s="152"/>
+      <c r="M62" s="153"/>
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E63" s="153" t="s">
+      <c r="E63" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F63" s="156"/>
-      <c r="G63" s="161" t="str">
+      <c r="F63" s="155"/>
+      <c r="G63" s="160" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="156"/>
-      <c r="I63" s="156" t="s">
+      <c r="H63" s="155"/>
+      <c r="I63" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J63" s="160">
+      <c r="J63" s="159">
         <v>45674</v>
       </c>
-      <c r="K63" s="154"/>
-      <c r="L63" s="181" t="s">
+      <c r="K63" s="153"/>
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="182"/>
+      <c r="M63" s="184"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E64" s="153" t="s">
+      <c r="E64" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F64" s="161">
+      <c r="F64" s="160">
         <v>4</v>
       </c>
-      <c r="G64" s="156"/>
-      <c r="H64" s="156"/>
-      <c r="I64" s="156"/>
-      <c r="J64" s="156"/>
-      <c r="K64" s="154"/>
-      <c r="L64" s="153"/>
-      <c r="M64" s="154"/>
+      <c r="G64" s="155"/>
+      <c r="H64" s="155"/>
+      <c r="I64" s="155"/>
+      <c r="J64" s="155"/>
+      <c r="K64" s="153"/>
+      <c r="L64" s="152"/>
+      <c r="M64" s="153"/>
     </row>
     <row r="65" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E65" s="153"/>
-      <c r="F65" s="156"/>
-      <c r="G65" s="156"/>
-      <c r="H65" s="156"/>
-      <c r="I65" s="156"/>
-      <c r="J65" s="156"/>
-      <c r="K65" s="154"/>
-      <c r="L65" s="183"/>
-      <c r="M65" s="182"/>
+      <c r="E65" s="152"/>
+      <c r="F65" s="155"/>
+      <c r="G65" s="155"/>
+      <c r="H65" s="155"/>
+      <c r="I65" s="155"/>
+      <c r="J65" s="155"/>
+      <c r="K65" s="153"/>
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E66" s="153" t="s">
+      <c r="E66" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="156"/>
-      <c r="G66" s="156"/>
-      <c r="H66" s="156"/>
-      <c r="I66" s="156"/>
-      <c r="J66" s="162">
+      <c r="F66" s="155"/>
+      <c r="G66" s="155"/>
+      <c r="H66" s="155"/>
+      <c r="I66" s="155"/>
+      <c r="J66" s="161">
         <f>J8</f>
-        <v>23542.564974999998</v>
-      </c>
-      <c r="K66" s="154"/>
-      <c r="L66" s="153"/>
-      <c r="M66" s="154"/>
+        <v>23166.0491</v>
+      </c>
+      <c r="K66" s="153"/>
+      <c r="L66" s="152"/>
+      <c r="M66" s="153"/>
     </row>
     <row r="67" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E67" s="163" t="s">
+      <c r="E67" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F67" s="156"/>
-      <c r="G67" s="156"/>
-      <c r="H67" s="156"/>
-      <c r="I67" s="156"/>
-      <c r="J67" s="162">
+      <c r="F67" s="155"/>
+      <c r="G67" s="155"/>
+      <c r="H67" s="155"/>
+      <c r="I67" s="155"/>
+      <c r="J67" s="161">
         <f>K8</f>
-        <v>25463.047424999997</v>
-      </c>
-      <c r="K67" s="154"/>
-      <c r="L67" s="153"/>
-      <c r="M67" s="154"/>
+        <v>81393.15378653571</v>
+      </c>
+      <c r="K67" s="153"/>
+      <c r="L67" s="152"/>
+      <c r="M67" s="153"/>
     </row>
     <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="163" t="s">
+      <c r="E68" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="F68" s="156"/>
-      <c r="G68" s="156"/>
-      <c r="H68" s="156"/>
-      <c r="I68" s="156"/>
-      <c r="J68" s="162">
+      <c r="F68" s="155"/>
+      <c r="G68" s="155"/>
+      <c r="H68" s="155"/>
+      <c r="I68" s="155"/>
+      <c r="J68" s="161">
         <f>G29+H29</f>
         <v>0</v>
       </c>
-      <c r="K68" s="154"/>
-      <c r="L68" s="153"/>
-      <c r="M68" s="154"/>
+      <c r="K68" s="153"/>
+      <c r="L68" s="152"/>
+      <c r="M68" s="153"/>
     </row>
     <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E69" s="163"/>
-      <c r="F69" s="156"/>
-      <c r="G69" s="156"/>
-      <c r="H69" s="156"/>
-      <c r="I69" s="156"/>
-      <c r="J69" s="162"/>
-      <c r="K69" s="154"/>
-      <c r="L69" s="153"/>
-      <c r="M69" s="154"/>
+      <c r="E69" s="162"/>
+      <c r="F69" s="155"/>
+      <c r="G69" s="155"/>
+      <c r="H69" s="155"/>
+      <c r="I69" s="155"/>
+      <c r="J69" s="161"/>
+      <c r="K69" s="153"/>
+      <c r="L69" s="152"/>
+      <c r="M69" s="153"/>
     </row>
     <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E70" s="163"/>
-      <c r="F70" s="156"/>
-      <c r="G70" s="156"/>
-      <c r="H70" s="156"/>
-      <c r="I70" s="156"/>
-      <c r="J70" s="162"/>
-      <c r="K70" s="154"/>
-      <c r="L70" s="153"/>
-      <c r="M70" s="154"/>
+      <c r="E70" s="162"/>
+      <c r="F70" s="155"/>
+      <c r="G70" s="155"/>
+      <c r="H70" s="155"/>
+      <c r="I70" s="155"/>
+      <c r="J70" s="161"/>
+      <c r="K70" s="153"/>
+      <c r="L70" s="152"/>
+      <c r="M70" s="153"/>
     </row>
     <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="F71" s="156"/>
-      <c r="G71" s="156"/>
-      <c r="H71" s="156"/>
-      <c r="I71" s="156"/>
-      <c r="J71" s="162"/>
-      <c r="K71" s="154"/>
-      <c r="L71" s="153"/>
-      <c r="M71" s="154"/>
+      <c r="F71" s="155"/>
+      <c r="G71" s="155"/>
+      <c r="H71" s="155"/>
+      <c r="I71" s="155"/>
+      <c r="J71" s="161"/>
+      <c r="K71" s="153"/>
+      <c r="L71" s="152"/>
+      <c r="M71" s="153"/>
     </row>
     <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E72" s="163"/>
-      <c r="F72" s="156"/>
-      <c r="G72" s="156"/>
-      <c r="H72" s="156"/>
-      <c r="I72" s="156"/>
-      <c r="J72" s="162"/>
-      <c r="K72" s="154"/>
-      <c r="L72" s="153"/>
-      <c r="M72" s="154"/>
+      <c r="E72" s="162"/>
+      <c r="F72" s="155"/>
+      <c r="G72" s="155"/>
+      <c r="H72" s="155"/>
+      <c r="I72" s="155"/>
+      <c r="J72" s="161"/>
+      <c r="K72" s="153"/>
+      <c r="L72" s="152"/>
+      <c r="M72" s="153"/>
     </row>
     <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E73" s="153"/>
-      <c r="F73" s="156"/>
-      <c r="G73" s="156"/>
-      <c r="H73" s="156"/>
-      <c r="I73" s="156"/>
-      <c r="J73" s="156"/>
-      <c r="K73" s="154"/>
-      <c r="L73" s="153"/>
-      <c r="M73" s="154"/>
+      <c r="E73" s="152"/>
+      <c r="F73" s="155"/>
+      <c r="G73" s="155"/>
+      <c r="H73" s="155"/>
+      <c r="I73" s="155"/>
+      <c r="J73" s="155"/>
+      <c r="K73" s="153"/>
+      <c r="L73" s="152"/>
+      <c r="M73" s="153"/>
     </row>
     <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E74" s="153"/>
-      <c r="F74" s="156"/>
-      <c r="G74" s="156"/>
-      <c r="H74" s="156"/>
-      <c r="I74" s="156"/>
-      <c r="J74" s="156"/>
-      <c r="K74" s="154"/>
-      <c r="L74" s="153"/>
-      <c r="M74" s="154"/>
+      <c r="E74" s="152"/>
+      <c r="F74" s="155"/>
+      <c r="G74" s="155"/>
+      <c r="H74" s="155"/>
+      <c r="I74" s="155"/>
+      <c r="J74" s="155"/>
+      <c r="K74" s="153"/>
+      <c r="L74" s="152"/>
+      <c r="M74" s="153"/>
     </row>
     <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E75" s="153"/>
-      <c r="F75" s="156"/>
-      <c r="G75" s="156"/>
-      <c r="H75" s="156"/>
-      <c r="I75" s="156"/>
-      <c r="J75" s="156"/>
-      <c r="K75" s="154"/>
-      <c r="L75" s="164"/>
-      <c r="M75" s="165"/>
+      <c r="E75" s="152"/>
+      <c r="F75" s="155"/>
+      <c r="G75" s="155"/>
+      <c r="H75" s="155"/>
+      <c r="I75" s="155"/>
+      <c r="J75" s="155"/>
+      <c r="K75" s="153"/>
+      <c r="L75" s="163"/>
+      <c r="M75" s="164"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="199" t="s">
+      <c r="E76" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="200"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="200"/>
-      <c r="I76" s="200"/>
-      <c r="J76" s="201">
+      <c r="F76" s="174"/>
+      <c r="G76" s="174"/>
+      <c r="H76" s="174"/>
+      <c r="I76" s="174"/>
+      <c r="J76" s="175">
         <f>SUM(J66:J75)</f>
-        <v>49005.612399999998</v>
-      </c>
-      <c r="K76" s="194"/>
-      <c r="L76" s="166"/>
-      <c r="M76" s="167"/>
+        <v>104559.20288653571</v>
+      </c>
+      <c r="K76" s="176"/>
+      <c r="L76" s="165"/>
+      <c r="M76" s="166"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="192" t="s">
+      <c r="E83" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="193"/>
-      <c r="G83" s="193"/>
-      <c r="H83" s="193"/>
-      <c r="I83" s="193"/>
-      <c r="J83" s="193"/>
-      <c r="K83" s="194"/>
-      <c r="L83" s="151"/>
-      <c r="M83" s="152"/>
+      <c r="F83" s="178"/>
+      <c r="G83" s="178"/>
+      <c r="H83" s="178"/>
+      <c r="I83" s="178"/>
+      <c r="J83" s="178"/>
+      <c r="K83" s="176"/>
+      <c r="L83" s="150"/>
+      <c r="M83" s="151"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="195" t="s">
+      <c r="E84" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="193"/>
-      <c r="G84" s="193"/>
-      <c r="H84" s="193"/>
-      <c r="I84" s="193"/>
-      <c r="J84" s="193"/>
-      <c r="K84" s="194"/>
-      <c r="L84" s="153"/>
-      <c r="M84" s="154"/>
+      <c r="F84" s="178"/>
+      <c r="G84" s="178"/>
+      <c r="H84" s="178"/>
+      <c r="I84" s="178"/>
+      <c r="J84" s="178"/>
+      <c r="K84" s="176"/>
+      <c r="L84" s="152"/>
+      <c r="M84" s="153"/>
     </row>
     <row r="85" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E85" s="151"/>
-      <c r="F85" s="155"/>
-      <c r="G85" s="155"/>
-      <c r="H85" s="155"/>
-      <c r="I85" s="156"/>
-      <c r="J85" s="156">
+      <c r="E85" s="150"/>
+      <c r="F85" s="154"/>
+      <c r="G85" s="154"/>
+      <c r="H85" s="154"/>
+      <c r="I85" s="155"/>
+      <c r="J85" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K85" s="154"/>
-      <c r="L85" s="153"/>
-      <c r="M85" s="154"/>
+      <c r="K85" s="153"/>
+      <c r="L85" s="152"/>
+      <c r="M85" s="153"/>
     </row>
     <row r="86" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E86" s="153" t="s">
+      <c r="E86" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F86" s="156"/>
-      <c r="G86" s="156"/>
-      <c r="H86" s="156"/>
-      <c r="I86" s="156"/>
-      <c r="J86" s="156"/>
-      <c r="K86" s="154"/>
-      <c r="L86" s="153"/>
-      <c r="M86" s="154"/>
+      <c r="F86" s="155"/>
+      <c r="G86" s="155"/>
+      <c r="H86" s="155"/>
+      <c r="I86" s="155"/>
+      <c r="J86" s="155"/>
+      <c r="K86" s="153"/>
+      <c r="L86" s="152"/>
+      <c r="M86" s="153"/>
     </row>
     <row r="87" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E87" s="157"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="158"/>
-      <c r="H87" s="158"/>
-      <c r="I87" s="158"/>
-      <c r="J87" s="158"/>
-      <c r="K87" s="159"/>
-      <c r="L87" s="153"/>
-      <c r="M87" s="154"/>
+      <c r="E87" s="156"/>
+      <c r="F87" s="157"/>
+      <c r="G87" s="157"/>
+      <c r="H87" s="157"/>
+      <c r="I87" s="157"/>
+      <c r="J87" s="157"/>
+      <c r="K87" s="158"/>
+      <c r="L87" s="152"/>
+      <c r="M87" s="153"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="196" t="s">
+      <c r="E88" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="197"/>
-      <c r="G88" s="197"/>
-      <c r="H88" s="197"/>
-      <c r="I88" s="197"/>
-      <c r="J88" s="197"/>
-      <c r="K88" s="198"/>
-      <c r="L88" s="153"/>
-      <c r="M88" s="154"/>
+      <c r="F88" s="181"/>
+      <c r="G88" s="181"/>
+      <c r="H88" s="181"/>
+      <c r="I88" s="181"/>
+      <c r="J88" s="181"/>
+      <c r="K88" s="182"/>
+      <c r="L88" s="152"/>
+      <c r="M88" s="153"/>
     </row>
     <row r="89" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E89" s="153"/>
-      <c r="F89" s="156"/>
-      <c r="G89" s="156"/>
-      <c r="H89" s="156"/>
-      <c r="I89" s="156"/>
-      <c r="J89" s="156"/>
-      <c r="K89" s="154"/>
-      <c r="L89" s="153"/>
-      <c r="M89" s="154"/>
+      <c r="E89" s="152"/>
+      <c r="F89" s="155"/>
+      <c r="G89" s="155"/>
+      <c r="H89" s="155"/>
+      <c r="I89" s="155"/>
+      <c r="J89" s="155"/>
+      <c r="K89" s="153"/>
+      <c r="L89" s="152"/>
+      <c r="M89" s="153"/>
     </row>
     <row r="90" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E90" s="153" t="s">
+      <c r="E90" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F90" s="156"/>
-      <c r="G90" s="161" t="str">
+      <c r="F90" s="155"/>
+      <c r="G90" s="160" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="156"/>
-      <c r="I90" s="156" t="s">
+      <c r="H90" s="155"/>
+      <c r="I90" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="160">
+      <c r="J90" s="159">
         <v>45674</v>
       </c>
-      <c r="K90" s="154"/>
-      <c r="L90" s="181" t="s">
+      <c r="K90" s="153"/>
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="182"/>
+      <c r="M90" s="184"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E91" s="153" t="s">
+      <c r="E91" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F91" s="161">
+      <c r="F91" s="160">
         <v>6</v>
       </c>
-      <c r="G91" s="156"/>
-      <c r="H91" s="156"/>
-      <c r="I91" s="156"/>
-      <c r="J91" s="156"/>
-      <c r="K91" s="154"/>
-      <c r="L91" s="153"/>
-      <c r="M91" s="154"/>
+      <c r="G91" s="155"/>
+      <c r="H91" s="155"/>
+      <c r="I91" s="155"/>
+      <c r="J91" s="155"/>
+      <c r="K91" s="153"/>
+      <c r="L91" s="152"/>
+      <c r="M91" s="153"/>
     </row>
     <row r="92" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E92" s="153"/>
-      <c r="F92" s="156"/>
-      <c r="G92" s="156"/>
-      <c r="H92" s="156"/>
-      <c r="I92" s="156"/>
-      <c r="J92" s="156"/>
-      <c r="K92" s="154"/>
-      <c r="L92" s="183"/>
-      <c r="M92" s="182"/>
+      <c r="E92" s="152"/>
+      <c r="F92" s="155"/>
+      <c r="G92" s="155"/>
+      <c r="H92" s="155"/>
+      <c r="I92" s="155"/>
+      <c r="J92" s="155"/>
+      <c r="K92" s="153"/>
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E93" s="153" t="s">
+      <c r="E93" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F93" s="156"/>
-      <c r="G93" s="156"/>
-      <c r="H93" s="156"/>
-      <c r="I93" s="156"/>
-      <c r="J93" s="162">
+      <c r="F93" s="155"/>
+      <c r="G93" s="155"/>
+      <c r="H93" s="155"/>
+      <c r="I93" s="155"/>
+      <c r="J93" s="161">
         <f>J10</f>
-        <v>19919.404127999998</v>
-      </c>
-      <c r="K93" s="154"/>
-      <c r="L93" s="153"/>
-      <c r="M93" s="154"/>
+        <v>19600.833408000002</v>
+      </c>
+      <c r="K93" s="153"/>
+      <c r="L93" s="152"/>
+      <c r="M93" s="153"/>
     </row>
     <row r="94" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E94" s="163" t="s">
+      <c r="E94" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="156"/>
-      <c r="G94" s="156"/>
-      <c r="H94" s="156"/>
-      <c r="I94" s="156"/>
-      <c r="J94" s="162">
+      <c r="F94" s="155"/>
+      <c r="G94" s="155"/>
+      <c r="H94" s="155"/>
+      <c r="I94" s="155"/>
+      <c r="J94" s="161">
         <f>K10</f>
-        <v>21544.327583999999</v>
-      </c>
-      <c r="K94" s="154"/>
-      <c r="L94" s="153"/>
-      <c r="M94" s="154"/>
+        <v>25000</v>
+      </c>
+      <c r="K94" s="153"/>
+      <c r="L94" s="152"/>
+      <c r="M94" s="153"/>
     </row>
     <row r="95" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E95" s="163" t="s">
+      <c r="E95" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="156"/>
-      <c r="G95" s="156"/>
-      <c r="H95" s="156"/>
-      <c r="I95" s="156"/>
-      <c r="J95" s="162">
+      <c r="F95" s="155"/>
+      <c r="G95" s="155"/>
+      <c r="H95" s="155"/>
+      <c r="I95" s="155"/>
+      <c r="J95" s="161">
         <v>23.89</v>
       </c>
-      <c r="K95" s="154"/>
-      <c r="L95" s="153"/>
-      <c r="M95" s="154"/>
+      <c r="K95" s="153"/>
+      <c r="L95" s="152"/>
+      <c r="M95" s="153"/>
     </row>
     <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E96" s="163"/>
-      <c r="F96" s="156"/>
-      <c r="G96" s="156"/>
-      <c r="H96" s="156"/>
-      <c r="I96" s="156"/>
-      <c r="J96" s="162"/>
-      <c r="K96" s="154"/>
-      <c r="L96" s="153"/>
-      <c r="M96" s="154"/>
+      <c r="E96" s="162"/>
+      <c r="F96" s="155"/>
+      <c r="G96" s="155"/>
+      <c r="H96" s="155"/>
+      <c r="I96" s="155"/>
+      <c r="J96" s="161"/>
+      <c r="K96" s="153"/>
+      <c r="L96" s="152"/>
+      <c r="M96" s="153"/>
     </row>
     <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E97" s="163"/>
-      <c r="F97" s="156"/>
-      <c r="G97" s="156"/>
-      <c r="H97" s="156"/>
-      <c r="I97" s="156"/>
-      <c r="J97" s="162"/>
-      <c r="K97" s="154"/>
-      <c r="L97" s="153"/>
-      <c r="M97" s="154"/>
+      <c r="E97" s="162"/>
+      <c r="F97" s="155"/>
+      <c r="G97" s="155"/>
+      <c r="H97" s="155"/>
+      <c r="I97" s="155"/>
+      <c r="J97" s="161"/>
+      <c r="K97" s="153"/>
+      <c r="L97" s="152"/>
+      <c r="M97" s="153"/>
     </row>
     <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F98" s="156"/>
-      <c r="G98" s="156"/>
-      <c r="H98" s="156"/>
-      <c r="I98" s="156"/>
-      <c r="J98" s="162"/>
-      <c r="K98" s="154"/>
-      <c r="L98" s="153"/>
-      <c r="M98" s="154"/>
+      <c r="F98" s="155"/>
+      <c r="G98" s="155"/>
+      <c r="H98" s="155"/>
+      <c r="I98" s="155"/>
+      <c r="J98" s="161"/>
+      <c r="K98" s="153"/>
+      <c r="L98" s="152"/>
+      <c r="M98" s="153"/>
     </row>
     <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E99" s="163"/>
-      <c r="F99" s="156"/>
-      <c r="G99" s="156"/>
-      <c r="H99" s="156"/>
-      <c r="I99" s="156"/>
-      <c r="J99" s="162"/>
-      <c r="K99" s="154"/>
-      <c r="L99" s="153"/>
-      <c r="M99" s="154"/>
+      <c r="E99" s="162"/>
+      <c r="F99" s="155"/>
+      <c r="G99" s="155"/>
+      <c r="H99" s="155"/>
+      <c r="I99" s="155"/>
+      <c r="J99" s="161"/>
+      <c r="K99" s="153"/>
+      <c r="L99" s="152"/>
+      <c r="M99" s="153"/>
     </row>
     <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E100" s="153"/>
-      <c r="F100" s="156"/>
-      <c r="G100" s="156"/>
-      <c r="H100" s="156"/>
-      <c r="I100" s="156"/>
-      <c r="J100" s="156"/>
-      <c r="K100" s="154"/>
-      <c r="L100" s="153"/>
-      <c r="M100" s="154"/>
+      <c r="E100" s="152"/>
+      <c r="F100" s="155"/>
+      <c r="G100" s="155"/>
+      <c r="H100" s="155"/>
+      <c r="I100" s="155"/>
+      <c r="J100" s="155"/>
+      <c r="K100" s="153"/>
+      <c r="L100" s="152"/>
+      <c r="M100" s="153"/>
     </row>
     <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E101" s="153"/>
-      <c r="F101" s="156"/>
-      <c r="G101" s="156"/>
-      <c r="H101" s="156"/>
-      <c r="I101" s="156"/>
-      <c r="J101" s="156"/>
-      <c r="K101" s="154"/>
-      <c r="L101" s="153"/>
-      <c r="M101" s="154"/>
+      <c r="E101" s="152"/>
+      <c r="F101" s="155"/>
+      <c r="G101" s="155"/>
+      <c r="H101" s="155"/>
+      <c r="I101" s="155"/>
+      <c r="J101" s="155"/>
+      <c r="K101" s="153"/>
+      <c r="L101" s="152"/>
+      <c r="M101" s="153"/>
     </row>
     <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E102" s="153"/>
-      <c r="F102" s="156"/>
-      <c r="G102" s="156"/>
-      <c r="H102" s="156"/>
-      <c r="I102" s="156"/>
-      <c r="J102" s="156"/>
-      <c r="K102" s="154"/>
-      <c r="L102" s="164"/>
-      <c r="M102" s="165"/>
+      <c r="E102" s="152"/>
+      <c r="F102" s="155"/>
+      <c r="G102" s="155"/>
+      <c r="H102" s="155"/>
+      <c r="I102" s="155"/>
+      <c r="J102" s="155"/>
+      <c r="K102" s="153"/>
+      <c r="L102" s="163"/>
+      <c r="M102" s="164"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="199" t="s">
+      <c r="E103" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="200"/>
-      <c r="G103" s="200"/>
-      <c r="H103" s="200"/>
-      <c r="I103" s="200"/>
-      <c r="J103" s="201">
+      <c r="F103" s="174"/>
+      <c r="G103" s="174"/>
+      <c r="H103" s="174"/>
+      <c r="I103" s="174"/>
+      <c r="J103" s="175">
         <f>SUM(J93:J102)</f>
-        <v>41487.621711999993</v>
-      </c>
-      <c r="K103" s="194"/>
-      <c r="L103" s="166"/>
-      <c r="M103" s="167"/>
+        <v>44624.723408000005</v>
+      </c>
+      <c r="K103" s="176"/>
+      <c r="L103" s="165"/>
+      <c r="M103" s="166"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="192" t="s">
+      <c r="E108" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="193"/>
-      <c r="G108" s="193"/>
-      <c r="H108" s="193"/>
-      <c r="I108" s="193"/>
-      <c r="J108" s="193"/>
-      <c r="K108" s="194"/>
-      <c r="L108" s="151"/>
-      <c r="M108" s="152"/>
+      <c r="F108" s="178"/>
+      <c r="G108" s="178"/>
+      <c r="H108" s="178"/>
+      <c r="I108" s="178"/>
+      <c r="J108" s="178"/>
+      <c r="K108" s="176"/>
+      <c r="L108" s="150"/>
+      <c r="M108" s="151"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="195" t="s">
+      <c r="E109" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="193"/>
-      <c r="G109" s="193"/>
-      <c r="H109" s="193"/>
-      <c r="I109" s="193"/>
-      <c r="J109" s="193"/>
-      <c r="K109" s="194"/>
-      <c r="L109" s="153"/>
-      <c r="M109" s="154"/>
+      <c r="F109" s="178"/>
+      <c r="G109" s="178"/>
+      <c r="H109" s="178"/>
+      <c r="I109" s="178"/>
+      <c r="J109" s="178"/>
+      <c r="K109" s="176"/>
+      <c r="L109" s="152"/>
+      <c r="M109" s="153"/>
     </row>
     <row r="110" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E110" s="151"/>
-      <c r="F110" s="155"/>
-      <c r="G110" s="155"/>
-      <c r="H110" s="155"/>
-      <c r="I110" s="156"/>
-      <c r="J110" s="156">
+      <c r="E110" s="150"/>
+      <c r="F110" s="154"/>
+      <c r="G110" s="154"/>
+      <c r="H110" s="154"/>
+      <c r="I110" s="155"/>
+      <c r="J110" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K110" s="154"/>
-      <c r="L110" s="153"/>
-      <c r="M110" s="154"/>
+      <c r="K110" s="153"/>
+      <c r="L110" s="152"/>
+      <c r="M110" s="153"/>
     </row>
     <row r="111" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E111" s="153" t="s">
+      <c r="E111" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F111" s="156"/>
-      <c r="G111" s="156"/>
-      <c r="H111" s="156"/>
-      <c r="I111" s="156"/>
-      <c r="J111" s="156"/>
-      <c r="K111" s="154"/>
-      <c r="L111" s="153"/>
-      <c r="M111" s="154"/>
+      <c r="F111" s="155"/>
+      <c r="G111" s="155"/>
+      <c r="H111" s="155"/>
+      <c r="I111" s="155"/>
+      <c r="J111" s="155"/>
+      <c r="K111" s="153"/>
+      <c r="L111" s="152"/>
+      <c r="M111" s="153"/>
     </row>
     <row r="112" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E112" s="157"/>
-      <c r="F112" s="158"/>
-      <c r="G112" s="158"/>
-      <c r="H112" s="158"/>
-      <c r="I112" s="158"/>
-      <c r="J112" s="158"/>
-      <c r="K112" s="159"/>
-      <c r="L112" s="153"/>
-      <c r="M112" s="154"/>
+      <c r="E112" s="156"/>
+      <c r="F112" s="157"/>
+      <c r="G112" s="157"/>
+      <c r="H112" s="157"/>
+      <c r="I112" s="157"/>
+      <c r="J112" s="157"/>
+      <c r="K112" s="158"/>
+      <c r="L112" s="152"/>
+      <c r="M112" s="153"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="196" t="s">
+      <c r="E113" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="197"/>
-      <c r="G113" s="197"/>
-      <c r="H113" s="197"/>
-      <c r="I113" s="197"/>
-      <c r="J113" s="197"/>
-      <c r="K113" s="198"/>
-      <c r="L113" s="153"/>
-      <c r="M113" s="154"/>
+      <c r="F113" s="181"/>
+      <c r="G113" s="181"/>
+      <c r="H113" s="181"/>
+      <c r="I113" s="181"/>
+      <c r="J113" s="181"/>
+      <c r="K113" s="182"/>
+      <c r="L113" s="152"/>
+      <c r="M113" s="153"/>
     </row>
     <row r="114" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E114" s="153"/>
-      <c r="F114" s="156"/>
-      <c r="G114" s="156"/>
-      <c r="H114" s="156"/>
-      <c r="I114" s="156"/>
-      <c r="J114" s="156"/>
-      <c r="K114" s="154"/>
-      <c r="L114" s="153"/>
-      <c r="M114" s="154"/>
+      <c r="E114" s="152"/>
+      <c r="F114" s="155"/>
+      <c r="G114" s="155"/>
+      <c r="H114" s="155"/>
+      <c r="I114" s="155"/>
+      <c r="J114" s="155"/>
+      <c r="K114" s="153"/>
+      <c r="L114" s="152"/>
+      <c r="M114" s="153"/>
     </row>
     <row r="115" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E115" s="153" t="s">
+      <c r="E115" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F115" s="156"/>
-      <c r="G115" s="161" t="str">
+      <c r="F115" s="155"/>
+      <c r="G115" s="160" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="156"/>
-      <c r="I115" s="156" t="s">
+      <c r="H115" s="155"/>
+      <c r="I115" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J115" s="160">
+      <c r="J115" s="159">
         <v>45674</v>
       </c>
-      <c r="K115" s="154"/>
-      <c r="L115" s="181" t="s">
+      <c r="K115" s="153"/>
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="182"/>
+      <c r="M115" s="184"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E116" s="153" t="s">
+      <c r="E116" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F116" s="161">
+      <c r="F116" s="160">
         <v>1</v>
       </c>
-      <c r="G116" s="156"/>
-      <c r="H116" s="156"/>
-      <c r="I116" s="156"/>
-      <c r="J116" s="156"/>
-      <c r="K116" s="154"/>
-      <c r="L116" s="153"/>
-      <c r="M116" s="154"/>
+      <c r="G116" s="155"/>
+      <c r="H116" s="155"/>
+      <c r="I116" s="155"/>
+      <c r="J116" s="155"/>
+      <c r="K116" s="153"/>
+      <c r="L116" s="152"/>
+      <c r="M116" s="153"/>
     </row>
     <row r="117" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E117" s="153"/>
-      <c r="F117" s="156"/>
-      <c r="G117" s="156"/>
-      <c r="H117" s="156"/>
-      <c r="I117" s="156"/>
-      <c r="J117" s="156"/>
-      <c r="K117" s="154"/>
-      <c r="L117" s="183"/>
-      <c r="M117" s="182"/>
+      <c r="E117" s="152"/>
+      <c r="F117" s="155"/>
+      <c r="G117" s="155"/>
+      <c r="H117" s="155"/>
+      <c r="I117" s="155"/>
+      <c r="J117" s="155"/>
+      <c r="K117" s="153"/>
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E118" s="153" t="s">
+      <c r="E118" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="156"/>
-      <c r="G118" s="156"/>
-      <c r="H118" s="156"/>
-      <c r="I118" s="156"/>
-      <c r="J118" s="162">
+      <c r="F118" s="155"/>
+      <c r="G118" s="155"/>
+      <c r="H118" s="155"/>
+      <c r="I118" s="155"/>
+      <c r="J118" s="161">
         <f>J5</f>
-        <v>22026.264180000002</v>
-      </c>
-      <c r="K118" s="154"/>
-      <c r="L118" s="153"/>
-      <c r="M118" s="154"/>
+        <v>21673.998480000002</v>
+      </c>
+      <c r="K118" s="153"/>
+      <c r="L118" s="152"/>
+      <c r="M118" s="153"/>
     </row>
     <row r="119" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E119" s="163" t="s">
+      <c r="E119" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F119" s="156"/>
-      <c r="G119" s="156"/>
-      <c r="H119" s="156"/>
-      <c r="I119" s="156"/>
-      <c r="J119" s="162">
+      <c r="F119" s="155"/>
+      <c r="G119" s="155"/>
+      <c r="H119" s="155"/>
+      <c r="I119" s="155"/>
+      <c r="J119" s="161">
         <f>K5</f>
-        <v>23823.054539999997</v>
-      </c>
-      <c r="K119" s="154"/>
-      <c r="L119" s="153"/>
-      <c r="M119" s="154"/>
+        <v>25000</v>
+      </c>
+      <c r="K119" s="153"/>
+      <c r="L119" s="152"/>
+      <c r="M119" s="153"/>
     </row>
     <row r="120" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E120" s="163" t="s">
+      <c r="E120" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="156"/>
-      <c r="G120" s="156"/>
-      <c r="H120" s="156"/>
-      <c r="I120" s="156"/>
-      <c r="J120" s="162">
+      <c r="F120" s="155"/>
+      <c r="G120" s="155"/>
+      <c r="H120" s="155"/>
+      <c r="I120" s="155"/>
+      <c r="J120" s="161">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="154"/>
-      <c r="L120" s="153"/>
-      <c r="M120" s="154"/>
+      <c r="K120" s="153"/>
+      <c r="L120" s="152"/>
+      <c r="M120" s="153"/>
     </row>
     <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E121" s="163"/>
-      <c r="F121" s="156"/>
-      <c r="G121" s="156"/>
-      <c r="H121" s="156"/>
-      <c r="I121" s="156"/>
-      <c r="J121" s="162"/>
-      <c r="K121" s="154"/>
-      <c r="L121" s="153"/>
-      <c r="M121" s="154"/>
+      <c r="E121" s="162"/>
+      <c r="F121" s="155"/>
+      <c r="G121" s="155"/>
+      <c r="H121" s="155"/>
+      <c r="I121" s="155"/>
+      <c r="J121" s="161"/>
+      <c r="K121" s="153"/>
+      <c r="L121" s="152"/>
+      <c r="M121" s="153"/>
     </row>
     <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E122" s="163"/>
-      <c r="F122" s="156"/>
-      <c r="G122" s="156"/>
-      <c r="H122" s="156"/>
-      <c r="I122" s="156"/>
-      <c r="J122" s="162"/>
-      <c r="K122" s="154"/>
-      <c r="L122" s="153"/>
-      <c r="M122" s="154"/>
+      <c r="E122" s="162"/>
+      <c r="F122" s="155"/>
+      <c r="G122" s="155"/>
+      <c r="H122" s="155"/>
+      <c r="I122" s="155"/>
+      <c r="J122" s="161"/>
+      <c r="K122" s="153"/>
+      <c r="L122" s="152"/>
+      <c r="M122" s="153"/>
     </row>
     <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F123" s="156"/>
-      <c r="G123" s="156"/>
-      <c r="H123" s="156"/>
-      <c r="I123" s="156"/>
-      <c r="J123" s="162"/>
-      <c r="K123" s="154"/>
-      <c r="L123" s="153"/>
-      <c r="M123" s="154"/>
+      <c r="F123" s="155"/>
+      <c r="G123" s="155"/>
+      <c r="H123" s="155"/>
+      <c r="I123" s="155"/>
+      <c r="J123" s="161"/>
+      <c r="K123" s="153"/>
+      <c r="L123" s="152"/>
+      <c r="M123" s="153"/>
     </row>
     <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E124" s="163"/>
-      <c r="F124" s="156"/>
-      <c r="G124" s="156"/>
-      <c r="H124" s="156"/>
-      <c r="I124" s="156"/>
-      <c r="J124" s="162"/>
-      <c r="K124" s="154"/>
-      <c r="L124" s="153"/>
-      <c r="M124" s="154"/>
+      <c r="E124" s="162"/>
+      <c r="F124" s="155"/>
+      <c r="G124" s="155"/>
+      <c r="H124" s="155"/>
+      <c r="I124" s="155"/>
+      <c r="J124" s="161"/>
+      <c r="K124" s="153"/>
+      <c r="L124" s="152"/>
+      <c r="M124" s="153"/>
     </row>
     <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E125" s="153"/>
-      <c r="F125" s="156"/>
-      <c r="G125" s="156"/>
-      <c r="H125" s="156"/>
-      <c r="I125" s="156"/>
-      <c r="J125" s="156"/>
-      <c r="K125" s="154"/>
-      <c r="L125" s="153"/>
-      <c r="M125" s="154"/>
+      <c r="E125" s="152"/>
+      <c r="F125" s="155"/>
+      <c r="G125" s="155"/>
+      <c r="H125" s="155"/>
+      <c r="I125" s="155"/>
+      <c r="J125" s="155"/>
+      <c r="K125" s="153"/>
+      <c r="L125" s="152"/>
+      <c r="M125" s="153"/>
     </row>
     <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E126" s="153"/>
-      <c r="F126" s="156"/>
-      <c r="G126" s="156"/>
-      <c r="H126" s="156"/>
-      <c r="I126" s="156"/>
-      <c r="J126" s="156"/>
-      <c r="K126" s="154"/>
-      <c r="L126" s="153"/>
-      <c r="M126" s="154"/>
+      <c r="E126" s="152"/>
+      <c r="F126" s="155"/>
+      <c r="G126" s="155"/>
+      <c r="H126" s="155"/>
+      <c r="I126" s="155"/>
+      <c r="J126" s="155"/>
+      <c r="K126" s="153"/>
+      <c r="L126" s="152"/>
+      <c r="M126" s="153"/>
     </row>
     <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E127" s="153"/>
-      <c r="F127" s="156"/>
-      <c r="G127" s="156"/>
-      <c r="H127" s="156"/>
-      <c r="I127" s="156"/>
-      <c r="J127" s="156"/>
-      <c r="K127" s="154"/>
-      <c r="L127" s="164"/>
-      <c r="M127" s="165"/>
+      <c r="E127" s="152"/>
+      <c r="F127" s="155"/>
+      <c r="G127" s="155"/>
+      <c r="H127" s="155"/>
+      <c r="I127" s="155"/>
+      <c r="J127" s="155"/>
+      <c r="K127" s="153"/>
+      <c r="L127" s="163"/>
+      <c r="M127" s="164"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="199" t="s">
+      <c r="E128" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="200"/>
-      <c r="G128" s="200"/>
-      <c r="H128" s="200"/>
-      <c r="I128" s="200"/>
-      <c r="J128" s="201">
+      <c r="F128" s="174"/>
+      <c r="G128" s="174"/>
+      <c r="H128" s="174"/>
+      <c r="I128" s="174"/>
+      <c r="J128" s="175">
         <f>SUM(J118:J127)</f>
-        <v>45796.978719999999</v>
-      </c>
-      <c r="K128" s="194"/>
-      <c r="L128" s="166"/>
-      <c r="M128" s="167"/>
+        <v>46621.658479999998</v>
+      </c>
+      <c r="K128" s="176"/>
+      <c r="L128" s="165"/>
+      <c r="M128" s="166"/>
     </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="E128:I128"/>
     <mergeCell ref="J128:K128"/>
@@ -4693,36 +4714,6 @@
     <mergeCell ref="E37:K37"/>
     <mergeCell ref="E76:I76"/>
     <mergeCell ref="J76:K76"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4747,7 +4738,7 @@
         <v>79</v>
       </c>
       <c r="C1" s="111" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D1" s="112"/>
       <c r="F1" t="s">
@@ -4756,8 +4747,8 @@
       <c r="G1" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="142">
-        <v>10296.959999999999</v>
+      <c r="H1" s="141">
+        <v>301581.15999999997</v>
       </c>
       <c r="K1" s="113"/>
       <c r="L1" s="114"/>
@@ -4806,7 +4797,7 @@
       <c r="F4" s="110"/>
       <c r="H4" s="119">
         <f>H1</f>
-        <v>10296.959999999999</v>
+        <v>301581.15999999997</v>
       </c>
       <c r="I4" s="119"/>
       <c r="J4" s="119"/>
@@ -4822,24 +4813,26 @@
         <v>7735</v>
       </c>
       <c r="D5" s="112">
-        <f>C5+82</f>
-        <v>7817</v>
+        <f>C5+46.65</f>
+        <v>7781.65</v>
       </c>
       <c r="E5" s="116">
         <f>D5-C5</f>
-        <v>82</v>
+        <v>46.649999999999636</v>
       </c>
       <c r="F5" s="116">
         <f>E5*100/D14</f>
-        <v>13.7123745819398</v>
+        <v>10.329937998228306</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="120">
-        <f>H4*(F5/100)</f>
-        <v>1411.9577257525084</v>
+        <v>25000</v>
       </c>
       <c r="I5" s="116"/>
-      <c r="J5" s="5"/>
+      <c r="J5" s="211">
+        <f>H1-H12</f>
+        <v>-1.5265719324816018E-2</v>
+      </c>
       <c r="K5" s="5"/>
       <c r="L5" s="121"/>
       <c r="M5" s="122"/>
@@ -4864,15 +4857,18 @@
       </c>
       <c r="F6" s="116">
         <f>E6*100/D14</f>
-        <v>16.387959866220736</v>
+        <v>21.700620017714513</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="120">
-        <f>H4*(F6/100)</f>
-        <v>1687.4616722408025</v>
+        <f>J$6*(F6/100)</f>
+        <v>74547.000664303734</v>
       </c>
       <c r="I6" s="116"/>
-      <c r="J6" s="5"/>
+      <c r="J6" s="212">
+        <f>301581.16+2412.59+26196+7825+3233+1336+225+420+180+70+26+15+3+2</f>
+        <v>343524.75</v>
+      </c>
       <c r="K6" s="5"/>
       <c r="L6" s="121"/>
       <c r="M6" s="122"/>
@@ -4888,23 +4884,22 @@
         <v>7694</v>
       </c>
       <c r="D7" s="112">
-        <f>C7+97</f>
-        <v>7791</v>
+        <f>C7+46.65</f>
+        <v>7740.65</v>
       </c>
       <c r="E7" s="116">
         <f t="shared" ref="E7:E11" si="0">D7-C7</f>
-        <v>97</v>
+        <v>46.649999999999636</v>
       </c>
       <c r="F7" s="116">
         <f>E7*100/D14</f>
-        <v>16.220735785953178</v>
-      </c>
-      <c r="H7" s="123">
-        <f>H4*(F7/100)</f>
-        <v>1670.2426755852841</v>
+        <v>10.329937998228306</v>
+      </c>
+      <c r="H7" s="120">
+        <v>25000</v>
       </c>
       <c r="I7" s="110"/>
-      <c r="J7" s="5"/>
+      <c r="J7" s="211"/>
       <c r="K7" s="5"/>
       <c r="L7" s="121"/>
       <c r="M7" s="122"/>
@@ -4929,15 +4924,15 @@
       </c>
       <c r="F8" s="116">
         <f>E8*100/D14</f>
-        <v>17.892976588628763</v>
+        <v>23.693534100974009</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="120">
-        <f>H4*(F8/100)</f>
-        <v>1842.432642140468</v>
+        <f>J$6*(F8/100)</f>
+        <v>81393.15378653571</v>
       </c>
       <c r="I8" s="116"/>
-      <c r="J8" s="5"/>
+      <c r="J8" s="211"/>
       <c r="K8" s="5"/>
       <c r="L8" s="121"/>
       <c r="M8" s="122"/>
@@ -4962,15 +4957,15 @@
       </c>
       <c r="F9" s="116">
         <f>E9*100/D14</f>
-        <v>10.033444816053512</v>
+        <v>13.286093888396641</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="120">
-        <f>H4*(F9/100)</f>
-        <v>1033.1397993311036</v>
+        <f>J$6*(F9/100)</f>
+        <v>45641.020814879841</v>
       </c>
       <c r="I9" s="116"/>
-      <c r="J9" s="5"/>
+      <c r="J9" s="211"/>
       <c r="K9" s="5"/>
       <c r="L9" s="121"/>
       <c r="M9" s="122"/>
@@ -4986,21 +4981,20 @@
         <v>10706</v>
       </c>
       <c r="D10" s="112">
-        <f>C10+37+12+12</f>
-        <v>10767</v>
+        <f>C10+46.65</f>
+        <v>10752.65</v>
       </c>
       <c r="E10" s="116">
         <f t="shared" si="0"/>
-        <v>61</v>
+        <v>46.649999999999636</v>
       </c>
       <c r="F10" s="116">
         <f>E10*100/D14</f>
-        <v>10.200668896321071</v>
+        <v>10.329937998228306</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="120">
-        <f>H4*(F10/100)</f>
-        <v>1050.358795986622</v>
+        <v>25000</v>
       </c>
       <c r="I10" s="116"/>
       <c r="J10" s="5"/>
@@ -5019,21 +5013,20 @@
         <v>13147</v>
       </c>
       <c r="D11" s="112">
-        <f>C11+93</f>
-        <v>13240</v>
+        <f>C11+46.65</f>
+        <v>13193.65</v>
       </c>
       <c r="E11" s="116">
         <f t="shared" si="0"/>
-        <v>93</v>
+        <v>46.649999999999636</v>
       </c>
       <c r="F11" s="116">
         <f>E11*100/D14</f>
-        <v>15.551839464882944</v>
+        <v>10.329937998228306</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="120">
-        <f>H4*(F11/100)</f>
-        <v>1601.3666889632107</v>
+        <v>25000</v>
       </c>
       <c r="I11" s="116"/>
       <c r="J11" s="5"/>
@@ -5042,35 +5035,35 @@
       <c r="M11" s="122"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="124"/>
-      <c r="C12" s="125">
+      <c r="B12" s="123"/>
+      <c r="C12" s="124">
         <f>SUM(C5:C11)</f>
         <v>66255</v>
       </c>
-      <c r="D12" s="125">
+      <c r="D12" s="124">
         <f>SUM(D5:D11)</f>
-        <v>66853</v>
-      </c>
-      <c r="E12" s="126">
+        <v>66706.600000000006</v>
+      </c>
+      <c r="E12" s="125">
         <f>SUM(E5:E11)</f>
-        <v>598</v>
-      </c>
-      <c r="F12" s="125">
+        <v>451.59999999999854</v>
+      </c>
+      <c r="F12" s="124">
         <f>SUM(F5:F11)</f>
-        <v>100.00000000000003</v>
+        <v>99.999999999998366</v>
       </c>
       <c r="G12" s="61"/>
-      <c r="H12" s="125">
+      <c r="H12" s="210">
         <f>SUM(H5:H11)</f>
-        <v>10296.959999999999</v>
-      </c>
-      <c r="I12" s="124"/>
-      <c r="J12" s="124"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="127"/>
+        <v>301581.1752657193</v>
+      </c>
+      <c r="I12" s="123"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="126"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="128"/>
+      <c r="C13" s="127"/>
       <c r="H13" s="116"/>
       <c r="I13" s="116"/>
       <c r="J13" s="116"/>
@@ -5079,9 +5072,9 @@
       <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="129">
+      <c r="D14" s="128">
         <f>D12-C12</f>
-        <v>598</v>
+        <v>451.60000000000582</v>
       </c>
       <c r="H14" s="116"/>
       <c r="I14" s="116"/>
@@ -5122,36 +5115,36 @@
       <c r="J18" s="116"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C19" s="130"/>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="132"/>
-      <c r="J19" s="132"/>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
-      <c r="M19" s="133"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="130"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="G19" s="130"/>
+      <c r="H19" s="131"/>
+      <c r="I19" s="131"/>
+      <c r="J19" s="131"/>
+      <c r="K19" s="130"/>
+      <c r="L19" s="130"/>
+      <c r="M19" s="132"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C20" s="134"/>
+      <c r="C20" s="133"/>
       <c r="E20" t="s">
         <v>99</v>
       </c>
-      <c r="H20" s="135">
+      <c r="H20" s="134">
         <f>D14</f>
-        <v>598</v>
-      </c>
-      <c r="I20" s="135"/>
-      <c r="J20" s="135"/>
+        <v>451.60000000000582</v>
+      </c>
+      <c r="I20" s="134"/>
+      <c r="J20" s="134"/>
       <c r="K20" t="s">
         <v>100</v>
       </c>
-      <c r="M20" s="136"/>
+      <c r="M20" s="135"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C21" s="134"/>
+      <c r="C21" s="133"/>
       <c r="D21" t="s">
         <v>101</v>
       </c>
@@ -5170,23 +5163,23 @@
       <c r="K21" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="136"/>
+      <c r="M21" s="135"/>
     </row>
     <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="137"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="139"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
+      <c r="L22" s="137"/>
+      <c r="M22" s="138"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="K25" s="140" t="s">
+      <c r="K25" s="139" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5279,11 +5272,11 @@
       <c r="D1" s="55">
         <v>50000</v>
       </c>
-      <c r="H1" s="207">
+      <c r="H1" s="204">
         <v>250000</v>
       </c>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
@@ -5347,13 +5340,13 @@
         <v>53</v>
       </c>
       <c r="K4" s="67"/>
-      <c r="L4" s="205" t="s">
+      <c r="L4" s="202" t="s">
         <v>60</v>
       </c>
       <c r="M4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="203" t="s">
+      <c r="N4" s="200" t="s">
         <v>54</v>
       </c>
       <c r="P4" s="21"/>
@@ -5382,11 +5375,11 @@
         <v>59</v>
       </c>
       <c r="K5" s="57"/>
-      <c r="L5" s="206"/>
+      <c r="L5" s="203"/>
       <c r="M5" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="N5" s="204"/>
+      <c r="N5" s="201"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -5857,22 +5850,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="211" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="211" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="212">
+      <c r="A1" s="206" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
+      <c r="F1" s="206" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="207">
         <v>800000</v>
       </c>
-      <c r="J1" s="212"/>
+      <c r="J1" s="207"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="96"/>
@@ -5889,14 +5882,14 @@
       <c r="L2" s="101"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="186" t="s">
+      <c r="A3" s="192" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="179" t="s">
+      <c r="B3" s="193"/>
+      <c r="C3" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="190" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -5905,77 +5898,77 @@
       <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="179" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="179" t="s">
+      <c r="G3" s="188" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="188" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="175" t="s">
+      <c r="I3" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="184" t="s">
-        <v>128</v>
-      </c>
-      <c r="K3" s="169" t="s">
+      <c r="J3" s="190" t="s">
         <v>127</v>
+      </c>
+      <c r="K3" s="168" t="s">
+        <v>126</v>
       </c>
       <c r="L3" s="208" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="188"/>
-      <c r="B4" s="189"/>
-      <c r="C4" s="180"/>
-      <c r="D4" s="185"/>
+      <c r="A4" s="194"/>
+      <c r="B4" s="195"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="191"/>
       <c r="E4" s="57" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="180"/>
-      <c r="H4" s="180"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="170" t="s">
-        <v>129</v>
+      <c r="G4" s="189"/>
+      <c r="H4" s="189"/>
+      <c r="I4" s="199"/>
+      <c r="J4" s="191"/>
+      <c r="K4" s="169" t="s">
+        <v>128</v>
       </c>
       <c r="L4" s="209"/>
     </row>
     <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="177">
+      <c r="A5" s="186">
         <v>1</v>
       </c>
-      <c r="B5" s="178"/>
+      <c r="B5" s="187"/>
       <c r="C5" s="109" t="s">
         <v>65</v>
       </c>
       <c r="D5" s="58"/>
-      <c r="E5" s="148">
+      <c r="E5" s="147">
         <v>160512.70037999999</v>
       </c>
-      <c r="F5" s="149">
+      <c r="F5" s="148">
         <f>E5</f>
         <v>160512.70037999999</v>
       </c>
-      <c r="G5" s="150">
+      <c r="G5" s="149">
         <f>E5-F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="150">
+      <c r="H5" s="149">
         <f>IF(G5&gt;0,G5*4%,0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="94">
         <v>13.8</v>
       </c>
-      <c r="J5" s="171">
+      <c r="J5" s="170">
         <f t="shared" ref="J5:J14" si="0">D$1*I5/100</f>
         <v>0</v>
       </c>
-      <c r="K5" s="172">
+      <c r="K5" s="171">
         <f>I$1*I5/100</f>
         <v>110400</v>
       </c>
@@ -5985,39 +5978,39 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="177">
+      <c r="A6" s="186">
         <v>2</v>
       </c>
-      <c r="B6" s="178"/>
+      <c r="B6" s="187"/>
       <c r="C6" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D6" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="148">
+      <c r="E6" s="147">
         <v>137947.87148599999</v>
       </c>
-      <c r="F6" s="149">
+      <c r="F6" s="148">
         <f>343581.33-F7-F13-F14</f>
         <v>167947.86799000003</v>
       </c>
-      <c r="G6" s="150">
+      <c r="G6" s="149">
         <f t="shared" ref="G6:G14" si="1">E6-F6</f>
         <v>-29999.996504000039</v>
       </c>
-      <c r="H6" s="150">
+      <c r="H6" s="149">
         <f t="shared" ref="H6:H14" si="2">IF(G6&gt;0,G6*4%,0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="94">
         <v>11.86</v>
       </c>
-      <c r="J6" s="171">
+      <c r="J6" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="172">
+      <c r="K6" s="171">
         <f t="shared" ref="K6:K14" si="3">I$1*I6/100</f>
         <v>94880</v>
       </c>
@@ -6027,39 +6020,39 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="177">
+      <c r="A7" s="186">
         <v>3</v>
       </c>
-      <c r="B7" s="178"/>
+      <c r="B7" s="187"/>
       <c r="C7" s="109" t="s">
         <v>66</v>
       </c>
       <c r="D7" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="148">
+      <c r="E7" s="147">
         <v>144926.684546</v>
       </c>
-      <c r="F7" s="149">
+      <c r="F7" s="148">
         <f>E7</f>
         <v>144926.684546</v>
       </c>
-      <c r="G7" s="150">
+      <c r="G7" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="150">
+      <c r="H7" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I7" s="94">
         <v>12.46</v>
       </c>
-      <c r="J7" s="171">
+      <c r="J7" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="172">
+      <c r="K7" s="171">
         <f t="shared" si="3"/>
         <v>99680</v>
       </c>
@@ -6069,39 +6062,39 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="177">
+      <c r="A8" s="186">
         <v>4</v>
       </c>
-      <c r="B8" s="178"/>
+      <c r="B8" s="187"/>
       <c r="C8" s="109" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="148">
+      <c r="E8" s="147">
         <v>171562.48772500001</v>
       </c>
-      <c r="F8" s="149">
+      <c r="F8" s="148">
         <f>E8</f>
         <v>171562.48772500001</v>
       </c>
-      <c r="G8" s="150">
+      <c r="G8" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="150">
+      <c r="H8" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I8" s="94">
         <v>14.75</v>
       </c>
-      <c r="J8" s="171">
+      <c r="J8" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="172">
+      <c r="K8" s="171">
         <f t="shared" si="3"/>
         <v>118000</v>
       </c>
@@ -6111,39 +6104,39 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="177">
+      <c r="A9" s="186">
         <v>5</v>
       </c>
-      <c r="B9" s="178"/>
+      <c r="B9" s="187"/>
       <c r="C9" s="109" t="s">
         <v>68</v>
       </c>
       <c r="D9" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="148">
+      <c r="E9" s="147">
         <v>144345.11679100001</v>
       </c>
-      <c r="F9" s="149">
+      <c r="F9" s="148">
         <f>159931.14-F12</f>
         <v>144345.12416600002</v>
       </c>
-      <c r="G9" s="150">
+      <c r="G9" s="149">
         <f t="shared" si="1"/>
         <v>-7.3750000155996531E-3</v>
       </c>
-      <c r="H9" s="150">
+      <c r="H9" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="94">
         <v>12.41</v>
       </c>
-      <c r="J9" s="171">
+      <c r="J9" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="172">
+      <c r="K9" s="171">
         <f t="shared" si="3"/>
         <v>99280</v>
       </c>
@@ -6153,37 +6146,37 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="177">
+      <c r="A10" s="186">
         <v>6</v>
       </c>
-      <c r="B10" s="178"/>
+      <c r="B10" s="187"/>
       <c r="C10" s="109" t="s">
         <v>69</v>
       </c>
       <c r="D10" s="72"/>
-      <c r="E10" s="148">
+      <c r="E10" s="147">
         <v>145159.311648</v>
       </c>
-      <c r="F10" s="149">
+      <c r="F10" s="148">
         <f>150000</f>
         <v>150000</v>
       </c>
-      <c r="G10" s="150">
+      <c r="G10" s="149">
         <f t="shared" si="1"/>
         <v>-4840.6883519999974</v>
       </c>
-      <c r="H10" s="150">
+      <c r="H10" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I10" s="94">
         <v>12.48</v>
       </c>
-      <c r="J10" s="171">
+      <c r="J10" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="172">
+      <c r="K10" s="171">
         <f t="shared" si="3"/>
         <v>99840</v>
       </c>
@@ -6193,37 +6186,37 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="177">
+      <c r="A11" s="186">
         <v>7</v>
       </c>
-      <c r="B11" s="178"/>
+      <c r="B11" s="187"/>
       <c r="C11" s="109" t="s">
         <v>70</v>
       </c>
       <c r="D11" s="72"/>
-      <c r="E11" s="148">
+      <c r="E11" s="147">
         <v>212388.54412600002</v>
       </c>
-      <c r="F11" s="149">
+      <c r="F11" s="148">
         <f>E11</f>
         <v>212388.54412600002</v>
       </c>
-      <c r="G11" s="150">
+      <c r="G11" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="150">
+      <c r="H11" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I11" s="94">
         <v>18.260000000000002</v>
       </c>
-      <c r="J11" s="171">
+      <c r="J11" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="172">
+      <c r="K11" s="171">
         <f t="shared" si="3"/>
         <v>146080.00000000003</v>
       </c>
@@ -6233,38 +6226,38 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="177" t="s">
+      <c r="A12" s="186" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="178"/>
+      <c r="B12" s="187"/>
       <c r="C12" s="109" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
       <c r="D12" s="72"/>
-      <c r="E12" s="148">
+      <c r="E12" s="147">
         <v>15586.015834000002</v>
       </c>
-      <c r="F12" s="149">
+      <c r="F12" s="148">
         <f>E12</f>
         <v>15586.015834000002</v>
       </c>
-      <c r="G12" s="150">
+      <c r="G12" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="150">
+      <c r="H12" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="94">
         <v>1.34</v>
       </c>
-      <c r="J12" s="171">
+      <c r="J12" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="172">
+      <c r="K12" s="171">
         <f t="shared" si="3"/>
         <v>10720</v>
       </c>
@@ -6274,38 +6267,38 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="177" t="s">
+      <c r="A13" s="186" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="178"/>
+      <c r="B13" s="187"/>
       <c r="C13" s="109" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D13" s="72"/>
-      <c r="E13" s="148">
+      <c r="E13" s="147">
         <v>15353.388731999999</v>
       </c>
-      <c r="F13" s="149">
+      <c r="F13" s="148">
         <f>E13</f>
         <v>15353.388731999999</v>
       </c>
-      <c r="G13" s="150">
+      <c r="G13" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="150">
+      <c r="H13" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13" s="94">
         <v>1.32</v>
       </c>
-      <c r="J13" s="171">
+      <c r="J13" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="172">
+      <c r="K13" s="171">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
@@ -6315,38 +6308,38 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="177" t="s">
+      <c r="A14" s="186" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="178"/>
+      <c r="B14" s="187"/>
       <c r="C14" s="58" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
       <c r="D14" s="72"/>
-      <c r="E14" s="148">
+      <c r="E14" s="147">
         <v>15353.388731999999</v>
       </c>
-      <c r="F14" s="149">
+      <c r="F14" s="148">
         <f>E14</f>
         <v>15353.388731999999</v>
       </c>
-      <c r="G14" s="150">
+      <c r="G14" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H14" s="150">
+      <c r="H14" s="149">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I14" s="94">
         <v>1.32</v>
       </c>
-      <c r="J14" s="171">
+      <c r="J14" s="170">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="172">
+      <c r="K14" s="171">
         <f t="shared" si="3"/>
         <v>10560</v>
       </c>
@@ -6784,345 +6777,345 @@
     <row r="32" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
-      <c r="E32" s="192" t="s">
+      <c r="E32" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="193"/>
-      <c r="G32" s="193"/>
-      <c r="H32" s="193"/>
-      <c r="I32" s="193"/>
-      <c r="J32" s="193"/>
-      <c r="K32" s="194"/>
-      <c r="L32" s="151"/>
-      <c r="M32" s="152"/>
+      <c r="F32" s="178"/>
+      <c r="G32" s="178"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="150"/>
+      <c r="M32" s="151"/>
       <c r="N32"/>
     </row>
     <row r="33" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="195" t="s">
+      <c r="E33" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="193"/>
-      <c r="G33" s="193"/>
-      <c r="H33" s="193"/>
-      <c r="I33" s="193"/>
-      <c r="J33" s="193"/>
-      <c r="K33" s="194"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="154"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="178"/>
+      <c r="H33" s="178"/>
+      <c r="I33" s="178"/>
+      <c r="J33" s="178"/>
+      <c r="K33" s="176"/>
+      <c r="L33" s="152"/>
+      <c r="M33" s="153"/>
       <c r="N33"/>
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156">
+      <c r="E34" s="150"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="155"/>
+      <c r="J34" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K34" s="154"/>
-      <c r="L34" s="153"/>
-      <c r="M34" s="154"/>
+      <c r="K34" s="153"/>
+      <c r="L34" s="152"/>
+      <c r="M34" s="153"/>
       <c r="N34"/>
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="153" t="s">
+      <c r="E35" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F35" s="156"/>
-      <c r="G35" s="156"/>
-      <c r="H35" s="156"/>
-      <c r="I35" s="156"/>
-      <c r="J35" s="156"/>
-      <c r="K35" s="154"/>
-      <c r="L35" s="153"/>
-      <c r="M35" s="154"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="155"/>
+      <c r="H35" s="155"/>
+      <c r="I35" s="155"/>
+      <c r="J35" s="155"/>
+      <c r="K35" s="153"/>
+      <c r="L35" s="152"/>
+      <c r="M35" s="153"/>
       <c r="N35"/>
     </row>
     <row r="36" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
-      <c r="E36" s="157"/>
-      <c r="F36" s="158"/>
-      <c r="G36" s="158"/>
-      <c r="H36" s="158"/>
-      <c r="I36" s="158"/>
-      <c r="J36" s="158"/>
-      <c r="K36" s="159"/>
-      <c r="L36" s="153"/>
-      <c r="M36" s="154"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="157"/>
+      <c r="H36" s="157"/>
+      <c r="I36" s="157"/>
+      <c r="J36" s="157"/>
+      <c r="K36" s="158"/>
+      <c r="L36" s="152"/>
+      <c r="M36" s="153"/>
       <c r="N36"/>
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
-      <c r="E37" s="196" t="s">
+      <c r="E37" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F37" s="197"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="197"/>
-      <c r="I37" s="197"/>
-      <c r="J37" s="197"/>
-      <c r="K37" s="198"/>
-      <c r="L37" s="153"/>
-      <c r="M37" s="154"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="181"/>
+      <c r="H37" s="181"/>
+      <c r="I37" s="181"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="182"/>
+      <c r="L37" s="152"/>
+      <c r="M37" s="153"/>
       <c r="N37"/>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
-      <c r="E38" s="153"/>
-      <c r="F38" s="156"/>
-      <c r="G38" s="156"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="156"/>
-      <c r="J38" s="156"/>
-      <c r="K38" s="154"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="154"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="155"/>
+      <c r="G38" s="155"/>
+      <c r="H38" s="155"/>
+      <c r="I38" s="155"/>
+      <c r="J38" s="155"/>
+      <c r="K38" s="153"/>
+      <c r="L38" s="152"/>
+      <c r="M38" s="153"/>
       <c r="N38"/>
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="153" t="s">
+      <c r="E39" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="156"/>
-      <c r="G39" s="156" t="str">
+      <c r="F39" s="155"/>
+      <c r="G39" s="155" t="str">
         <f>C7</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="H39" s="156"/>
-      <c r="I39" s="156" t="s">
+      <c r="H39" s="155"/>
+      <c r="I39" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J39" s="160">
+      <c r="J39" s="159">
         <v>45674</v>
       </c>
-      <c r="K39" s="154"/>
-      <c r="L39" s="181" t="s">
+      <c r="K39" s="153"/>
+      <c r="L39" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M39" s="182"/>
+      <c r="M39" s="184"/>
       <c r="N39"/>
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
-      <c r="E40" s="153" t="s">
+      <c r="E40" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F40" s="161">
+      <c r="F40" s="160">
         <v>3</v>
       </c>
-      <c r="G40" s="156"/>
-      <c r="H40" s="156"/>
-      <c r="I40" s="156"/>
-      <c r="J40" s="156"/>
-      <c r="K40" s="154"/>
-      <c r="L40" s="153"/>
-      <c r="M40" s="154"/>
+      <c r="G40" s="155"/>
+      <c r="H40" s="155"/>
+      <c r="I40" s="155"/>
+      <c r="J40" s="155"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="152"/>
+      <c r="M40" s="153"/>
       <c r="N40"/>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="153"/>
-      <c r="F41" s="156"/>
-      <c r="G41" s="156"/>
-      <c r="H41" s="156"/>
-      <c r="I41" s="156"/>
-      <c r="J41" s="156"/>
-      <c r="K41" s="154"/>
-      <c r="L41" s="183"/>
-      <c r="M41" s="182"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="155"/>
+      <c r="G41" s="155"/>
+      <c r="H41" s="155"/>
+      <c r="I41" s="155"/>
+      <c r="J41" s="155"/>
+      <c r="K41" s="153"/>
+      <c r="L41" s="185"/>
+      <c r="M41" s="184"/>
       <c r="N41"/>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
-      <c r="E42" s="153" t="s">
+      <c r="E42" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="156"/>
-      <c r="G42" s="156"/>
-      <c r="H42" s="156"/>
-      <c r="I42" s="156"/>
-      <c r="J42" s="162">
+      <c r="F42" s="155"/>
+      <c r="G42" s="155"/>
+      <c r="H42" s="155"/>
+      <c r="I42" s="155"/>
+      <c r="J42" s="161">
         <f>J7</f>
         <v>0</v>
       </c>
-      <c r="K42" s="154"/>
-      <c r="L42" s="153"/>
-      <c r="M42" s="154"/>
+      <c r="K42" s="153"/>
+      <c r="L42" s="152"/>
+      <c r="M42" s="153"/>
       <c r="N42"/>
     </row>
     <row r="43" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
-      <c r="E43" s="163" t="s">
+      <c r="E43" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="156"/>
-      <c r="G43" s="156"/>
-      <c r="H43" s="156"/>
-      <c r="I43" s="156"/>
-      <c r="J43" s="162">
+      <c r="F43" s="155"/>
+      <c r="G43" s="155"/>
+      <c r="H43" s="155"/>
+      <c r="I43" s="155"/>
+      <c r="J43" s="161">
         <f>K7</f>
         <v>99680</v>
       </c>
-      <c r="K43" s="154"/>
-      <c r="L43" s="153"/>
-      <c r="M43" s="154"/>
+      <c r="K43" s="153"/>
+      <c r="L43" s="152"/>
+      <c r="M43" s="153"/>
       <c r="N43"/>
     </row>
     <row r="44" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
-      <c r="E44" s="163" t="s">
+      <c r="E44" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="F44" s="156"/>
-      <c r="G44" s="156"/>
-      <c r="H44" s="156"/>
-      <c r="I44" s="156"/>
-      <c r="J44" s="162">
+      <c r="F44" s="155"/>
+      <c r="G44" s="155"/>
+      <c r="H44" s="155"/>
+      <c r="I44" s="155"/>
+      <c r="J44" s="161">
         <f>G7+H7</f>
         <v>0</v>
       </c>
-      <c r="K44" s="154"/>
-      <c r="L44" s="153"/>
-      <c r="M44" s="154"/>
+      <c r="K44" s="153"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="153"/>
       <c r="N44"/>
     </row>
     <row r="45" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
-      <c r="E45" s="163"/>
-      <c r="F45" s="156"/>
-      <c r="G45" s="156"/>
-      <c r="H45" s="156"/>
-      <c r="I45" s="156"/>
-      <c r="J45" s="162"/>
-      <c r="K45" s="154"/>
-      <c r="L45" s="153"/>
-      <c r="M45" s="154"/>
+      <c r="E45" s="162"/>
+      <c r="F45" s="155"/>
+      <c r="G45" s="155"/>
+      <c r="H45" s="155"/>
+      <c r="I45" s="155"/>
+      <c r="J45" s="161"/>
+      <c r="K45" s="153"/>
+      <c r="L45" s="152"/>
+      <c r="M45" s="153"/>
       <c r="N45"/>
     </row>
     <row r="46" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
-      <c r="E46" s="163"/>
-      <c r="F46" s="156"/>
-      <c r="G46" s="156"/>
-      <c r="H46" s="156"/>
-      <c r="I46" s="156"/>
-      <c r="J46" s="162"/>
-      <c r="K46" s="154"/>
-      <c r="L46" s="153"/>
-      <c r="M46" s="154"/>
+      <c r="E46" s="162"/>
+      <c r="F46" s="155"/>
+      <c r="G46" s="155"/>
+      <c r="H46" s="155"/>
+      <c r="I46" s="155"/>
+      <c r="J46" s="161"/>
+      <c r="K46" s="153"/>
+      <c r="L46" s="152"/>
+      <c r="M46" s="153"/>
       <c r="N46"/>
     </row>
     <row r="47" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
-      <c r="F47" s="156"/>
-      <c r="G47" s="156"/>
-      <c r="H47" s="156"/>
-      <c r="I47" s="156"/>
-      <c r="J47" s="162"/>
-      <c r="K47" s="154"/>
-      <c r="L47" s="153"/>
-      <c r="M47" s="154"/>
+      <c r="F47" s="155"/>
+      <c r="G47" s="155"/>
+      <c r="H47" s="155"/>
+      <c r="I47" s="155"/>
+      <c r="J47" s="161"/>
+      <c r="K47" s="153"/>
+      <c r="L47" s="152"/>
+      <c r="M47" s="153"/>
       <c r="N47"/>
     </row>
     <row r="48" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
-      <c r="E48" s="163"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="156"/>
-      <c r="H48" s="156"/>
-      <c r="I48" s="156"/>
-      <c r="J48" s="162"/>
-      <c r="K48" s="154"/>
-      <c r="L48" s="153"/>
-      <c r="M48" s="154"/>
+      <c r="E48" s="162"/>
+      <c r="F48" s="155"/>
+      <c r="G48" s="155"/>
+      <c r="H48" s="155"/>
+      <c r="I48" s="155"/>
+      <c r="J48" s="161"/>
+      <c r="K48" s="153"/>
+      <c r="L48" s="152"/>
+      <c r="M48" s="153"/>
       <c r="N48"/>
     </row>
     <row r="49" spans="3:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
-      <c r="E49" s="153"/>
-      <c r="F49" s="156"/>
-      <c r="G49" s="156"/>
-      <c r="H49" s="156"/>
-      <c r="I49" s="156"/>
-      <c r="J49" s="156"/>
-      <c r="K49" s="154"/>
-      <c r="L49" s="153"/>
-      <c r="M49" s="154"/>
+      <c r="E49" s="152"/>
+      <c r="F49" s="155"/>
+      <c r="G49" s="155"/>
+      <c r="H49" s="155"/>
+      <c r="I49" s="155"/>
+      <c r="J49" s="155"/>
+      <c r="K49" s="153"/>
+      <c r="L49" s="152"/>
+      <c r="M49" s="153"/>
       <c r="N49"/>
     </row>
     <row r="50" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
-      <c r="E50" s="153" t="s">
+      <c r="E50" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="F50" s="156"/>
-      <c r="G50" s="156"/>
-      <c r="H50" s="156"/>
-      <c r="I50" s="156"/>
-      <c r="J50" s="156">
+      <c r="F50" s="155"/>
+      <c r="G50" s="155"/>
+      <c r="H50" s="155"/>
+      <c r="I50" s="155"/>
+      <c r="J50" s="155">
         <f>77200-77124.2</f>
         <v>75.80000000000291</v>
       </c>
-      <c r="K50" s="154"/>
-      <c r="L50" s="153"/>
-      <c r="M50" s="154"/>
+      <c r="K50" s="153"/>
+      <c r="L50" s="152"/>
+      <c r="M50" s="153"/>
       <c r="N50"/>
     </row>
     <row r="51" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
-      <c r="E51" s="153"/>
-      <c r="F51" s="156"/>
-      <c r="G51" s="156"/>
-      <c r="H51" s="156"/>
-      <c r="I51" s="156"/>
-      <c r="J51" s="156"/>
-      <c r="K51" s="154"/>
-      <c r="L51" s="164"/>
-      <c r="M51" s="165"/>
+      <c r="E51" s="152"/>
+      <c r="F51" s="155"/>
+      <c r="G51" s="155"/>
+      <c r="H51" s="155"/>
+      <c r="I51" s="155"/>
+      <c r="J51" s="155"/>
+      <c r="K51" s="153"/>
+      <c r="L51" s="163"/>
+      <c r="M51" s="164"/>
       <c r="N51"/>
     </row>
     <row r="52" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="199" t="s">
+      <c r="E52" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="200"/>
-      <c r="G52" s="200"/>
-      <c r="H52" s="200"/>
-      <c r="I52" s="200"/>
-      <c r="J52" s="201">
+      <c r="F52" s="174"/>
+      <c r="G52" s="174"/>
+      <c r="H52" s="174"/>
+      <c r="I52" s="174"/>
+      <c r="J52" s="175">
         <f>SUM(J42:J51)</f>
         <v>99755.8</v>
       </c>
-      <c r="K52" s="194"/>
-      <c r="L52" s="166"/>
-      <c r="M52" s="167"/>
+      <c r="K52" s="176"/>
+      <c r="L52" s="165"/>
+      <c r="M52" s="166"/>
       <c r="N52"/>
     </row>
     <row r="53" spans="3:14" x14ac:dyDescent="0.25">
@@ -7132,870 +7125,836 @@
     </row>
     <row r="55" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E56" s="192" t="s">
+      <c r="E56" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="194"/>
-      <c r="L56" s="151"/>
-      <c r="M56" s="152"/>
+      <c r="F56" s="178"/>
+      <c r="G56" s="178"/>
+      <c r="H56" s="178"/>
+      <c r="I56" s="178"/>
+      <c r="J56" s="178"/>
+      <c r="K56" s="176"/>
+      <c r="L56" s="150"/>
+      <c r="M56" s="151"/>
     </row>
     <row r="57" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E57" s="195" t="s">
+      <c r="E57" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F57" s="193"/>
-      <c r="G57" s="193"/>
-      <c r="H57" s="193"/>
-      <c r="I57" s="193"/>
-      <c r="J57" s="193"/>
-      <c r="K57" s="194"/>
-      <c r="L57" s="153"/>
-      <c r="M57" s="154"/>
+      <c r="F57" s="178"/>
+      <c r="G57" s="178"/>
+      <c r="H57" s="178"/>
+      <c r="I57" s="178"/>
+      <c r="J57" s="178"/>
+      <c r="K57" s="176"/>
+      <c r="L57" s="152"/>
+      <c r="M57" s="153"/>
     </row>
     <row r="58" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E58" s="151"/>
-      <c r="F58" s="155"/>
-      <c r="G58" s="155"/>
-      <c r="H58" s="155"/>
-      <c r="I58" s="156"/>
-      <c r="J58" s="156">
+      <c r="E58" s="150"/>
+      <c r="F58" s="154"/>
+      <c r="G58" s="154"/>
+      <c r="H58" s="154"/>
+      <c r="I58" s="155"/>
+      <c r="J58" s="155">
         <f>J34</f>
         <v>0</v>
       </c>
-      <c r="K58" s="154"/>
-      <c r="L58" s="153"/>
-      <c r="M58" s="154"/>
+      <c r="K58" s="153"/>
+      <c r="L58" s="152"/>
+      <c r="M58" s="153"/>
     </row>
     <row r="59" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E59" s="153" t="s">
+      <c r="E59" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F59" s="156"/>
-      <c r="G59" s="156"/>
-      <c r="H59" s="156"/>
-      <c r="I59" s="156"/>
-      <c r="J59" s="156"/>
-      <c r="K59" s="154"/>
-      <c r="L59" s="153"/>
-      <c r="M59" s="154"/>
+      <c r="F59" s="155"/>
+      <c r="G59" s="155"/>
+      <c r="H59" s="155"/>
+      <c r="I59" s="155"/>
+      <c r="J59" s="155"/>
+      <c r="K59" s="153"/>
+      <c r="L59" s="152"/>
+      <c r="M59" s="153"/>
     </row>
     <row r="60" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E60" s="157"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="158"/>
-      <c r="H60" s="158"/>
-      <c r="I60" s="158"/>
-      <c r="J60" s="158"/>
-      <c r="K60" s="159"/>
-      <c r="L60" s="153"/>
-      <c r="M60" s="154"/>
+      <c r="E60" s="156"/>
+      <c r="F60" s="157"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="157"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="158"/>
+      <c r="L60" s="152"/>
+      <c r="M60" s="153"/>
     </row>
     <row r="61" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E61" s="196" t="s">
+      <c r="E61" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F61" s="197"/>
-      <c r="G61" s="197"/>
-      <c r="H61" s="197"/>
-      <c r="I61" s="197"/>
-      <c r="J61" s="197"/>
-      <c r="K61" s="198"/>
-      <c r="L61" s="153"/>
-      <c r="M61" s="154"/>
+      <c r="F61" s="181"/>
+      <c r="G61" s="181"/>
+      <c r="H61" s="181"/>
+      <c r="I61" s="181"/>
+      <c r="J61" s="181"/>
+      <c r="K61" s="182"/>
+      <c r="L61" s="152"/>
+      <c r="M61" s="153"/>
     </row>
     <row r="62" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E62" s="153"/>
-      <c r="F62" s="156"/>
-      <c r="G62" s="156"/>
-      <c r="H62" s="156"/>
-      <c r="I62" s="156"/>
-      <c r="J62" s="156"/>
-      <c r="K62" s="154"/>
-      <c r="L62" s="153"/>
-      <c r="M62" s="154"/>
+      <c r="E62" s="152"/>
+      <c r="F62" s="155"/>
+      <c r="G62" s="155"/>
+      <c r="H62" s="155"/>
+      <c r="I62" s="155"/>
+      <c r="J62" s="155"/>
+      <c r="K62" s="153"/>
+      <c r="L62" s="152"/>
+      <c r="M62" s="153"/>
     </row>
     <row r="63" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E63" s="153" t="s">
+      <c r="E63" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F63" s="156"/>
-      <c r="G63" s="161" t="str">
+      <c r="F63" s="155"/>
+      <c r="G63" s="160" t="str">
         <f>C8</f>
         <v>Castelao Lorena</v>
       </c>
-      <c r="H63" s="156"/>
-      <c r="I63" s="156" t="s">
+      <c r="H63" s="155"/>
+      <c r="I63" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J63" s="160">
+      <c r="J63" s="159">
         <v>45674</v>
       </c>
-      <c r="K63" s="154"/>
-      <c r="L63" s="181" t="s">
+      <c r="K63" s="153"/>
+      <c r="L63" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M63" s="182"/>
+      <c r="M63" s="184"/>
     </row>
     <row r="64" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E64" s="153" t="s">
+      <c r="E64" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F64" s="161">
+      <c r="F64" s="160">
         <v>4</v>
       </c>
-      <c r="G64" s="156"/>
-      <c r="H64" s="156"/>
-      <c r="I64" s="156"/>
-      <c r="J64" s="156"/>
-      <c r="K64" s="154"/>
-      <c r="L64" s="153"/>
-      <c r="M64" s="154"/>
+      <c r="G64" s="155"/>
+      <c r="H64" s="155"/>
+      <c r="I64" s="155"/>
+      <c r="J64" s="155"/>
+      <c r="K64" s="153"/>
+      <c r="L64" s="152"/>
+      <c r="M64" s="153"/>
     </row>
     <row r="65" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E65" s="153"/>
-      <c r="F65" s="156"/>
-      <c r="G65" s="156"/>
-      <c r="H65" s="156"/>
-      <c r="I65" s="156"/>
-      <c r="J65" s="156"/>
-      <c r="K65" s="154"/>
-      <c r="L65" s="183"/>
-      <c r="M65" s="182"/>
+      <c r="E65" s="152"/>
+      <c r="F65" s="155"/>
+      <c r="G65" s="155"/>
+      <c r="H65" s="155"/>
+      <c r="I65" s="155"/>
+      <c r="J65" s="155"/>
+      <c r="K65" s="153"/>
+      <c r="L65" s="185"/>
+      <c r="M65" s="184"/>
     </row>
     <row r="66" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E66" s="153" t="s">
+      <c r="E66" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="156"/>
-      <c r="G66" s="156"/>
-      <c r="H66" s="156"/>
-      <c r="I66" s="156"/>
-      <c r="J66" s="162">
+      <c r="F66" s="155"/>
+      <c r="G66" s="155"/>
+      <c r="H66" s="155"/>
+      <c r="I66" s="155"/>
+      <c r="J66" s="161">
         <f>J8</f>
         <v>0</v>
       </c>
-      <c r="K66" s="154"/>
-      <c r="L66" s="153"/>
-      <c r="M66" s="154"/>
+      <c r="K66" s="153"/>
+      <c r="L66" s="152"/>
+      <c r="M66" s="153"/>
     </row>
     <row r="67" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E67" s="163" t="s">
+      <c r="E67" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F67" s="156"/>
-      <c r="G67" s="156"/>
-      <c r="H67" s="156"/>
-      <c r="I67" s="156"/>
-      <c r="J67" s="162">
+      <c r="F67" s="155"/>
+      <c r="G67" s="155"/>
+      <c r="H67" s="155"/>
+      <c r="I67" s="155"/>
+      <c r="J67" s="161">
         <f>K8</f>
         <v>118000</v>
       </c>
-      <c r="K67" s="154"/>
-      <c r="L67" s="153"/>
-      <c r="M67" s="154"/>
+      <c r="K67" s="153"/>
+      <c r="L67" s="152"/>
+      <c r="M67" s="153"/>
     </row>
     <row r="68" spans="5:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E68" s="163" t="s">
+      <c r="E68" s="162" t="s">
         <v>120</v>
       </c>
-      <c r="F68" s="156"/>
-      <c r="G68" s="156"/>
-      <c r="H68" s="156"/>
-      <c r="I68" s="156"/>
-      <c r="J68" s="162">
+      <c r="F68" s="155"/>
+      <c r="G68" s="155"/>
+      <c r="H68" s="155"/>
+      <c r="I68" s="155"/>
+      <c r="J68" s="161">
         <f>G29+H29</f>
         <v>0</v>
       </c>
-      <c r="K68" s="154"/>
-      <c r="L68" s="153"/>
-      <c r="M68" s="154"/>
+      <c r="K68" s="153"/>
+      <c r="L68" s="152"/>
+      <c r="M68" s="153"/>
     </row>
     <row r="69" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E69" s="163"/>
-      <c r="F69" s="156"/>
-      <c r="G69" s="156"/>
-      <c r="H69" s="156"/>
-      <c r="I69" s="156"/>
-      <c r="J69" s="162"/>
-      <c r="K69" s="154"/>
-      <c r="L69" s="153"/>
-      <c r="M69" s="154"/>
+      <c r="E69" s="162"/>
+      <c r="F69" s="155"/>
+      <c r="G69" s="155"/>
+      <c r="H69" s="155"/>
+      <c r="I69" s="155"/>
+      <c r="J69" s="161"/>
+      <c r="K69" s="153"/>
+      <c r="L69" s="152"/>
+      <c r="M69" s="153"/>
     </row>
     <row r="70" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E70" s="163"/>
-      <c r="F70" s="156"/>
-      <c r="G70" s="156"/>
-      <c r="H70" s="156"/>
-      <c r="I70" s="156"/>
-      <c r="J70" s="162"/>
-      <c r="K70" s="154"/>
-      <c r="L70" s="153"/>
-      <c r="M70" s="154"/>
+      <c r="E70" s="162"/>
+      <c r="F70" s="155"/>
+      <c r="G70" s="155"/>
+      <c r="H70" s="155"/>
+      <c r="I70" s="155"/>
+      <c r="J70" s="161"/>
+      <c r="K70" s="153"/>
+      <c r="L70" s="152"/>
+      <c r="M70" s="153"/>
     </row>
     <row r="71" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="F71" s="156"/>
-      <c r="G71" s="156"/>
-      <c r="H71" s="156"/>
-      <c r="I71" s="156"/>
-      <c r="J71" s="162"/>
-      <c r="K71" s="154"/>
-      <c r="L71" s="153"/>
-      <c r="M71" s="154"/>
+      <c r="F71" s="155"/>
+      <c r="G71" s="155"/>
+      <c r="H71" s="155"/>
+      <c r="I71" s="155"/>
+      <c r="J71" s="161"/>
+      <c r="K71" s="153"/>
+      <c r="L71" s="152"/>
+      <c r="M71" s="153"/>
     </row>
     <row r="72" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E72" s="163"/>
-      <c r="F72" s="156"/>
-      <c r="G72" s="156"/>
-      <c r="H72" s="156"/>
-      <c r="I72" s="156"/>
-      <c r="J72" s="162"/>
-      <c r="K72" s="154"/>
-      <c r="L72" s="153"/>
-      <c r="M72" s="154"/>
+      <c r="E72" s="162"/>
+      <c r="F72" s="155"/>
+      <c r="G72" s="155"/>
+      <c r="H72" s="155"/>
+      <c r="I72" s="155"/>
+      <c r="J72" s="161"/>
+      <c r="K72" s="153"/>
+      <c r="L72" s="152"/>
+      <c r="M72" s="153"/>
     </row>
     <row r="73" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E73" s="153"/>
-      <c r="F73" s="156"/>
-      <c r="G73" s="156"/>
-      <c r="H73" s="156"/>
-      <c r="I73" s="156"/>
-      <c r="J73" s="156"/>
-      <c r="K73" s="154"/>
-      <c r="L73" s="153"/>
-      <c r="M73" s="154"/>
+      <c r="E73" s="152"/>
+      <c r="F73" s="155"/>
+      <c r="G73" s="155"/>
+      <c r="H73" s="155"/>
+      <c r="I73" s="155"/>
+      <c r="J73" s="155"/>
+      <c r="K73" s="153"/>
+      <c r="L73" s="152"/>
+      <c r="M73" s="153"/>
     </row>
     <row r="74" spans="5:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="E74" s="153"/>
-      <c r="F74" s="156"/>
-      <c r="G74" s="156"/>
-      <c r="H74" s="156"/>
-      <c r="I74" s="156"/>
-      <c r="J74" s="156"/>
-      <c r="K74" s="154"/>
-      <c r="L74" s="153"/>
-      <c r="M74" s="154"/>
+      <c r="E74" s="152"/>
+      <c r="F74" s="155"/>
+      <c r="G74" s="155"/>
+      <c r="H74" s="155"/>
+      <c r="I74" s="155"/>
+      <c r="J74" s="155"/>
+      <c r="K74" s="153"/>
+      <c r="L74" s="152"/>
+      <c r="M74" s="153"/>
     </row>
     <row r="75" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E75" s="153"/>
-      <c r="F75" s="156"/>
-      <c r="G75" s="156"/>
-      <c r="H75" s="156"/>
-      <c r="I75" s="156"/>
-      <c r="J75" s="156"/>
-      <c r="K75" s="154"/>
-      <c r="L75" s="164"/>
-      <c r="M75" s="165"/>
+      <c r="E75" s="152"/>
+      <c r="F75" s="155"/>
+      <c r="G75" s="155"/>
+      <c r="H75" s="155"/>
+      <c r="I75" s="155"/>
+      <c r="J75" s="155"/>
+      <c r="K75" s="153"/>
+      <c r="L75" s="163"/>
+      <c r="M75" s="164"/>
     </row>
     <row r="76" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E76" s="199" t="s">
+      <c r="E76" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="200"/>
-      <c r="G76" s="200"/>
-      <c r="H76" s="200"/>
-      <c r="I76" s="200"/>
-      <c r="J76" s="201">
+      <c r="F76" s="174"/>
+      <c r="G76" s="174"/>
+      <c r="H76" s="174"/>
+      <c r="I76" s="174"/>
+      <c r="J76" s="175">
         <f>SUM(J66:J75)</f>
         <v>118000</v>
       </c>
-      <c r="K76" s="194"/>
-      <c r="L76" s="166"/>
-      <c r="M76" s="167"/>
+      <c r="K76" s="176"/>
+      <c r="L76" s="165"/>
+      <c r="M76" s="166"/>
     </row>
     <row r="82" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E83" s="192" t="s">
+      <c r="E83" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="193"/>
-      <c r="G83" s="193"/>
-      <c r="H83" s="193"/>
-      <c r="I83" s="193"/>
-      <c r="J83" s="193"/>
-      <c r="K83" s="194"/>
-      <c r="L83" s="151"/>
-      <c r="M83" s="152"/>
+      <c r="F83" s="178"/>
+      <c r="G83" s="178"/>
+      <c r="H83" s="178"/>
+      <c r="I83" s="178"/>
+      <c r="J83" s="178"/>
+      <c r="K83" s="176"/>
+      <c r="L83" s="150"/>
+      <c r="M83" s="151"/>
     </row>
     <row r="84" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E84" s="195" t="s">
+      <c r="E84" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="193"/>
-      <c r="G84" s="193"/>
-      <c r="H84" s="193"/>
-      <c r="I84" s="193"/>
-      <c r="J84" s="193"/>
-      <c r="K84" s="194"/>
-      <c r="L84" s="153"/>
-      <c r="M84" s="154"/>
+      <c r="F84" s="178"/>
+      <c r="G84" s="178"/>
+      <c r="H84" s="178"/>
+      <c r="I84" s="178"/>
+      <c r="J84" s="178"/>
+      <c r="K84" s="176"/>
+      <c r="L84" s="152"/>
+      <c r="M84" s="153"/>
     </row>
     <row r="85" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E85" s="151"/>
-      <c r="F85" s="155"/>
-      <c r="G85" s="155"/>
-      <c r="H85" s="155"/>
-      <c r="I85" s="156"/>
-      <c r="J85" s="156">
+      <c r="E85" s="150"/>
+      <c r="F85" s="154"/>
+      <c r="G85" s="154"/>
+      <c r="H85" s="154"/>
+      <c r="I85" s="155"/>
+      <c r="J85" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K85" s="154"/>
-      <c r="L85" s="153"/>
-      <c r="M85" s="154"/>
+      <c r="K85" s="153"/>
+      <c r="L85" s="152"/>
+      <c r="M85" s="153"/>
     </row>
     <row r="86" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E86" s="153" t="s">
+      <c r="E86" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F86" s="156"/>
-      <c r="G86" s="156"/>
-      <c r="H86" s="156"/>
-      <c r="I86" s="156"/>
-      <c r="J86" s="156"/>
-      <c r="K86" s="154"/>
-      <c r="L86" s="153"/>
-      <c r="M86" s="154"/>
+      <c r="F86" s="155"/>
+      <c r="G86" s="155"/>
+      <c r="H86" s="155"/>
+      <c r="I86" s="155"/>
+      <c r="J86" s="155"/>
+      <c r="K86" s="153"/>
+      <c r="L86" s="152"/>
+      <c r="M86" s="153"/>
     </row>
     <row r="87" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E87" s="157"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="158"/>
-      <c r="H87" s="158"/>
-      <c r="I87" s="158"/>
-      <c r="J87" s="158"/>
-      <c r="K87" s="159"/>
-      <c r="L87" s="153"/>
-      <c r="M87" s="154"/>
+      <c r="E87" s="156"/>
+      <c r="F87" s="157"/>
+      <c r="G87" s="157"/>
+      <c r="H87" s="157"/>
+      <c r="I87" s="157"/>
+      <c r="J87" s="157"/>
+      <c r="K87" s="158"/>
+      <c r="L87" s="152"/>
+      <c r="M87" s="153"/>
     </row>
     <row r="88" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E88" s="196" t="s">
+      <c r="E88" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F88" s="197"/>
-      <c r="G88" s="197"/>
-      <c r="H88" s="197"/>
-      <c r="I88" s="197"/>
-      <c r="J88" s="197"/>
-      <c r="K88" s="198"/>
-      <c r="L88" s="153"/>
-      <c r="M88" s="154"/>
+      <c r="F88" s="181"/>
+      <c r="G88" s="181"/>
+      <c r="H88" s="181"/>
+      <c r="I88" s="181"/>
+      <c r="J88" s="181"/>
+      <c r="K88" s="182"/>
+      <c r="L88" s="152"/>
+      <c r="M88" s="153"/>
     </row>
     <row r="89" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E89" s="153"/>
-      <c r="F89" s="156"/>
-      <c r="G89" s="156"/>
-      <c r="H89" s="156"/>
-      <c r="I89" s="156"/>
-      <c r="J89" s="156"/>
-      <c r="K89" s="154"/>
-      <c r="L89" s="153"/>
-      <c r="M89" s="154"/>
+      <c r="E89" s="152"/>
+      <c r="F89" s="155"/>
+      <c r="G89" s="155"/>
+      <c r="H89" s="155"/>
+      <c r="I89" s="155"/>
+      <c r="J89" s="155"/>
+      <c r="K89" s="153"/>
+      <c r="L89" s="152"/>
+      <c r="M89" s="153"/>
     </row>
     <row r="90" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E90" s="153" t="s">
+      <c r="E90" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F90" s="156"/>
-      <c r="G90" s="161" t="str">
+      <c r="F90" s="155"/>
+      <c r="G90" s="160" t="str">
         <f>C10</f>
         <v>Valdez Norberto</v>
       </c>
-      <c r="H90" s="156"/>
-      <c r="I90" s="156" t="s">
+      <c r="H90" s="155"/>
+      <c r="I90" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J90" s="160">
+      <c r="J90" s="159">
         <v>45674</v>
       </c>
-      <c r="K90" s="154"/>
-      <c r="L90" s="181" t="s">
+      <c r="K90" s="153"/>
+      <c r="L90" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M90" s="182"/>
+      <c r="M90" s="184"/>
     </row>
     <row r="91" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E91" s="153" t="s">
+      <c r="E91" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F91" s="161">
+      <c r="F91" s="160">
         <v>6</v>
       </c>
-      <c r="G91" s="156"/>
-      <c r="H91" s="156"/>
-      <c r="I91" s="156"/>
-      <c r="J91" s="156"/>
-      <c r="K91" s="154"/>
-      <c r="L91" s="153"/>
-      <c r="M91" s="154"/>
+      <c r="G91" s="155"/>
+      <c r="H91" s="155"/>
+      <c r="I91" s="155"/>
+      <c r="J91" s="155"/>
+      <c r="K91" s="153"/>
+      <c r="L91" s="152"/>
+      <c r="M91" s="153"/>
     </row>
     <row r="92" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E92" s="153"/>
-      <c r="F92" s="156"/>
-      <c r="G92" s="156"/>
-      <c r="H92" s="156"/>
-      <c r="I92" s="156"/>
-      <c r="J92" s="156"/>
-      <c r="K92" s="154"/>
-      <c r="L92" s="183"/>
-      <c r="M92" s="182"/>
+      <c r="E92" s="152"/>
+      <c r="F92" s="155"/>
+      <c r="G92" s="155"/>
+      <c r="H92" s="155"/>
+      <c r="I92" s="155"/>
+      <c r="J92" s="155"/>
+      <c r="K92" s="153"/>
+      <c r="L92" s="185"/>
+      <c r="M92" s="184"/>
     </row>
     <row r="93" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E93" s="153" t="s">
+      <c r="E93" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F93" s="156"/>
-      <c r="G93" s="156"/>
-      <c r="H93" s="156"/>
-      <c r="I93" s="156"/>
-      <c r="J93" s="162">
+      <c r="F93" s="155"/>
+      <c r="G93" s="155"/>
+      <c r="H93" s="155"/>
+      <c r="I93" s="155"/>
+      <c r="J93" s="161">
         <f>J10</f>
         <v>0</v>
       </c>
-      <c r="K93" s="154"/>
-      <c r="L93" s="153"/>
-      <c r="M93" s="154"/>
+      <c r="K93" s="153"/>
+      <c r="L93" s="152"/>
+      <c r="M93" s="153"/>
     </row>
     <row r="94" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E94" s="163" t="s">
+      <c r="E94" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F94" s="156"/>
-      <c r="G94" s="156"/>
-      <c r="H94" s="156"/>
-      <c r="I94" s="156"/>
-      <c r="J94" s="162">
+      <c r="F94" s="155"/>
+      <c r="G94" s="155"/>
+      <c r="H94" s="155"/>
+      <c r="I94" s="155"/>
+      <c r="J94" s="161">
         <f>K10</f>
         <v>99840</v>
       </c>
-      <c r="K94" s="154"/>
-      <c r="L94" s="153"/>
-      <c r="M94" s="154"/>
+      <c r="K94" s="153"/>
+      <c r="L94" s="152"/>
+      <c r="M94" s="153"/>
     </row>
     <row r="95" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E95" s="163" t="s">
+      <c r="E95" s="162" t="s">
         <v>121</v>
       </c>
-      <c r="F95" s="156"/>
-      <c r="G95" s="156"/>
-      <c r="H95" s="156"/>
-      <c r="I95" s="156"/>
-      <c r="J95" s="162">
+      <c r="F95" s="155"/>
+      <c r="G95" s="155"/>
+      <c r="H95" s="155"/>
+      <c r="I95" s="155"/>
+      <c r="J95" s="161">
         <v>23.89</v>
       </c>
-      <c r="K95" s="154"/>
-      <c r="L95" s="153"/>
-      <c r="M95" s="154"/>
+      <c r="K95" s="153"/>
+      <c r="L95" s="152"/>
+      <c r="M95" s="153"/>
     </row>
     <row r="96" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E96" s="163"/>
-      <c r="F96" s="156"/>
-      <c r="G96" s="156"/>
-      <c r="H96" s="156"/>
-      <c r="I96" s="156"/>
-      <c r="J96" s="162"/>
-      <c r="K96" s="154"/>
-      <c r="L96" s="153"/>
-      <c r="M96" s="154"/>
+      <c r="E96" s="162"/>
+      <c r="F96" s="155"/>
+      <c r="G96" s="155"/>
+      <c r="H96" s="155"/>
+      <c r="I96" s="155"/>
+      <c r="J96" s="161"/>
+      <c r="K96" s="153"/>
+      <c r="L96" s="152"/>
+      <c r="M96" s="153"/>
     </row>
     <row r="97" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E97" s="163"/>
-      <c r="F97" s="156"/>
-      <c r="G97" s="156"/>
-      <c r="H97" s="156"/>
-      <c r="I97" s="156"/>
-      <c r="J97" s="162"/>
-      <c r="K97" s="154"/>
-      <c r="L97" s="153"/>
-      <c r="M97" s="154"/>
+      <c r="E97" s="162"/>
+      <c r="F97" s="155"/>
+      <c r="G97" s="155"/>
+      <c r="H97" s="155"/>
+      <c r="I97" s="155"/>
+      <c r="J97" s="161"/>
+      <c r="K97" s="153"/>
+      <c r="L97" s="152"/>
+      <c r="M97" s="153"/>
     </row>
     <row r="98" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F98" s="156"/>
-      <c r="G98" s="156"/>
-      <c r="H98" s="156"/>
-      <c r="I98" s="156"/>
-      <c r="J98" s="162"/>
-      <c r="K98" s="154"/>
-      <c r="L98" s="153"/>
-      <c r="M98" s="154"/>
+      <c r="F98" s="155"/>
+      <c r="G98" s="155"/>
+      <c r="H98" s="155"/>
+      <c r="I98" s="155"/>
+      <c r="J98" s="161"/>
+      <c r="K98" s="153"/>
+      <c r="L98" s="152"/>
+      <c r="M98" s="153"/>
     </row>
     <row r="99" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E99" s="163"/>
-      <c r="F99" s="156"/>
-      <c r="G99" s="156"/>
-      <c r="H99" s="156"/>
-      <c r="I99" s="156"/>
-      <c r="J99" s="162"/>
-      <c r="K99" s="154"/>
-      <c r="L99" s="153"/>
-      <c r="M99" s="154"/>
+      <c r="E99" s="162"/>
+      <c r="F99" s="155"/>
+      <c r="G99" s="155"/>
+      <c r="H99" s="155"/>
+      <c r="I99" s="155"/>
+      <c r="J99" s="161"/>
+      <c r="K99" s="153"/>
+      <c r="L99" s="152"/>
+      <c r="M99" s="153"/>
     </row>
     <row r="100" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E100" s="153"/>
-      <c r="F100" s="156"/>
-      <c r="G100" s="156"/>
-      <c r="H100" s="156"/>
-      <c r="I100" s="156"/>
-      <c r="J100" s="156"/>
-      <c r="K100" s="154"/>
-      <c r="L100" s="153"/>
-      <c r="M100" s="154"/>
+      <c r="E100" s="152"/>
+      <c r="F100" s="155"/>
+      <c r="G100" s="155"/>
+      <c r="H100" s="155"/>
+      <c r="I100" s="155"/>
+      <c r="J100" s="155"/>
+      <c r="K100" s="153"/>
+      <c r="L100" s="152"/>
+      <c r="M100" s="153"/>
     </row>
     <row r="101" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E101" s="153"/>
-      <c r="F101" s="156"/>
-      <c r="G101" s="156"/>
-      <c r="H101" s="156"/>
-      <c r="I101" s="156"/>
-      <c r="J101" s="156"/>
-      <c r="K101" s="154"/>
-      <c r="L101" s="153"/>
-      <c r="M101" s="154"/>
+      <c r="E101" s="152"/>
+      <c r="F101" s="155"/>
+      <c r="G101" s="155"/>
+      <c r="H101" s="155"/>
+      <c r="I101" s="155"/>
+      <c r="J101" s="155"/>
+      <c r="K101" s="153"/>
+      <c r="L101" s="152"/>
+      <c r="M101" s="153"/>
     </row>
     <row r="102" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E102" s="153"/>
-      <c r="F102" s="156"/>
-      <c r="G102" s="156"/>
-      <c r="H102" s="156"/>
-      <c r="I102" s="156"/>
-      <c r="J102" s="156"/>
-      <c r="K102" s="154"/>
-      <c r="L102" s="164"/>
-      <c r="M102" s="165"/>
+      <c r="E102" s="152"/>
+      <c r="F102" s="155"/>
+      <c r="G102" s="155"/>
+      <c r="H102" s="155"/>
+      <c r="I102" s="155"/>
+      <c r="J102" s="155"/>
+      <c r="K102" s="153"/>
+      <c r="L102" s="163"/>
+      <c r="M102" s="164"/>
     </row>
     <row r="103" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E103" s="199" t="s">
+      <c r="E103" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F103" s="200"/>
-      <c r="G103" s="200"/>
-      <c r="H103" s="200"/>
-      <c r="I103" s="200"/>
-      <c r="J103" s="201">
+      <c r="F103" s="174"/>
+      <c r="G103" s="174"/>
+      <c r="H103" s="174"/>
+      <c r="I103" s="174"/>
+      <c r="J103" s="175">
         <f>SUM(J93:J102)</f>
         <v>99863.89</v>
       </c>
-      <c r="K103" s="194"/>
-      <c r="L103" s="166"/>
-      <c r="M103" s="167"/>
+      <c r="K103" s="176"/>
+      <c r="L103" s="165"/>
+      <c r="M103" s="166"/>
     </row>
     <row r="107" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E108" s="192" t="s">
+      <c r="E108" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="F108" s="193"/>
-      <c r="G108" s="193"/>
-      <c r="H108" s="193"/>
-      <c r="I108" s="193"/>
-      <c r="J108" s="193"/>
-      <c r="K108" s="194"/>
-      <c r="L108" s="151"/>
-      <c r="M108" s="152"/>
+      <c r="F108" s="178"/>
+      <c r="G108" s="178"/>
+      <c r="H108" s="178"/>
+      <c r="I108" s="178"/>
+      <c r="J108" s="178"/>
+      <c r="K108" s="176"/>
+      <c r="L108" s="150"/>
+      <c r="M108" s="151"/>
     </row>
     <row r="109" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E109" s="195" t="s">
+      <c r="E109" s="179" t="s">
         <v>112</v>
       </c>
-      <c r="F109" s="193"/>
-      <c r="G109" s="193"/>
-      <c r="H109" s="193"/>
-      <c r="I109" s="193"/>
-      <c r="J109" s="193"/>
-      <c r="K109" s="194"/>
-      <c r="L109" s="153"/>
-      <c r="M109" s="154"/>
+      <c r="F109" s="178"/>
+      <c r="G109" s="178"/>
+      <c r="H109" s="178"/>
+      <c r="I109" s="178"/>
+      <c r="J109" s="178"/>
+      <c r="K109" s="176"/>
+      <c r="L109" s="152"/>
+      <c r="M109" s="153"/>
     </row>
     <row r="110" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E110" s="151"/>
-      <c r="F110" s="155"/>
-      <c r="G110" s="155"/>
-      <c r="H110" s="155"/>
-      <c r="I110" s="156"/>
-      <c r="J110" s="156">
+      <c r="E110" s="150"/>
+      <c r="F110" s="154"/>
+      <c r="G110" s="154"/>
+      <c r="H110" s="154"/>
+      <c r="I110" s="155"/>
+      <c r="J110" s="155">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="K110" s="154"/>
-      <c r="L110" s="153"/>
-      <c r="M110" s="154"/>
+      <c r="K110" s="153"/>
+      <c r="L110" s="152"/>
+      <c r="M110" s="153"/>
     </row>
     <row r="111" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E111" s="153" t="s">
+      <c r="E111" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="F111" s="156"/>
-      <c r="G111" s="156"/>
-      <c r="H111" s="156"/>
-      <c r="I111" s="156"/>
-      <c r="J111" s="156"/>
-      <c r="K111" s="154"/>
-      <c r="L111" s="153"/>
-      <c r="M111" s="154"/>
+      <c r="F111" s="155"/>
+      <c r="G111" s="155"/>
+      <c r="H111" s="155"/>
+      <c r="I111" s="155"/>
+      <c r="J111" s="155"/>
+      <c r="K111" s="153"/>
+      <c r="L111" s="152"/>
+      <c r="M111" s="153"/>
     </row>
     <row r="112" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E112" s="157"/>
-      <c r="F112" s="158"/>
-      <c r="G112" s="158"/>
-      <c r="H112" s="158"/>
-      <c r="I112" s="158"/>
-      <c r="J112" s="158"/>
-      <c r="K112" s="159"/>
-      <c r="L112" s="153"/>
-      <c r="M112" s="154"/>
+      <c r="E112" s="156"/>
+      <c r="F112" s="157"/>
+      <c r="G112" s="157"/>
+      <c r="H112" s="157"/>
+      <c r="I112" s="157"/>
+      <c r="J112" s="157"/>
+      <c r="K112" s="158"/>
+      <c r="L112" s="152"/>
+      <c r="M112" s="153"/>
     </row>
     <row r="113" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E113" s="196" t="s">
+      <c r="E113" s="180" t="s">
         <v>49</v>
       </c>
-      <c r="F113" s="197"/>
-      <c r="G113" s="197"/>
-      <c r="H113" s="197"/>
-      <c r="I113" s="197"/>
-      <c r="J113" s="197"/>
-      <c r="K113" s="198"/>
-      <c r="L113" s="153"/>
-      <c r="M113" s="154"/>
+      <c r="F113" s="181"/>
+      <c r="G113" s="181"/>
+      <c r="H113" s="181"/>
+      <c r="I113" s="181"/>
+      <c r="J113" s="181"/>
+      <c r="K113" s="182"/>
+      <c r="L113" s="152"/>
+      <c r="M113" s="153"/>
     </row>
     <row r="114" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E114" s="153"/>
-      <c r="F114" s="156"/>
-      <c r="G114" s="156"/>
-      <c r="H114" s="156"/>
-      <c r="I114" s="156"/>
-      <c r="J114" s="156"/>
-      <c r="K114" s="154"/>
-      <c r="L114" s="153"/>
-      <c r="M114" s="154"/>
+      <c r="E114" s="152"/>
+      <c r="F114" s="155"/>
+      <c r="G114" s="155"/>
+      <c r="H114" s="155"/>
+      <c r="I114" s="155"/>
+      <c r="J114" s="155"/>
+      <c r="K114" s="153"/>
+      <c r="L114" s="152"/>
+      <c r="M114" s="153"/>
     </row>
     <row r="115" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E115" s="153" t="s">
+      <c r="E115" s="152" t="s">
         <v>114</v>
       </c>
-      <c r="F115" s="156"/>
-      <c r="G115" s="161" t="str">
+      <c r="F115" s="155"/>
+      <c r="G115" s="160" t="str">
         <f>C5</f>
         <v>Gomez Elizabeth</v>
       </c>
-      <c r="H115" s="156"/>
-      <c r="I115" s="156" t="s">
+      <c r="H115" s="155"/>
+      <c r="I115" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="J115" s="160">
+      <c r="J115" s="159">
         <v>45674</v>
       </c>
-      <c r="K115" s="154"/>
-      <c r="L115" s="181" t="s">
+      <c r="K115" s="153"/>
+      <c r="L115" s="183" t="s">
         <v>116</v>
       </c>
-      <c r="M115" s="182"/>
+      <c r="M115" s="184"/>
     </row>
     <row r="116" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E116" s="153" t="s">
+      <c r="E116" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="F116" s="161">
+      <c r="F116" s="160">
         <v>1</v>
       </c>
-      <c r="G116" s="156"/>
-      <c r="H116" s="156"/>
-      <c r="I116" s="156"/>
-      <c r="J116" s="156"/>
-      <c r="K116" s="154"/>
-      <c r="L116" s="153"/>
-      <c r="M116" s="154"/>
+      <c r="G116" s="155"/>
+      <c r="H116" s="155"/>
+      <c r="I116" s="155"/>
+      <c r="J116" s="155"/>
+      <c r="K116" s="153"/>
+      <c r="L116" s="152"/>
+      <c r="M116" s="153"/>
     </row>
     <row r="117" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E117" s="153"/>
-      <c r="F117" s="156"/>
-      <c r="G117" s="156"/>
-      <c r="H117" s="156"/>
-      <c r="I117" s="156"/>
-      <c r="J117" s="156"/>
-      <c r="K117" s="154"/>
-      <c r="L117" s="183"/>
-      <c r="M117" s="182"/>
+      <c r="E117" s="152"/>
+      <c r="F117" s="155"/>
+      <c r="G117" s="155"/>
+      <c r="H117" s="155"/>
+      <c r="I117" s="155"/>
+      <c r="J117" s="155"/>
+      <c r="K117" s="153"/>
+      <c r="L117" s="185"/>
+      <c r="M117" s="184"/>
     </row>
     <row r="118" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E118" s="153" t="s">
+      <c r="E118" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="F118" s="156"/>
-      <c r="G118" s="156"/>
-      <c r="H118" s="156"/>
-      <c r="I118" s="156"/>
-      <c r="J118" s="162">
+      <c r="F118" s="155"/>
+      <c r="G118" s="155"/>
+      <c r="H118" s="155"/>
+      <c r="I118" s="155"/>
+      <c r="J118" s="161">
         <f>J5</f>
         <v>0</v>
       </c>
-      <c r="K118" s="154"/>
-      <c r="L118" s="153"/>
-      <c r="M118" s="154"/>
+      <c r="K118" s="153"/>
+      <c r="L118" s="152"/>
+      <c r="M118" s="153"/>
     </row>
     <row r="119" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E119" s="163" t="s">
+      <c r="E119" s="162" t="s">
         <v>118</v>
       </c>
-      <c r="F119" s="156"/>
-      <c r="G119" s="156"/>
-      <c r="H119" s="156"/>
-      <c r="I119" s="156"/>
-      <c r="J119" s="162">
+      <c r="F119" s="155"/>
+      <c r="G119" s="155"/>
+      <c r="H119" s="155"/>
+      <c r="I119" s="155"/>
+      <c r="J119" s="161">
         <f>K5</f>
         <v>110400</v>
       </c>
-      <c r="K119" s="154"/>
-      <c r="L119" s="153"/>
-      <c r="M119" s="154"/>
+      <c r="K119" s="153"/>
+      <c r="L119" s="152"/>
+      <c r="M119" s="153"/>
     </row>
     <row r="120" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E120" s="163" t="s">
+      <c r="E120" s="162" t="s">
         <v>122</v>
       </c>
-      <c r="F120" s="156"/>
-      <c r="G120" s="156"/>
-      <c r="H120" s="156"/>
-      <c r="I120" s="156"/>
-      <c r="J120" s="162">
+      <c r="F120" s="155"/>
+      <c r="G120" s="155"/>
+      <c r="H120" s="155"/>
+      <c r="I120" s="155"/>
+      <c r="J120" s="161">
         <f>-20862.34+20810</f>
         <v>-52.340000000000146</v>
       </c>
-      <c r="K120" s="154"/>
-      <c r="L120" s="153"/>
-      <c r="M120" s="154"/>
+      <c r="K120" s="153"/>
+      <c r="L120" s="152"/>
+      <c r="M120" s="153"/>
     </row>
     <row r="121" spans="5:13" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E121" s="163"/>
-      <c r="F121" s="156"/>
-      <c r="G121" s="156"/>
-      <c r="H121" s="156"/>
-      <c r="I121" s="156"/>
-      <c r="J121" s="162"/>
-      <c r="K121" s="154"/>
-      <c r="L121" s="153"/>
-      <c r="M121" s="154"/>
+      <c r="E121" s="162"/>
+      <c r="F121" s="155"/>
+      <c r="G121" s="155"/>
+      <c r="H121" s="155"/>
+      <c r="I121" s="155"/>
+      <c r="J121" s="161"/>
+      <c r="K121" s="153"/>
+      <c r="L121" s="152"/>
+      <c r="M121" s="153"/>
     </row>
     <row r="122" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E122" s="163"/>
-      <c r="F122" s="156"/>
-      <c r="G122" s="156"/>
-      <c r="H122" s="156"/>
-      <c r="I122" s="156"/>
-      <c r="J122" s="162"/>
-      <c r="K122" s="154"/>
-      <c r="L122" s="153"/>
-      <c r="M122" s="154"/>
+      <c r="E122" s="162"/>
+      <c r="F122" s="155"/>
+      <c r="G122" s="155"/>
+      <c r="H122" s="155"/>
+      <c r="I122" s="155"/>
+      <c r="J122" s="161"/>
+      <c r="K122" s="153"/>
+      <c r="L122" s="152"/>
+      <c r="M122" s="153"/>
     </row>
     <row r="123" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F123" s="156"/>
-      <c r="G123" s="156"/>
-      <c r="H123" s="156"/>
-      <c r="I123" s="156"/>
-      <c r="J123" s="162"/>
-      <c r="K123" s="154"/>
-      <c r="L123" s="153"/>
-      <c r="M123" s="154"/>
+      <c r="F123" s="155"/>
+      <c r="G123" s="155"/>
+      <c r="H123" s="155"/>
+      <c r="I123" s="155"/>
+      <c r="J123" s="161"/>
+      <c r="K123" s="153"/>
+      <c r="L123" s="152"/>
+      <c r="M123" s="153"/>
     </row>
     <row r="124" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E124" s="163"/>
-      <c r="F124" s="156"/>
-      <c r="G124" s="156"/>
-      <c r="H124" s="156"/>
-      <c r="I124" s="156"/>
-      <c r="J124" s="162"/>
-      <c r="K124" s="154"/>
-      <c r="L124" s="153"/>
-      <c r="M124" s="154"/>
+      <c r="E124" s="162"/>
+      <c r="F124" s="155"/>
+      <c r="G124" s="155"/>
+      <c r="H124" s="155"/>
+      <c r="I124" s="155"/>
+      <c r="J124" s="161"/>
+      <c r="K124" s="153"/>
+      <c r="L124" s="152"/>
+      <c r="M124" s="153"/>
     </row>
     <row r="125" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E125" s="153"/>
-      <c r="F125" s="156"/>
-      <c r="G125" s="156"/>
-      <c r="H125" s="156"/>
-      <c r="I125" s="156"/>
-      <c r="J125" s="156"/>
-      <c r="K125" s="154"/>
-      <c r="L125" s="153"/>
-      <c r="M125" s="154"/>
+      <c r="E125" s="152"/>
+      <c r="F125" s="155"/>
+      <c r="G125" s="155"/>
+      <c r="H125" s="155"/>
+      <c r="I125" s="155"/>
+      <c r="J125" s="155"/>
+      <c r="K125" s="153"/>
+      <c r="L125" s="152"/>
+      <c r="M125" s="153"/>
     </row>
     <row r="126" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E126" s="153"/>
-      <c r="F126" s="156"/>
-      <c r="G126" s="156"/>
-      <c r="H126" s="156"/>
-      <c r="I126" s="156"/>
-      <c r="J126" s="156"/>
-      <c r="K126" s="154"/>
-      <c r="L126" s="153"/>
-      <c r="M126" s="154"/>
+      <c r="E126" s="152"/>
+      <c r="F126" s="155"/>
+      <c r="G126" s="155"/>
+      <c r="H126" s="155"/>
+      <c r="I126" s="155"/>
+      <c r="J126" s="155"/>
+      <c r="K126" s="153"/>
+      <c r="L126" s="152"/>
+      <c r="M126" s="153"/>
     </row>
     <row r="127" spans="5:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E127" s="153"/>
-      <c r="F127" s="156"/>
-      <c r="G127" s="156"/>
-      <c r="H127" s="156"/>
-      <c r="I127" s="156"/>
-      <c r="J127" s="156"/>
-      <c r="K127" s="154"/>
-      <c r="L127" s="164"/>
-      <c r="M127" s="165"/>
+      <c r="E127" s="152"/>
+      <c r="F127" s="155"/>
+      <c r="G127" s="155"/>
+      <c r="H127" s="155"/>
+      <c r="I127" s="155"/>
+      <c r="J127" s="155"/>
+      <c r="K127" s="153"/>
+      <c r="L127" s="163"/>
+      <c r="M127" s="164"/>
     </row>
     <row r="128" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E128" s="199" t="s">
+      <c r="E128" s="173" t="s">
         <v>119</v>
       </c>
-      <c r="F128" s="200"/>
-      <c r="G128" s="200"/>
-      <c r="H128" s="200"/>
-      <c r="I128" s="200"/>
-      <c r="J128" s="201">
+      <c r="F128" s="174"/>
+      <c r="G128" s="174"/>
+      <c r="H128" s="174"/>
+      <c r="I128" s="174"/>
+      <c r="J128" s="175">
         <f>SUM(J118:J127)</f>
         <v>110347.66</v>
       </c>
-      <c r="K128" s="194"/>
-      <c r="L128" s="166"/>
-      <c r="M128" s="167"/>
+      <c r="K128" s="176"/>
+      <c r="L128" s="165"/>
+      <c r="M128" s="166"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="E32:K32"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="E128:I128"/>
-    <mergeCell ref="J128:K128"/>
-    <mergeCell ref="E83:K83"/>
-    <mergeCell ref="E84:K84"/>
-    <mergeCell ref="E88:K88"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="L92:M92"/>
-    <mergeCell ref="E103:I103"/>
-    <mergeCell ref="J103:K103"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="E108:K108"/>
     <mergeCell ref="E109:K109"/>
@@ -8012,6 +7971,40 @@
     <mergeCell ref="L39:M39"/>
     <mergeCell ref="L41:M41"/>
     <mergeCell ref="E52:I52"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="L117:M117"/>
+    <mergeCell ref="E128:I128"/>
+    <mergeCell ref="J128:K128"/>
+    <mergeCell ref="E83:K83"/>
+    <mergeCell ref="E84:K84"/>
+    <mergeCell ref="E88:K88"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="L92:M92"/>
+    <mergeCell ref="E103:I103"/>
+    <mergeCell ref="J103:K103"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
